--- a/results/job_matches_2026-03-04.xlsx
+++ b/results/job_matches_2026-03-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G153"/>
+  <dimension ref="A1:G156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer II (Hybrid Work Schedule)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Hilti Group</t>
+          <t>Quorum Software</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.3</v>
+        <v>22.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9998eca1dfe5af6d</t>
+          <t>https://www.indeed.com/viewjob?jk=76a633e7c45d5fa0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Application Developer</t>
+          <t>Data Engineer II (Hybrid Work Schedule)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PENNYMAC</t>
+          <t>Quorum Business Solutions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Carrollton, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23.6</v>
+        <v>22.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Step Functions, S3, SQS, SNS, ECS</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc189598639baae0</t>
+          <t>https://www.indeed.com/viewjob?jk=5f1e509811f28e16</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer II (Hybrid Work Schedule)</t>
+          <t>Software Engineer in Test III - Data Analytics</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Quorum Software</t>
+          <t>Emburse</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>22.9</v>
+        <v>21.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76a633e7c45d5fa0</t>
+          <t>https://www.indeed.com/viewjob?jk=450782bf82b6fc2f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer II (Hybrid Work Schedule)</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Quorum Business Solutions</t>
+          <t>Altak Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>22.9</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,102 +601,102 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f1e509811f28e16</t>
+          <t>https://www.indeed.com/viewjob?jk=afe6c49fa2525821</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AWS/Python Engineer</t>
+          <t>Full Stack Engineer (React + Node.js)-4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>22.2</v>
+        <v>20.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=188fa78b94de887a</t>
+          <t>https://www.indeed.com/viewjob?jk=e082e26fc29250a3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer in Test III - Data Analytics</t>
+          <t>Data Engineer/Python Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Emburse</t>
+          <t>Zifo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>21.5</v>
+        <v>20.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=450782bf82b6fc2f</t>
+          <t>https://www.indeed.com/viewjob?jk=3419a1d7b4acb559</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Network IoT Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Altak Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Azure</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,102 +706,102 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afe6c49fa2525821</t>
+          <t>https://www.indeed.com/viewjob?jk=4725509304854f9e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (React + Node.js)-4</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Quilt</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e082e26fc29250a3</t>
+          <t>https://www.indeed.com/viewjob?jk=27d883fd388e687a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Systems Integration Engineer</t>
+          <t>Data Engineer - AI Practice Team</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Bureau of Shipping (ABS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Eau Claire, WI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Timestream, S3, API Gateway, ECS, IAM, RDS, Kafka</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Azure, Data Factory, Databricks, Event Hubs, BigQuery</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c312e3c7f58bcc51</t>
+          <t>https://www.indeed.com/viewjob?jk=98e9bc7cd1938bfd</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Network IoT Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, API Gateway, IAM</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4725509304854f9e</t>
+          <t>https://www.indeed.com/viewjob?jk=a6c4839e7fe64d8e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer - AI Practice Team</t>
+          <t>Senior Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>American Bureau of Shipping (ABS)</t>
+          <t>ALTRUIST</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Azure, Data Factory, Databricks, Event Hubs, BigQuery</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98e9bc7cd1938bfd</t>
+          <t>https://www.indeed.com/viewjob?jk=cc6ad57eba624292</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc6ad57eba624292</t>
+          <t>https://www.indeed.com/viewjob?jk=15325ad687b27337</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Infrastructure</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ALTRUIST</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15325ad687b27337</t>
+          <t>https://www.indeed.com/viewjob?jk=17c87f0de0ddb952</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Backend Software Engineer III - API Platform</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, API Gateway, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,59 +951,59 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17c87f0de0ddb952</t>
+          <t>https://www.indeed.com/viewjob?jk=fd1c3ba542522bad</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Backend Software Engineer III - API Platform</t>
+          <t>Cloud Engineer- Remote US</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, API Gateway, RDS, Databricks, Spark</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd1c3ba542522bad</t>
+          <t>https://www.indeed.com/viewjob?jk=f25625460182eb8e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud Engineer- Remote US</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f25625460182eb8e</t>
+          <t>https://www.indeed.com/viewjob?jk=0997a11d6aaf4e73</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Analyst, Risk Data Engineering</t>
+          <t>Software Engineer II,</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Redshift, ECS, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52bc5a9a6e784515</t>
+          <t>https://www.indeed.com/viewjob?jk=b4edb591674d441f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Engineering Analytics</t>
+          <t>Software Engineer II,</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Delta Air Lines</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Snowflake, NoSQL</t>
+          <t>AWS, Redshift, ECS, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b32e7d55317e214e</t>
+          <t>https://www.indeed.com/viewjob?jk=28ab3491bb9f5589</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Blockchain Java Backend Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,94 +1126,94 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0997a11d6aaf4e73</t>
+          <t>https://www.indeed.com/viewjob?jk=e49019e3e57d794c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer II,</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4edb591674d441f</t>
+          <t>https://www.indeed.com/viewjob?jk=4cc63cdd2328277c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer II,</t>
+          <t>Sr. Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>ELLKAY, LLC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Elmwood Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, Athena, IAM, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28ab3491bb9f5589</t>
+          <t>https://www.indeed.com/viewjob?jk=28b63f4ef510667a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Cloud Software Engineer</t>
+          <t>Associate/Consultant Engineer - Remote</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ELLKAY, LLC</t>
+          <t>Rancho BioSciences</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Elmwood Park, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28b63f4ef510667a</t>
+          <t>https://www.indeed.com/viewjob?jk=72630d316687619c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer, AI Analytics</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>Residex, LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,42 +1256,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7d093becf8bff38</t>
+          <t>https://www.indeed.com/viewjob?jk=3b994e1736909aed</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Associate/Consultant Engineer - Remote</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Rancho BioSciences</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72630d316687619c</t>
+          <t>https://www.indeed.com/viewjob?jk=2b12dfc8a5459a4f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b12dfc8a5459a4f</t>
+          <t>https://www.indeed.com/viewjob?jk=b08c3dc1b325be49</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b08c3dc1b325be49</t>
+          <t>https://www.indeed.com/viewjob?jk=7d49d017dead0cec</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer - Kafka Connect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>CloudRay Inc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d49d017dead0cec</t>
+          <t>https://www.indeed.com/viewjob?jk=d5df3111682f7946</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer - Kafka Connect</t>
+          <t>Associate/Consultant Engineer - Remote</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CloudRay Inc</t>
+          <t>Rancho BioSciences</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5df3111682f7946</t>
+          <t>https://www.indeed.com/viewjob?jk=cd467efc7d909226</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Production Engineer (Oracle/Snowflake/Python)</t>
+          <t>Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,77 +1466,77 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7435b55b7adadc42</t>
+          <t>https://www.indeed.com/viewjob?jk=80460d4e824e28cc</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Associate/Consultant Engineer - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Rancho BioSciences</t>
+          <t>ROLLER</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd467efc7d909226</t>
+          <t>https://www.indeed.com/viewjob?jk=afb709659d664135</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer - Remote</t>
+          <t>Cloud Data Engineer + Snowflake (On-Site)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
+          <t>AWS, Glue, EMR, RDS, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80460d4e824e28cc</t>
+          <t>https://www.indeed.com/viewjob?jk=58e9f31119d31013</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer, CDC</t>
+          <t>PDM Implementation Data Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DRT Strategies, Inc.</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Scala, ETL, Power BI, Tableau, CI/CD, Docker</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a223a368864e5d1b</t>
+          <t>https://www.indeed.com/viewjob?jk=3576de9e88dd4c5c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data engineer</t>
+          <t>Cloud Identity Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=892431136a2962f3</t>
+          <t>https://www.indeed.com/viewjob?jk=fdd1e41d5949d150</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PDM Implementation Data Architect</t>
+          <t>Senior Java / IBM ACE Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,17 +1711,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3576de9e88dd4c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=70a91ea32c4e2e98</t>
         </is>
       </c>
     </row>
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Java / IBM ACE Developer</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>ivo</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70a91ea32c4e2e98</t>
+          <t>https://www.indeed.com/viewjob?jk=8bc5aaef611937ad</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cloud Identity Architect</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ai Vantage</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdd1e41d5949d150</t>
+          <t>https://www.indeed.com/viewjob?jk=87747bfcd30cdbc2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>System Integration Test Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ai Vantage</t>
+          <t>BGIT India Private Limited</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Hudson, NH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87747bfcd30cdbc2</t>
+          <t>https://www.indeed.com/viewjob?jk=426d1d0d6a93918c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>System Integration Test Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BGIT India Private Limited</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hudson, NH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,59 +1896,59 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=426d1d0d6a93918c</t>
+          <t>https://www.indeed.com/viewjob?jk=a7c80e2086f0d108</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Data Platform Engineer-2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7c80e2086f0d108</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f9103ddd4f544e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-2</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,17 +1956,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f9103ddd4f544e</t>
+          <t>https://www.indeed.com/viewjob?jk=75d602908669423e</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d602908669423e</t>
+          <t>https://www.indeed.com/viewjob?jk=10de5f0ca2f7673d</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10de5f0ca2f7673d</t>
+          <t>https://www.indeed.com/viewjob?jk=8e6750fd9ad4e72e</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6750fd9ad4e72e</t>
+          <t>https://www.indeed.com/viewjob?jk=c45db6ac50eb5587</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45db6ac50eb5587</t>
+          <t>https://www.indeed.com/viewjob?jk=d1c0f7e27e90a87e</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1c0f7e27e90a87e</t>
+          <t>https://www.indeed.com/viewjob?jk=a4dc81e5cd9b6b72</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4dc81e5cd9b6b72</t>
+          <t>https://www.indeed.com/viewjob?jk=14fea47c1dbfabac</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14fea47c1dbfabac</t>
+          <t>https://www.indeed.com/viewjob?jk=02d7bcc2bd0697b0</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02d7bcc2bd0697b0</t>
+          <t>https://www.indeed.com/viewjob?jk=50e0ff85e5f89851</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50e0ff85e5f89851</t>
+          <t>https://www.indeed.com/viewjob?jk=662840de4364e997</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Software Engineer II - Scala</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=662840de4364e997</t>
+          <t>https://www.indeed.com/viewjob?jk=d148fa8c6ae39fd8</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer II - Scala</t>
+          <t>ETL Testing with Azure Databricks in Healthcare</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d148fa8c6ae39fd8</t>
+          <t>https://www.indeed.com/viewjob?jk=9af37a4075a8760f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cloud &amp; Systems Engineer</t>
+          <t>Risk Data AI/ML Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Global Healing Center</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SNS, API Gateway, IAM, Scala, SQL Server, DynamoDB</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ae1e7d38a178a6</t>
+          <t>https://www.indeed.com/viewjob?jk=979402388d34b409</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ETL Testing with Azure Databricks in Healthcare</t>
+          <t>Senior Databricks AI Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>Powerplan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Scala, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9af37a4075a8760f</t>
+          <t>https://www.indeed.com/viewjob?jk=3b5753d39b44c782</t>
         </is>
       </c>
     </row>
@@ -2533,35 +2533,35 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>KLA</t>
+          <t>PEARLY</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Santa Barbara, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=659e59333f0b2e8c</t>
+          <t>https://www.indeed.com/viewjob?jk=52fbd92226aade92</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Santa Barbara, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52fbd92226aade92</t>
+          <t>https://www.indeed.com/viewjob?jk=3e77317858ff838d</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e77317858ff838d</t>
+          <t>https://www.indeed.com/viewjob?jk=9737f288d965528f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9737f288d965528f</t>
+          <t>https://www.indeed.com/viewjob?jk=7fc978b16714d0d2</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fc978b16714d0d2</t>
+          <t>https://www.indeed.com/viewjob?jk=9649d08cb62a9ac0</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Network IoT Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9649d08cb62a9ac0</t>
+          <t>https://www.indeed.com/viewjob?jk=0da29d3af250447a</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Hadoop, Spark, Scala, Kafka, Cassandra, NoSQL</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56c2a6bb8439d052</t>
+          <t>https://www.indeed.com/viewjob?jk=b7dfde3b442bd5c7</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Network IoT Engineer</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Clarksville, TN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da29d3af250447a</t>
+          <t>https://www.indeed.com/viewjob?jk=503ceed67966f48a</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>DatamanUSA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, PostgreSQL, Dimensional Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7dfde3b442bd5c7</t>
+          <t>https://www.indeed.com/viewjob?jk=9672d81f2806d2a2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Cloud Identity Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Clarksville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, Google Cloud Platform, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503ceed67966f48a</t>
+          <t>https://www.indeed.com/viewjob?jk=5b1a799d8b14436a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>DatamanUSA</t>
+          <t>ABCorp NA Inc.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, PostgreSQL, Dimensional Modeling, Star Schema, Snowflake Schema</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9672d81f2806d2a2</t>
+          <t>https://www.indeed.com/viewjob?jk=5d8f6d93b707b783</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Cloud Identity Architect</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, Google Cloud Platform, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b1a799d8b14436a</t>
+          <t>https://www.indeed.com/viewjob?jk=6006f51c65e9f139</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ABCorp NA Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d8f6d93b707b783</t>
+          <t>https://www.indeed.com/viewjob?jk=205804a055fd2049</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6006f51c65e9f139</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c5706918e358a0</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=205804a055fd2049</t>
+          <t>https://www.indeed.com/viewjob?jk=10a398f9aeeb6c7d</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5c5706918e358a0</t>
+          <t>https://www.indeed.com/viewjob?jk=c8977f5b4ab10d23</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10a398f9aeeb6c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=e93b71ab143505ef</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8977f5b4ab10d23</t>
+          <t>https://www.indeed.com/viewjob?jk=640d49c55b368f21</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93b71ab143505ef</t>
+          <t>https://www.indeed.com/viewjob?jk=d37ce07d5d4393f3</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=640d49c55b368f21</t>
+          <t>https://www.indeed.com/viewjob?jk=e10aa5fc172c0cf9</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d37ce07d5d4393f3</t>
+          <t>https://www.indeed.com/viewjob?jk=58a1d20202a2aef8</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10aa5fc172c0cf9</t>
+          <t>https://www.indeed.com/viewjob?jk=a8185d403faf25e2</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58a1d20202a2aef8</t>
+          <t>https://www.indeed.com/viewjob?jk=6a014ab60dbd75f0</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8185d403faf25e2</t>
+          <t>https://www.indeed.com/viewjob?jk=f103c6f8f1eabe61</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a014ab60dbd75f0</t>
+          <t>https://www.indeed.com/viewjob?jk=3ae886d34419a9a7</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f103c6f8f1eabe61</t>
+          <t>https://www.indeed.com/viewjob?jk=7cfd83638c49b733</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae886d34419a9a7</t>
+          <t>https://www.indeed.com/viewjob?jk=592db9bfc62c64e2</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cfd83638c49b733</t>
+          <t>https://www.indeed.com/viewjob?jk=83814a502692afe0</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=592db9bfc62c64e2</t>
+          <t>https://www.indeed.com/viewjob?jk=1a7005ca8416f01f</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83814a502692afe0</t>
+          <t>https://www.indeed.com/viewjob?jk=616e989c777fcd64</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a7005ca8416f01f</t>
+          <t>https://www.indeed.com/viewjob?jk=4a46aa375a4da0e2</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=616e989c777fcd64</t>
+          <t>https://www.indeed.com/viewjob?jk=6904e697ef07baaf</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a46aa375a4da0e2</t>
+          <t>https://www.indeed.com/viewjob?jk=3dc64b2070c5c6f8</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6904e697ef07baaf</t>
+          <t>https://www.indeed.com/viewjob?jk=3ee7574e666ce713</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dc64b2070c5c6f8</t>
+          <t>https://www.indeed.com/viewjob?jk=e99bc4057502816b</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ee7574e666ce713</t>
+          <t>https://www.indeed.com/viewjob?jk=8810eb13c55de856</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99bc4057502816b</t>
+          <t>https://www.indeed.com/viewjob?jk=7372945ed1cbee22</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8810eb13c55de856</t>
+          <t>https://www.indeed.com/viewjob?jk=e06b4f714255d00b</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7372945ed1cbee22</t>
+          <t>https://www.indeed.com/viewjob?jk=c81cd4c9bce9e715</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06b4f714255d00b</t>
+          <t>https://www.indeed.com/viewjob?jk=8cec639e703e1f70</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c81cd4c9bce9e715</t>
+          <t>https://www.indeed.com/viewjob?jk=c7628f7ec7ab09a9</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cec639e703e1f70</t>
+          <t>https://www.indeed.com/viewjob?jk=d764f5358afc422f</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7628f7ec7ab09a9</t>
+          <t>https://www.indeed.com/viewjob?jk=95628c711a619430</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d764f5358afc422f</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4e67862f3b9941</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95628c711a619430</t>
+          <t>https://www.indeed.com/viewjob?jk=2963649fc0f492cf</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4e67862f3b9941</t>
+          <t>https://www.indeed.com/viewjob?jk=745b60449ed066d9</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2963649fc0f492cf</t>
+          <t>https://www.indeed.com/viewjob?jk=8c80024050212c2d</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=745b60449ed066d9</t>
+          <t>https://www.indeed.com/viewjob?jk=4b032019de44f8fc</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c80024050212c2d</t>
+          <t>https://www.indeed.com/viewjob?jk=9a0ff3586081cca1</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b032019de44f8fc</t>
+          <t>https://www.indeed.com/viewjob?jk=c2a1744462634cc8</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a0ff3586081cca1</t>
+          <t>https://www.indeed.com/viewjob?jk=49f69babc93629c9</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2a1744462634cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=d8ca948db3aefbff</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49f69babc93629c9</t>
+          <t>https://www.indeed.com/viewjob?jk=61326d67184dc890</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8ca948db3aefbff</t>
+          <t>https://www.indeed.com/viewjob?jk=c4f0c70aeab55966</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61326d67184dc890</t>
+          <t>https://www.indeed.com/viewjob?jk=84f5e91eebbc9f06</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4f0c70aeab55966</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2b8dad0cc443b9</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84f5e91eebbc9f06</t>
+          <t>https://www.indeed.com/viewjob?jk=d7e348dae6016f17</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2b8dad0cc443b9</t>
+          <t>https://www.indeed.com/viewjob?jk=c0cf9334f4d71f83</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7e348dae6016f17</t>
+          <t>https://www.indeed.com/viewjob?jk=d9c6c1388c411eb4</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0cf9334f4d71f83</t>
+          <t>https://www.indeed.com/viewjob?jk=19d19e0ea73bf12c</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,32 +4661,32 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9c6c1388c411eb4</t>
+          <t>https://www.indeed.com/viewjob?jk=8f611a382e3aa720</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Middesk</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, Lambda, RDS, Azure, Spark, Data Modeling, Terraform, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,32 +4696,32 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d19e0ea73bf12c</t>
+          <t>https://www.indeed.com/viewjob?jk=514717df8eb087ca</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Engineer III - Data Engineering Java/Python</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f611a382e3aa720</t>
+          <t>https://www.indeed.com/viewjob?jk=6dfc1c1ddf5b07e8</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Platform</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Middesk</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Spark, Data Modeling, Terraform, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=514717df8eb087ca</t>
+          <t>https://www.indeed.com/viewjob?jk=cab7b07d708701fa</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Engineering Java/Python</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
+          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, Kafka, Dimensional Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dfc1c1ddf5b07e8</t>
+          <t>https://www.indeed.com/viewjob?jk=503c92a0918e2779</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>API Developer Jr.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>MKS2 Technologies</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, RDS, Scala, Oracle, MySQL, MongoDB, DynamoDB, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab7b07d708701fa</t>
+          <t>https://www.indeed.com/viewjob?jk=976d4320b891418b</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>API Developer, Mid</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>MKS2 Technologies</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
+          <t>AWS, RDS, Scala, Oracle, MySQL, MongoDB, DynamoDB, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d0cf03fccf9f1cb</t>
+          <t>https://www.indeed.com/viewjob?jk=982682f617c5fe52</t>
         </is>
       </c>
     </row>
@@ -5053,17 +5053,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Risk Developer (Python/Azure)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, MLflow, CI/CD</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7762d03304071b69</t>
+          <t>https://www.indeed.com/viewjob?jk=6d0cf03fccf9f1cb</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Risk Developer (Python/Azure)</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>hatch IT</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, ETL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b260e746e7b9c233</t>
+          <t>https://www.indeed.com/viewjob?jk=7762d03304071b69</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE)</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>hatch IT</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c08c735142c13e1b</t>
+          <t>https://www.indeed.com/viewjob?jk=57ca41478bb936cd</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>hatch IT</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Dresher, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a3b73f36e3384d3</t>
+          <t>https://www.indeed.com/viewjob?jk=b260e746e7b9c233</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>.NET Angular Reporting Developer</t>
+          <t>Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>hatch IT</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, Star Schema, ETL, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, ECS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,32 +5221,32 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21a948f0ac42414</t>
+          <t>https://www.indeed.com/viewjob?jk=c08c735142c13e1b</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer III</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Kapitus</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dresher, PA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,32 +5256,32 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31099f3a1c434171</t>
+          <t>https://www.indeed.com/viewjob?jk=2a3b73f36e3384d3</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>.NET Angular Reporting Developer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, Star Schema, ETL, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fd50cad36943ce</t>
+          <t>https://www.indeed.com/viewjob?jk=f21a948f0ac42414</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Data Engineer(61249-1)</t>
+          <t>Entry-Level Data Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Vytwo Technologies</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Prosper, TX, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5fdd13d31dd0aa1</t>
+          <t>https://www.indeed.com/viewjob?jk=dd80dc2e6636141e</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer - Oracle Cloud Infrastructure (OCI)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>APi Group, Inc.</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>New Brighton, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Git</t>
+          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6450f77aa7cdc7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=8b5cdc524b199967</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Azure Stack Data Engineer</t>
+          <t>DevSecOps Engineer III</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>AAON</t>
+          <t>Kapitus</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,34 +5386,34 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Data Modeling, ETL, Power BI, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20dcbc83d5643838</t>
+          <t>https://www.indeed.com/viewjob?jk=31099f3a1c434171</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=843b039e4e75f61f</t>
+          <t>https://www.indeed.com/viewjob?jk=29fd50cad36943ce</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Senior Data Engineer(61249-1)</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Vytwo Technologies</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Prosper, TX, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, Airflow</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5c91aac0db662ae</t>
+          <t>https://www.indeed.com/viewjob?jk=b5fdd13d31dd0aa1</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>SSO Administrator</t>
+          <t>Senior Systems Engineer - Oracle Cloud Infrastructure (OCI)</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>APi Group, Inc.</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New Brighton, MN, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b109c86f55c8c21f</t>
+          <t>https://www.indeed.com/viewjob?jk=6450f77aa7cdc7c1</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>DOCSIS Testing Engineer</t>
+          <t>Azure Stack Data Engineer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AAON</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,34 +5526,34 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, NoSQL, ETL, ELT, Splunk, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Data Modeling, ETL, Power BI, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e134c7566cf151c</t>
+          <t>https://www.indeed.com/viewjob?jk=20dcbc83d5643838</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>DOCSIS Testing Engineer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, NoSQL, ETL, ELT, Splunk, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ead7f0da7c5db1</t>
+          <t>https://www.indeed.com/viewjob?jk=0e134c7566cf151c</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>SSO Administrator</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae8a17a1c6f39e3</t>
+          <t>https://www.indeed.com/viewjob?jk=b109c86f55c8c21f</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=739e08afe4ba1176</t>
+          <t>https://www.indeed.com/viewjob?jk=843b039e4e75f61f</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (FDE)</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>ISHIR</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,34 +5666,34 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ecc0cd2b5a2111</t>
+          <t>https://www.indeed.com/viewjob?jk=e5c91aac0db662ae</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
+          <t>Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>ISHIR</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,34 +5701,34 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=151fe9868f44f2f1</t>
+          <t>https://www.indeed.com/viewjob?jk=15ecc0cd2b5a2111</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>IT PROFESSIONAL-APPLICATIONS (Database Administrator) (HEC)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>City of Houston, TX</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c369e1e8241c9f</t>
+          <t>https://www.indeed.com/viewjob?jk=c1ead7f0da7c5db1</t>
         </is>
       </c>
     </row>
@@ -5758,12 +5758,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,17 +5771,122 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b2c457ac06652a</t>
+          <t>https://www.indeed.com/viewjob?jk=1ae8a17a1c6f39e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Reporting Engineer</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Surgery Partners</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=739e08afe4ba1176</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>CrowdStrike</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=151fe9868f44f2f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>IT PROFESSIONAL-APPLICATIONS (Database Administrator) (HEC)</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>City of Houston, TX</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1c369e1e8241c9f</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-04.xlsx
+++ b/results/job_matches_2026-03-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G156"/>
+  <dimension ref="A1:G159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1063,17 +1063,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer II,</t>
+          <t>Blockchain Java Backend Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28ab3491bb9f5589</t>
+          <t>https://www.indeed.com/viewjob?jk=e49019e3e57d794c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Blockchain Java Backend Engineer</t>
+          <t>Software Engineer, AI Analytics</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Residex, LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e49019e3e57d794c</t>
+          <t>https://www.indeed.com/viewjob?jk=3b994e1736909aed</t>
         </is>
       </c>
     </row>
@@ -1238,25 +1238,25 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer, AI Analytics</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Residex, LLC</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b994e1736909aed</t>
+          <t>https://www.indeed.com/viewjob?jk=2b12dfc8a5459a4f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b12dfc8a5459a4f</t>
+          <t>https://www.indeed.com/viewjob?jk=b08c3dc1b325be49</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b08c3dc1b325be49</t>
+          <t>https://www.indeed.com/viewjob?jk=7d49d017dead0cec</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer - Kafka Connect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>CloudRay Inc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d49d017dead0cec</t>
+          <t>https://www.indeed.com/viewjob?jk=d5df3111682f7946</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer - Kafka Connect</t>
+          <t>Senior Data Cloud Architect - SI Partners</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CloudRay Inc</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Azure, Data Factory, GCP, Spark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5df3111682f7946</t>
+          <t>https://www.indeed.com/viewjob?jk=ba51b24a2f032664</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PDM Implementation Data Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Spark, PySpark</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3576de9e88dd4c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=39a6c4ab9efc012e</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cloud Identity Architect</t>
+          <t>PDM Implementation Data Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdd1e41d5949d150</t>
+          <t>https://www.indeed.com/viewjob?jk=3576de9e88dd4c5c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Java / IBM ACE Developer</t>
+          <t>Cloud Identity Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,24 +1711,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, Azure DevOps</t>
+          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70a91ea32c4e2e98</t>
+          <t>https://www.indeed.com/viewjob?jk=fdd1e41d5949d150</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Java / IBM ACE Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd0439895496e24</t>
+          <t>https://www.indeed.com/viewjob?jk=70a91ea32c4e2e98</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ivo</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bc5aaef611937ad</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd0439895496e24</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ai Vantage</t>
+          <t>ivo</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87747bfcd30cdbc2</t>
+          <t>https://www.indeed.com/viewjob?jk=8bc5aaef611937ad</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>System Integration Test Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BGIT India Private Limited</t>
+          <t>Ai Vantage</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Hudson, NH, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=426d1d0d6a93918c</t>
+          <t>https://www.indeed.com/viewjob?jk=87747bfcd30cdbc2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>System Integration Test Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>BGIT India Private Limited</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Hudson, NH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,59 +1896,59 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7c80e2086f0d108</t>
+          <t>https://www.indeed.com/viewjob?jk=426d1d0d6a93918c</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-2</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f9103ddd4f544e</t>
+          <t>https://www.indeed.com/viewjob?jk=a7c80e2086f0d108</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>Data Platform Engineer-2</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,17 +1956,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d602908669423e</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f9103ddd4f544e</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10de5f0ca2f7673d</t>
+          <t>https://www.indeed.com/viewjob?jk=75d602908669423e</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6750fd9ad4e72e</t>
+          <t>https://www.indeed.com/viewjob?jk=10de5f0ca2f7673d</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45db6ac50eb5587</t>
+          <t>https://www.indeed.com/viewjob?jk=8e6750fd9ad4e72e</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1c0f7e27e90a87e</t>
+          <t>https://www.indeed.com/viewjob?jk=c45db6ac50eb5587</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4dc81e5cd9b6b72</t>
+          <t>https://www.indeed.com/viewjob?jk=d1c0f7e27e90a87e</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14fea47c1dbfabac</t>
+          <t>https://www.indeed.com/viewjob?jk=a4dc81e5cd9b6b72</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02d7bcc2bd0697b0</t>
+          <t>https://www.indeed.com/viewjob?jk=14fea47c1dbfabac</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50e0ff85e5f89851</t>
+          <t>https://www.indeed.com/viewjob?jk=02d7bcc2bd0697b0</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=662840de4364e997</t>
+          <t>https://www.indeed.com/viewjob?jk=50e0ff85e5f89851</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer II - Scala</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d148fa8c6ae39fd8</t>
+          <t>https://www.indeed.com/viewjob?jk=662840de4364e997</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ETL Testing with Azure Databricks in Healthcare</t>
+          <t>Software Engineer II - Scala</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Scala, Oracle</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9af37a4075a8760f</t>
+          <t>https://www.indeed.com/viewjob?jk=d148fa8c6ae39fd8</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Risk Data AI/ML Engineer</t>
+          <t>ETL Testing with Azure Databricks in Healthcare</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=979402388d34b409</t>
+          <t>https://www.indeed.com/viewjob?jk=9af37a4075a8760f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Databricks AI Engineer</t>
+          <t>Risk Data AI/ML Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Powerplan</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5753d39b44c782</t>
+          <t>https://www.indeed.com/viewjob?jk=979402388d34b409</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Databricks AI Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ELLKAY, LLC</t>
+          <t>Powerplan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Elmwood Park, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Streams/Tasks</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7bfd917914d4728</t>
+          <t>https://www.indeed.com/viewjob?jk=3b5753d39b44c782</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>ELLKAY, LLC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Elmwood Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, EMR, S3, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Streams/Tasks</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9886d247b0ec7a02</t>
+          <t>https://www.indeed.com/viewjob?jk=c7bfd917914d4728</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Platform-DevOps Engineer</t>
+          <t>Sr DevOPS Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NXLog</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e7328772f0c8abe</t>
+          <t>https://www.indeed.com/viewjob?jk=9886d247b0ec7a02</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Platform-DevOps Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>NXLog</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Santa Barbara, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52fbd92226aade92</t>
+          <t>https://www.indeed.com/viewjob?jk=6e7328772f0c8abe</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Santa Barbara, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e77317858ff838d</t>
+          <t>https://www.indeed.com/viewjob?jk=52fbd92226aade92</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9737f288d965528f</t>
+          <t>https://www.indeed.com/viewjob?jk=3e77317858ff838d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PEARLY</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT, MLflow</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fc978b16714d0d2</t>
+          <t>https://www.indeed.com/viewjob?jk=9737f288d965528f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9649d08cb62a9ac0</t>
+          <t>https://www.indeed.com/viewjob?jk=7fc978b16714d0d2</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Network IoT Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da29d3af250447a</t>
+          <t>https://www.indeed.com/viewjob?jk=9649d08cb62a9ac0</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Network IoT Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7dfde3b442bd5c7</t>
+          <t>https://www.indeed.com/viewjob?jk=0da29d3af250447a</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>AI Solution Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>Velvetech</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Clarksville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503ceed67966f48a</t>
+          <t>https://www.indeed.com/viewjob?jk=e6435ac5193c56de</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>DatamanUSA</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, PostgreSQL, Dimensional Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9672d81f2806d2a2</t>
+          <t>https://www.indeed.com/viewjob?jk=b7dfde3b442bd5c7</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cloud Identity Architect</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Clarksville, TN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, Google Cloud Platform, Vertex AI, Scala</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b1a799d8b14436a</t>
+          <t>https://www.indeed.com/viewjob?jk=503ceed67966f48a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ABCorp NA Inc.</t>
+          <t>DatamanUSA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, PostgreSQL, Dimensional Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d8f6d93b707b783</t>
+          <t>https://www.indeed.com/viewjob?jk=9672d81f2806d2a2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Cloud Identity Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, Google Cloud Platform, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6006f51c65e9f139</t>
+          <t>https://www.indeed.com/viewjob?jk=5b1a799d8b14436a</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>ABCorp NA Inc.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=205804a055fd2049</t>
+          <t>https://www.indeed.com/viewjob?jk=5d8f6d93b707b783</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5c5706918e358a0</t>
+          <t>https://www.indeed.com/viewjob?jk=6006f51c65e9f139</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10a398f9aeeb6c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=205804a055fd2049</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8977f5b4ab10d23</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c5706918e358a0</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93b71ab143505ef</t>
+          <t>https://www.indeed.com/viewjob?jk=10a398f9aeeb6c7d</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=640d49c55b368f21</t>
+          <t>https://www.indeed.com/viewjob?jk=c8977f5b4ab10d23</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d37ce07d5d4393f3</t>
+          <t>https://www.indeed.com/viewjob?jk=e93b71ab143505ef</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10aa5fc172c0cf9</t>
+          <t>https://www.indeed.com/viewjob?jk=640d49c55b368f21</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58a1d20202a2aef8</t>
+          <t>https://www.indeed.com/viewjob?jk=d37ce07d5d4393f3</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8185d403faf25e2</t>
+          <t>https://www.indeed.com/viewjob?jk=e10aa5fc172c0cf9</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a014ab60dbd75f0</t>
+          <t>https://www.indeed.com/viewjob?jk=58a1d20202a2aef8</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f103c6f8f1eabe61</t>
+          <t>https://www.indeed.com/viewjob?jk=a8185d403faf25e2</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae886d34419a9a7</t>
+          <t>https://www.indeed.com/viewjob?jk=6a014ab60dbd75f0</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cfd83638c49b733</t>
+          <t>https://www.indeed.com/viewjob?jk=f103c6f8f1eabe61</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=592db9bfc62c64e2</t>
+          <t>https://www.indeed.com/viewjob?jk=3ae886d34419a9a7</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83814a502692afe0</t>
+          <t>https://www.indeed.com/viewjob?jk=7cfd83638c49b733</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a7005ca8416f01f</t>
+          <t>https://www.indeed.com/viewjob?jk=592db9bfc62c64e2</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=616e989c777fcd64</t>
+          <t>https://www.indeed.com/viewjob?jk=83814a502692afe0</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a46aa375a4da0e2</t>
+          <t>https://www.indeed.com/viewjob?jk=1a7005ca8416f01f</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6904e697ef07baaf</t>
+          <t>https://www.indeed.com/viewjob?jk=616e989c777fcd64</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dc64b2070c5c6f8</t>
+          <t>https://www.indeed.com/viewjob?jk=4a46aa375a4da0e2</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ee7574e666ce713</t>
+          <t>https://www.indeed.com/viewjob?jk=6904e697ef07baaf</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99bc4057502816b</t>
+          <t>https://www.indeed.com/viewjob?jk=3dc64b2070c5c6f8</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8810eb13c55de856</t>
+          <t>https://www.indeed.com/viewjob?jk=3ee7574e666ce713</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7372945ed1cbee22</t>
+          <t>https://www.indeed.com/viewjob?jk=e99bc4057502816b</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06b4f714255d00b</t>
+          <t>https://www.indeed.com/viewjob?jk=8810eb13c55de856</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c81cd4c9bce9e715</t>
+          <t>https://www.indeed.com/viewjob?jk=7372945ed1cbee22</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cec639e703e1f70</t>
+          <t>https://www.indeed.com/viewjob?jk=e06b4f714255d00b</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7628f7ec7ab09a9</t>
+          <t>https://www.indeed.com/viewjob?jk=c81cd4c9bce9e715</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d764f5358afc422f</t>
+          <t>https://www.indeed.com/viewjob?jk=8cec639e703e1f70</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95628c711a619430</t>
+          <t>https://www.indeed.com/viewjob?jk=c7628f7ec7ab09a9</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4e67862f3b9941</t>
+          <t>https://www.indeed.com/viewjob?jk=d764f5358afc422f</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2963649fc0f492cf</t>
+          <t>https://www.indeed.com/viewjob?jk=95628c711a619430</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=745b60449ed066d9</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4e67862f3b9941</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c80024050212c2d</t>
+          <t>https://www.indeed.com/viewjob?jk=2963649fc0f492cf</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b032019de44f8fc</t>
+          <t>https://www.indeed.com/viewjob?jk=745b60449ed066d9</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a0ff3586081cca1</t>
+          <t>https://www.indeed.com/viewjob?jk=8c80024050212c2d</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2a1744462634cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=4b032019de44f8fc</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49f69babc93629c9</t>
+          <t>https://www.indeed.com/viewjob?jk=9a0ff3586081cca1</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8ca948db3aefbff</t>
+          <t>https://www.indeed.com/viewjob?jk=c2a1744462634cc8</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61326d67184dc890</t>
+          <t>https://www.indeed.com/viewjob?jk=49f69babc93629c9</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4f0c70aeab55966</t>
+          <t>https://www.indeed.com/viewjob?jk=d8ca948db3aefbff</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84f5e91eebbc9f06</t>
+          <t>https://www.indeed.com/viewjob?jk=61326d67184dc890</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2b8dad0cc443b9</t>
+          <t>https://www.indeed.com/viewjob?jk=c4f0c70aeab55966</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7e348dae6016f17</t>
+          <t>https://www.indeed.com/viewjob?jk=84f5e91eebbc9f06</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0cf9334f4d71f83</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2b8dad0cc443b9</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9c6c1388c411eb4</t>
+          <t>https://www.indeed.com/viewjob?jk=d7e348dae6016f17</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d19e0ea73bf12c</t>
+          <t>https://www.indeed.com/viewjob?jk=c0cf9334f4d71f83</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,32 +4661,32 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f611a382e3aa720</t>
+          <t>https://www.indeed.com/viewjob?jk=d9c6c1388c411eb4</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Platform</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Middesk</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Spark, Data Modeling, Terraform, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,32 +4696,32 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=514717df8eb087ca</t>
+          <t>https://www.indeed.com/viewjob?jk=19d19e0ea73bf12c</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Engineering Java/Python</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dfc1c1ddf5b07e8</t>
+          <t>https://www.indeed.com/viewjob?jk=8f611a382e3aa720</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Middesk</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, Spark, Data Modeling, Terraform, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab7b07d708701fa</t>
+          <t>https://www.indeed.com/viewjob?jk=514717df8eb087ca</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Software Engineer III - Data Engineering Java/Python</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, Kafka, Dimensional Modeling, ETL, Airflow</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503c92a0918e2779</t>
+          <t>https://www.indeed.com/viewjob?jk=6dfc1c1ddf5b07e8</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>API Developer Jr.</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>MKS2 Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, MySQL, MongoDB, DynamoDB, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=976d4320b891418b</t>
+          <t>https://www.indeed.com/viewjob?jk=cab7b07d708701fa</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>API Developer, Mid</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>MKS2 Technologies</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, MySQL, MongoDB, DynamoDB, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, Kafka, Dimensional Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=982682f617c5fe52</t>
+          <t>https://www.indeed.com/viewjob?jk=503c92a0918e2779</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
+          <t>Software Engineer (Backend) - Global Dining</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2698e1f59bd5def7</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f71d52efce43e2</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
+          <t>API Developer Jr.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>MKS2 Technologies</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>AWS, RDS, Scala, Oracle, MySQL, MongoDB, DynamoDB, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d0bc94cbe8822db</t>
+          <t>https://www.indeed.com/viewjob?jk=976d4320b891418b</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
+          <t>API Developer, Mid</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>MKS2 Technologies</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Paterson, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>AWS, RDS, Scala, Oracle, MySQL, MongoDB, DynamoDB, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75f6d90e6b234f60</t>
+          <t>https://www.indeed.com/viewjob?jk=982682f617c5fe52</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e53f9ddcb5f4c2b9</t>
+          <t>https://www.indeed.com/viewjob?jk=2698e1f59bd5def7</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44fb3987d11d1123</t>
+          <t>https://www.indeed.com/viewjob?jk=4d0bc94cbe8822db</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>Paterson, NJ, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d0cf03fccf9f1cb</t>
+          <t>https://www.indeed.com/viewjob?jk=75f6d90e6b234f60</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Risk Developer (Python/Azure)</t>
+          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, MLflow, CI/CD</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7762d03304071b69</t>
+          <t>https://www.indeed.com/viewjob?jk=e53f9ddcb5f4c2b9</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ca41478bb936cd</t>
+          <t>https://www.indeed.com/viewjob?jk=44fb3987d11d1123</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>hatch IT</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, ETL, CI/CD, Terraform</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b260e746e7b9c233</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf4b62fe049b84e</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE)</t>
+          <t>Senior Risk Developer (Python/Azure)</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>hatch IT</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Datadog</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c08c735142c13e1b</t>
+          <t>https://www.indeed.com/viewjob?jk=7762d03304071b69</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Dresher, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a3b73f36e3384d3</t>
+          <t>https://www.indeed.com/viewjob?jk=57ca41478bb936cd</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>.NET Angular Reporting Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>hatch IT</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, Star Schema, ETL, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,32 +5291,32 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21a948f0ac42414</t>
+          <t>https://www.indeed.com/viewjob?jk=b260e746e7b9c233</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Entry-Level Data Engineer</t>
+          <t>Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>hatch IT</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, ECS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,32 +5326,32 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd80dc2e6636141e</t>
+          <t>https://www.indeed.com/viewjob?jk=c08c735142c13e1b</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dresher, PA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,32 +5361,32 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b5cdc524b199967</t>
+          <t>https://www.indeed.com/viewjob?jk=2a3b73f36e3384d3</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer III</t>
+          <t>.NET Angular Reporting Developer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Kapitus</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, Star Schema, ETL, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31099f3a1c434171</t>
+          <t>https://www.indeed.com/viewjob?jk=f21a948f0ac42414</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Entry-Level Data Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fd50cad36943ce</t>
+          <t>https://www.indeed.com/viewjob?jk=dd80dc2e6636141e</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Senior Data Engineer(61249-1)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Vytwo Technologies</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Prosper, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, Airflow</t>
+          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5fdd13d31dd0aa1</t>
+          <t>https://www.indeed.com/viewjob?jk=8b5cdc524b199967</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer - Oracle Cloud Infrastructure (OCI)</t>
+          <t>DevSecOps Engineer III</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>APi Group, Inc.</t>
+          <t>Kapitus</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>New Brighton, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Git</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6450f77aa7cdc7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=31099f3a1c434171</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Azure Stack Data Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>AAON</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,34 +5526,34 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Data Modeling, ETL, Power BI, CI/CD, Docker</t>
+          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20dcbc83d5643838</t>
+          <t>https://www.indeed.com/viewjob?jk=29fd50cad36943ce</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>DOCSIS Testing Engineer</t>
+          <t>Senior Data Engineer(61249-1)</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vytwo Technologies</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Prosper, TX, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, NoSQL, ETL, ELT, Splunk, CI/CD, Docker</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, Airflow</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e134c7566cf151c</t>
+          <t>https://www.indeed.com/viewjob?jk=b5fdd13d31dd0aa1</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>SSO Administrator</t>
+          <t>Senior Systems Engineer - Oracle Cloud Infrastructure (OCI)</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>APi Group, Inc.</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New Brighton, MN, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b109c86f55c8c21f</t>
+          <t>https://www.indeed.com/viewjob?jk=6450f77aa7cdc7c1</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Azure Stack Data Engineer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>AAON</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,34 +5631,34 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Data Modeling, ETL, Power BI, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=843b039e4e75f61f</t>
+          <t>https://www.indeed.com/viewjob?jk=20dcbc83d5643838</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>DOCSIS Testing Engineer</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, NoSQL, ETL, ELT, Splunk, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,24 +5676,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5c91aac0db662ae</t>
+          <t>https://www.indeed.com/viewjob?jk=0e134c7566cf151c</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (FDE)</t>
+          <t>SSO Administrator</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>ISHIR</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,24 +5701,24 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ecc0cd2b5a2111</t>
+          <t>https://www.indeed.com/viewjob?jk=b109c86f55c8c21f</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5746,14 +5746,14 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ead7f0da7c5db1</t>
+          <t>https://www.indeed.com/viewjob?jk=843b039e4e75f61f</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5781,24 +5781,24 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae8a17a1c6f39e3</t>
+          <t>https://www.indeed.com/viewjob?jk=e5c91aac0db662ae</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5816,24 +5816,24 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=739e08afe4ba1176</t>
+          <t>https://www.indeed.com/viewjob?jk=c1ead7f0da7c5db1</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5851,24 +5851,24 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=151fe9868f44f2f1</t>
+          <t>https://www.indeed.com/viewjob?jk=1ae8a17a1c6f39e3</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>IT PROFESSIONAL-APPLICATIONS (Database Administrator) (HEC)</t>
+          <t>Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>City of Houston, TX</t>
+          <t>ISHIR</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,15 +5876,120 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15ecc0cd2b5a2111</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Reporting Engineer</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Surgery Partners</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=739e08afe4ba1176</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>CrowdStrike</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=151fe9868f44f2f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>IT PROFESSIONAL-APPLICATIONS (Database Administrator) (HEC)</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>City of Houston, TX</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=e1c369e1e8241c9f</t>
         </is>

--- a/results/job_matches_2026-03-04.xlsx
+++ b/results/job_matches_2026-03-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G159"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cloud Engineer- Remote US</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f25625460182eb8e</t>
+          <t>https://www.indeed.com/viewjob?jk=0997a11d6aaf4e73</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Blockchain Java Backend Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0997a11d6aaf4e73</t>
+          <t>https://www.indeed.com/viewjob?jk=e49019e3e57d794c</t>
         </is>
       </c>
     </row>
@@ -1063,25 +1063,25 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Blockchain Java Backend Engineer</t>
+          <t>Software Engineer, AI Analytics</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Residex, LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e49019e3e57d794c</t>
+          <t>https://www.indeed.com/viewjob?jk=3b994e1736909aed</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer, AI Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Residex, LLC</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b994e1736909aed</t>
+          <t>https://www.indeed.com/viewjob?jk=4cc63cdd2328277c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>ELLKAY, LLC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Elmwood Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Athena, IAM, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cc63cdd2328277c</t>
+          <t>https://www.indeed.com/viewjob?jk=28b63f4ef510667a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Cloud Software Engineer</t>
+          <t>Associate/Consultant Engineer - Remote</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ELLKAY, LLC</t>
+          <t>Rancho BioSciences</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Elmwood Park, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28b63f4ef510667a</t>
+          <t>https://www.indeed.com/viewjob?jk=72630d316687619c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Associate/Consultant Engineer - Remote</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rancho BioSciences</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72630d316687619c</t>
+          <t>https://www.indeed.com/viewjob?jk=2b12dfc8a5459a4f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b12dfc8a5459a4f</t>
+          <t>https://www.indeed.com/viewjob?jk=b08c3dc1b325be49</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b08c3dc1b325be49</t>
+          <t>https://www.indeed.com/viewjob?jk=7d49d017dead0cec</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Ncontracts</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d49d017dead0cec</t>
+          <t>https://www.indeed.com/viewjob?jk=da52963e4860aaaa</t>
         </is>
       </c>
     </row>
@@ -1413,17 +1413,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Associate/Consultant Engineer - Remote</t>
+          <t>Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Rancho BioSciences</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd467efc7d909226</t>
+          <t>https://www.indeed.com/viewjob?jk=80460d4e824e28cc</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer - Remote</t>
+          <t>Associate/Consultant Engineer - Remote</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Rancho BioSciences</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80460d4e824e28cc</t>
+          <t>https://www.indeed.com/viewjob?jk=cd467efc7d909226</t>
         </is>
       </c>
     </row>
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PDM Implementation Data Architect</t>
+          <t>Data Engineer, CDC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>DRT Strategies, Inc.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Spark, PySpark</t>
+          <t>AWS, EMR, RDS, Azure, Scala, ETL, Power BI, Tableau, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3576de9e88dd4c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=a223a368864e5d1b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cloud Identity Architect</t>
+          <t>PDM Implementation Data Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdd1e41d5949d150</t>
+          <t>https://www.indeed.com/viewjob?jk=3576de9e88dd4c5c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Java / IBM ACE Developer</t>
+          <t>Cloud Identity Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,24 +1746,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, Azure DevOps</t>
+          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70a91ea32c4e2e98</t>
+          <t>https://www.indeed.com/viewjob?jk=fdd1e41d5949d150</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Java / IBM ACE Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd0439895496e24</t>
+          <t>https://www.indeed.com/viewjob?jk=70a91ea32c4e2e98</t>
         </is>
       </c>
     </row>
@@ -2778,17 +2778,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AI Solution Architect</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Velvetech</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, MLOps, CI/CD</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6435ac5193c56de</t>
+          <t>https://www.indeed.com/viewjob?jk=b7dfde3b442bd5c7</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Clarksville, TN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7dfde3b442bd5c7</t>
+          <t>https://www.indeed.com/viewjob?jk=503ceed67966f48a</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>DatamanUSA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Clarksville, TN, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, PostgreSQL, Dimensional Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503ceed67966f48a</t>
+          <t>https://www.indeed.com/viewjob?jk=9672d81f2806d2a2</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Cloud Identity Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>DatamanUSA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, PostgreSQL, Dimensional Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, Google Cloud Platform, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9672d81f2806d2a2</t>
+          <t>https://www.indeed.com/viewjob?jk=5b1a799d8b14436a</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Cloud Identity Architect</t>
+          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ABCorp NA Inc.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, Google Cloud Platform, Vertex AI, Scala</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b1a799d8b14436a</t>
+          <t>https://www.indeed.com/viewjob?jk=5d8f6d93b707b783</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
+          <t>Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ABCorp NA Inc.</t>
+          <t>Middesk</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, RDS, Azure, Spark, Data Modeling, Terraform, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d8f6d93b707b783</t>
+          <t>https://www.indeed.com/viewjob?jk=514717df8eb087ca</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Engineer III - Data Engineering Java/Python</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6006f51c65e9f139</t>
+          <t>https://www.indeed.com/viewjob?jk=6dfc1c1ddf5b07e8</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=205804a055fd2049</t>
+          <t>https://www.indeed.com/viewjob?jk=cab7b07d708701fa</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, Kafka, Dimensional Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,67 +3086,67 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5c5706918e358a0</t>
+          <t>https://www.indeed.com/viewjob?jk=503c92a0918e2779</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Engineer (Backend) - Global Dining</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10a398f9aeeb6c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f71d52efce43e2</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>API Developer Jr.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>MKS2 Technologies</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, Oracle, MySQL, MongoDB, DynamoDB, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8977f5b4ab10d23</t>
+          <t>https://www.indeed.com/viewjob?jk=976d4320b891418b</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>API Developer, Mid</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>MKS2 Technologies</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, Oracle, MySQL, MongoDB, DynamoDB, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93b71ab143505ef</t>
+          <t>https://www.indeed.com/viewjob?jk=982682f617c5fe52</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=640d49c55b368f21</t>
+          <t>https://www.indeed.com/viewjob?jk=2698e1f59bd5def7</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d37ce07d5d4393f3</t>
+          <t>https://www.indeed.com/viewjob?jk=4d0bc94cbe8822db</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>Paterson, NJ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10aa5fc172c0cf9</t>
+          <t>https://www.indeed.com/viewjob?jk=75f6d90e6b234f60</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58a1d20202a2aef8</t>
+          <t>https://www.indeed.com/viewjob?jk=e53f9ddcb5f4c2b9</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8185d403faf25e2</t>
+          <t>https://www.indeed.com/viewjob?jk=44fb3987d11d1123</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a014ab60dbd75f0</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf4b62fe049b84e</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Risk Developer (Python/Azure)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f103c6f8f1eabe61</t>
+          <t>https://www.indeed.com/viewjob?jk=7762d03304071b69</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>hatch IT</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae886d34419a9a7</t>
+          <t>https://www.indeed.com/viewjob?jk=b260e746e7b9c233</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>hatch IT</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, ECS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cfd83638c49b733</t>
+          <t>https://www.indeed.com/viewjob?jk=c08c735142c13e1b</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Dresher, PA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=592db9bfc62c64e2</t>
+          <t>https://www.indeed.com/viewjob?jk=2a3b73f36e3384d3</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83814a502692afe0</t>
+          <t>https://www.indeed.com/viewjob?jk=57ca41478bb936cd</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>.NET Angular Reporting Developer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, Star Schema, ETL, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a7005ca8416f01f</t>
+          <t>https://www.indeed.com/viewjob?jk=f21a948f0ac42414</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Entry-Level Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=616e989c777fcd64</t>
+          <t>https://www.indeed.com/viewjob?jk=dd80dc2e6636141e</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a46aa375a4da0e2</t>
+          <t>https://www.indeed.com/viewjob?jk=8b5cdc524b199967</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>DevSecOps Engineer III</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Kapitus</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6904e697ef07baaf</t>
+          <t>https://www.indeed.com/viewjob?jk=31099f3a1c434171</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dc64b2070c5c6f8</t>
+          <t>https://www.indeed.com/viewjob?jk=29fd50cad36943ce</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Engineer(61249-1)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Vytwo Technologies</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Prosper, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, Airflow</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ee7574e666ce713</t>
+          <t>https://www.indeed.com/viewjob?jk=b5fdd13d31dd0aa1</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Systems Engineer - Oracle Cloud Infrastructure (OCI)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>APi Group, Inc.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>New Brighton, MN, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,67 +3821,67 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99bc4057502816b</t>
+          <t>https://www.indeed.com/viewjob?jk=6450f77aa7cdc7c1</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Azure Stack Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>AAON</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Data Modeling, ETL, Power BI, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8810eb13c55de856</t>
+          <t>https://www.indeed.com/viewjob?jk=20dcbc83d5643838</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>DOCSIS Testing Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, NoSQL, ETL, ELT, Splunk, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7372945ed1cbee22</t>
+          <t>https://www.indeed.com/viewjob?jk=0e134c7566cf151c</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>SSO Administrator</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06b4f714255d00b</t>
+          <t>https://www.indeed.com/viewjob?jk=b109c86f55c8c21f</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c81cd4c9bce9e715</t>
+          <t>https://www.indeed.com/viewjob?jk=843b039e4e75f61f</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,67 +3996,67 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cec639e703e1f70</t>
+          <t>https://www.indeed.com/viewjob?jk=e5c91aac0db662ae</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>ISHIR</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7628f7ec7ab09a9</t>
+          <t>https://www.indeed.com/viewjob?jk=15ecc0cd2b5a2111</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d764f5358afc422f</t>
+          <t>https://www.indeed.com/viewjob?jk=c1ead7f0da7c5db1</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95628c711a619430</t>
+          <t>https://www.indeed.com/viewjob?jk=1ae8a17a1c6f39e3</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4e67862f3b9941</t>
+          <t>https://www.indeed.com/viewjob?jk=151fe9868f44f2f1</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2963649fc0f492cf</t>
+          <t>https://www.indeed.com/viewjob?jk=739e08afe4ba1176</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>IT PROFESSIONAL-APPLICATIONS (Database Administrator) (HEC)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>City of Houston, TX</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4205,1791 +4205,6 @@
         </is>
       </c>
       <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=745b60449ed066d9</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>SD, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8c80024050212c2d</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>ND, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4b032019de44f8fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>MN, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9a0ff3586081cca1</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>SC, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c2a1744462634cc8</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=49f69babc93629c9</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>OH, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d8ca948db3aefbff</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=61326d67184dc890</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>WA, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c4f0c70aeab55966</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>WY, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=84f5e91eebbc9f06</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>NM, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2b8dad0cc443b9</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d7e348dae6016f17</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c0cf9334f4d71f83</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>TN, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d9c6c1388c411eb4</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>IL, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=19d19e0ea73bf12c</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>NE, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8f611a382e3aa720</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Software Engineer, Data Platform</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Middesk</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, RDS, Azure, Spark, Data Modeling, Terraform, Kubernetes, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=514717df8eb087ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Software Engineer III - Data Engineering Java/Python</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6dfc1c1ddf5b07e8</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Multi-Cloud Networking Engineer</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cab7b07d708701fa</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>GCP Data Engineer</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Infosys</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Richardson, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, Kafka, Dimensional Modeling, ETL, Airflow</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=503c92a0918e2779</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Software Engineer (Backend) - Global Dining</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>American Express</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f71d52efce43e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>API Developer Jr.</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>MKS2 Technologies</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, MySQL, MongoDB, DynamoDB, GitHub Actions, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=976d4320b891418b</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>API Developer, Mid</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>MKS2 Technologies</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, MySQL, MongoDB, DynamoDB, GitHub Actions, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=982682f617c5fe52</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>NavitasPartners</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2698e1f59bd5def7</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>NavitasPartners</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Long Island City, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4d0bc94cbe8822db</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>NavitasPartners</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Paterson, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=75f6d90e6b234f60</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>NavitasPartners</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Yonkers, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e53f9ddcb5f4c2b9</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>NavitasPartners</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=44fb3987d11d1123</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Skechers</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Hermosa Beach, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf4b62fe049b84e</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Senior Risk Developer (Python/Azure)</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Sumitomo Group</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7762d03304071b69</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Reporting Engineer</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Surgery Partners</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=57ca41478bb936cd</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>hatch IT</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, ETL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b260e746e7b9c233</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer (SRE)</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>hatch IT</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AWS, ECS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Datadog</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c08c735142c13e1b</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Ascensus</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Dresher, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2a3b73f36e3384d3</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>.NET Angular Reporting Developer</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, Star Schema, ETL, Power BI, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f21a948f0ac42414</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Entry-Level Data Engineer</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Warren, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dd80dc2e6636141e</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Lyric</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8b5cdc524b199967</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>DevSecOps Engineer III</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Kapitus</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, AWS CodePipeline</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=31099f3a1c434171</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Azure Network Engineer</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=29fd50cad36943ce</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer(61249-1)</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Vytwo Technologies</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Prosper, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, Airflow</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b5fdd13d31dd0aa1</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Senior Systems Engineer - Oracle Cloud Infrastructure (OCI)</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>APi Group, Inc.</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>New Brighton, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Git</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6450f77aa7cdc7c1</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Azure Stack Data Engineer</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>AAON</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Tulsa, OK, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Data Modeling, ETL, Power BI, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-01-13</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=20dcbc83d5643838</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>DOCSIS Testing Engineer</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, NoSQL, ETL, ELT, Splunk, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0e134c7566cf151c</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>SSO Administrator</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b109c86f55c8c21f</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Senior Engineer - .NET</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=843b039e4e75f61f</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Senior Engineer - .NET</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e5c91aac0db662ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ead7f0da7c5db1</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae8a17a1c6f39e3</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Forward Deployed Engineer (FDE)</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>ISHIR</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=15ecc0cd2b5a2111</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Reporting Engineer</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Surgery Partners</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=739e08afe4ba1176</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>CrowdStrike</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=151fe9868f44f2f1</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>IT PROFESSIONAL-APPLICATIONS (Database Administrator) (HEC)</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>City of Houston, TX</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=e1c369e1e8241c9f</t>
         </is>

--- a/results/job_matches_2026-03-04.xlsx
+++ b/results/job_matches_2026-03-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1063,17 +1063,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer, AI Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Residex, LLC</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b994e1736909aed</t>
+          <t>https://www.indeed.com/viewjob?jk=4cc63cdd2328277c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer, AI Analytics</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Residex, LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cc63cdd2328277c</t>
+          <t>https://www.indeed.com/viewjob?jk=3b994e1736909aed</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Data Engineer + Snowflake (On-Site)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ROLLER</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Glue, EMR, RDS, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb709659d664135</t>
+          <t>https://www.indeed.com/viewjob?jk=58e9f31119d31013</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer + Snowflake (On-Site)</t>
+          <t>PDM Implementation Data Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e9f31119d31013</t>
+          <t>https://www.indeed.com/viewjob?jk=3576de9e88dd4c5c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Google Cloud Network Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c97eb9417ef8ebcf</t>
+          <t>https://www.indeed.com/viewjob?jk=a53eba2ddb1389c4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a53eba2ddb1389c4</t>
+          <t>https://www.indeed.com/viewjob?jk=39a6c4ab9efc012e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>ROLLER</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a6c4ab9efc012e</t>
+          <t>https://www.indeed.com/viewjob?jk=afb709659d664135</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer, CDC</t>
+          <t>Google Cloud Network Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DRT Strategies, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Scala, ETL, Power BI, Tableau, CI/CD, Docker</t>
+          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a223a368864e5d1b</t>
+          <t>https://www.indeed.com/viewjob?jk=c97eb9417ef8ebcf</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PDM Implementation Data Architect</t>
+          <t>Data Engineer, CDC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>DRT Strategies, Inc.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,17 +1711,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Spark, PySpark</t>
+          <t>AWS, EMR, RDS, Azure, Scala, ETL, Power BI, Tableau, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3576de9e88dd4c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=a223a368864e5d1b</t>
         </is>
       </c>
     </row>
@@ -1938,17 +1938,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-2</t>
+          <t>ETL Testing with Azure Databricks in Healthcare</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f9103ddd4f544e</t>
+          <t>https://www.indeed.com/viewjob?jk=9af37a4075a8760f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d602908669423e</t>
+          <t>https://www.indeed.com/viewjob?jk=662840de4364e997</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>Software Engineer II - Scala</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10de5f0ca2f7673d</t>
+          <t>https://www.indeed.com/viewjob?jk=d148fa8c6ae39fd8</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>Data Platform Engineer-2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6750fd9ad4e72e</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f9103ddd4f544e</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45db6ac50eb5587</t>
+          <t>https://www.indeed.com/viewjob?jk=75d602908669423e</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1c0f7e27e90a87e</t>
+          <t>https://www.indeed.com/viewjob?jk=10de5f0ca2f7673d</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4dc81e5cd9b6b72</t>
+          <t>https://www.indeed.com/viewjob?jk=8e6750fd9ad4e72e</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14fea47c1dbfabac</t>
+          <t>https://www.indeed.com/viewjob?jk=c45db6ac50eb5587</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02d7bcc2bd0697b0</t>
+          <t>https://www.indeed.com/viewjob?jk=d1c0f7e27e90a87e</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50e0ff85e5f89851</t>
+          <t>https://www.indeed.com/viewjob?jk=a4dc81e5cd9b6b72</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=662840de4364e997</t>
+          <t>https://www.indeed.com/viewjob?jk=14fea47c1dbfabac</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer II - Scala</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d148fa8c6ae39fd8</t>
+          <t>https://www.indeed.com/viewjob?jk=02d7bcc2bd0697b0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ETL Testing with Azure Databricks in Healthcare</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Scala, Oracle</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9af37a4075a8760f</t>
+          <t>https://www.indeed.com/viewjob?jk=50e0ff85e5f89851</t>
         </is>
       </c>
     </row>
@@ -2568,17 +2568,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Network IoT Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Santa Barbara, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52fbd92226aade92</t>
+          <t>https://www.indeed.com/viewjob?jk=0da29d3af250447a</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e77317858ff838d</t>
+          <t>https://www.indeed.com/viewjob?jk=7fc978b16714d0d2</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9737f288d965528f</t>
+          <t>https://www.indeed.com/viewjob?jk=9649d08cb62a9ac0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PEARLY</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Santa Barbara, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT, MLflow</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fc978b16714d0d2</t>
+          <t>https://www.indeed.com/viewjob?jk=52fbd92226aade92</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>PEARLY</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9649d08cb62a9ac0</t>
+          <t>https://www.indeed.com/viewjob?jk=3e77317858ff838d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Network IoT Engineer</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PEARLY</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da29d3af250447a</t>
+          <t>https://www.indeed.com/viewjob?jk=9737f288d965528f</t>
         </is>
       </c>
     </row>
@@ -2953,17 +2953,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Platform</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Middesk</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Spark, Data Modeling, Terraform, Kubernetes, Airflow, Git</t>
+          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, Kafka, Dimensional Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=514717df8eb087ca</t>
+          <t>https://www.indeed.com/viewjob?jk=503c92a0918e2779</t>
         </is>
       </c>
     </row>
@@ -3058,17 +3058,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Software Engineer (Backend) - Global Dining</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, Kafka, Dimensional Modeling, ETL, Airflow</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503c92a0918e2779</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f71d52efce43e2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend) - Global Dining</t>
+          <t>Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Middesk</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, RDS, Azure, Spark, Data Modeling, Terraform, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f71d52efce43e2</t>
+          <t>https://www.indeed.com/viewjob?jk=514717df8eb087ca</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>API Developer Jr.</t>
+          <t>Senior Database Reliability Engineer (Oracle &amp; Automation Focus)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>MKS2 Technologies</t>
+          <t>BILL</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,24 +3146,24 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, MySQL, MongoDB, DynamoDB, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Oracle, DynamoDB, NoSQL, Splunk, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=976d4320b891418b</t>
+          <t>https://www.indeed.com/viewjob?jk=104eb630cab2bc86</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>API Developer, Mid</t>
+          <t>API Developer Jr.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=982682f617c5fe52</t>
+          <t>https://www.indeed.com/viewjob?jk=976d4320b891418b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
+          <t>API Developer, Mid</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>MKS2 Technologies</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>AWS, RDS, Scala, Oracle, MySQL, MongoDB, DynamoDB, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2698e1f59bd5def7</t>
+          <t>https://www.indeed.com/viewjob?jk=982682f617c5fe52</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d0bc94cbe8822db</t>
+          <t>https://www.indeed.com/viewjob?jk=2698e1f59bd5def7</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Paterson, NJ, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75f6d90e6b234f60</t>
+          <t>https://www.indeed.com/viewjob?jk=4d0bc94cbe8822db</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>Paterson, NJ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e53f9ddcb5f4c2b9</t>
+          <t>https://www.indeed.com/viewjob?jk=75f6d90e6b234f60</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44fb3987d11d1123</t>
+          <t>https://www.indeed.com/viewjob?jk=e53f9ddcb5f4c2b9</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf4b62fe049b84e</t>
+          <t>https://www.indeed.com/viewjob?jk=44fb3987d11d1123</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Risk Developer (Python/Azure)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, MLflow, CI/CD</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7762d03304071b69</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf4b62fe049b84e</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Risk Developer (Python/Azure)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>hatch IT</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, ETL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,14 +3471,14 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b260e746e7b9c233</t>
+          <t>https://www.indeed.com/viewjob?jk=7762d03304071b69</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Datadog</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c08c735142c13e1b</t>
+          <t>https://www.indeed.com/viewjob?jk=b260e746e7b9c233</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>hatch IT</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Dresher, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, ECS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a3b73f36e3384d3</t>
+          <t>https://www.indeed.com/viewjob?jk=c08c735142c13e1b</t>
         </is>
       </c>
     </row>
@@ -3618,17 +3618,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Entry-Level Data Engineer</t>
+          <t>Senior Data Engineer(61249-1)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Vytwo Technologies</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Prosper, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, Airflow</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd80dc2e6636141e</t>
+          <t>https://www.indeed.com/viewjob?jk=b5fdd13d31dd0aa1</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Entry-Level Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b5cdc524b199967</t>
+          <t>https://www.indeed.com/viewjob?jk=dd80dc2e6636141e</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Kapitus</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31099f3a1c434171</t>
+          <t>https://www.indeed.com/viewjob?jk=8b5cdc524b199967</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>DevSecOps Engineer III</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Kapitus</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fd50cad36943ce</t>
+          <t>https://www.indeed.com/viewjob?jk=31099f3a1c434171</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Data Engineer(61249-1)</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Vytwo Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Prosper, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, Airflow</t>
+          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5fdd13d31dd0aa1</t>
+          <t>https://www.indeed.com/viewjob?jk=29fd50cad36943ce</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer - Oracle Cloud Infrastructure (OCI)</t>
+          <t>Azure Stack Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>APi Group, Inc.</t>
+          <t>AAON</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>New Brighton, MN, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Git</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Data Modeling, ETL, Power BI, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6450f77aa7cdc7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=20dcbc83d5643838</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Azure Stack Data Engineer</t>
+          <t>DOCSIS Testing Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>AAON</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,24 +3846,24 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Data Modeling, ETL, Power BI, CI/CD, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, NoSQL, ETL, ELT, Splunk, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20dcbc83d5643838</t>
+          <t>https://www.indeed.com/viewjob?jk=0e134c7566cf151c</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>DOCSIS Testing Engineer</t>
+          <t>SSO Administrator</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, NoSQL, ETL, ELT, Splunk, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e134c7566cf151c</t>
+          <t>https://www.indeed.com/viewjob?jk=b109c86f55c8c21f</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SSO Administrator</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,14 +3926,14 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b109c86f55c8c21f</t>
+          <t>https://www.indeed.com/viewjob?jk=843b039e4e75f61f</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,14 +3961,14 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=843b039e4e75f61f</t>
+          <t>https://www.indeed.com/viewjob?jk=c1ead7f0da7c5db1</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5c91aac0db662ae</t>
+          <t>https://www.indeed.com/viewjob?jk=1ae8a17a1c6f39e3</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (FDE)</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ISHIR</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ecc0cd2b5a2111</t>
+          <t>https://www.indeed.com/viewjob?jk=e5c91aac0db662ae</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>ISHIR</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ead7f0da7c5db1</t>
+          <t>https://www.indeed.com/viewjob?jk=15ecc0cd2b5a2111</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae8a17a1c6f39e3</t>
+          <t>https://www.indeed.com/viewjob?jk=151fe9868f44f2f1</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=151fe9868f44f2f1</t>
+          <t>https://www.indeed.com/viewjob?jk=739e08afe4ba1176</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>IT PROFESSIONAL-APPLICATIONS (Database Administrator) (HEC)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>City of Houston, TX</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4170,41 +4170,6 @@
         </is>
       </c>
       <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=739e08afe4ba1176</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>IT PROFESSIONAL-APPLICATIONS (Database Administrator) (HEC)</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>City of Houston, TX</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=e1c369e1e8241c9f</t>
         </is>

--- a/results/job_matches_2026-03-04.xlsx
+++ b/results/job_matches_2026-03-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (React + Node.js)-4</t>
+          <t>Data Engineer/Python Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Zifo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e082e26fc29250a3</t>
+          <t>https://www.indeed.com/viewjob?jk=3419a1d7b4acb559</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer/Python Developer</t>
+          <t>Full Stack Engineer (React + Node.js)-4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Zifo</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3419a1d7b4acb559</t>
+          <t>https://www.indeed.com/viewjob?jk=e082e26fc29250a3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Network IoT Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Quilt</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, API Gateway, IAM</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4725509304854f9e</t>
+          <t>https://www.indeed.com/viewjob?jk=27d883fd388e687a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - AI Practice Team</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Quilt</t>
+          <t>American Bureau of Shipping (ABS)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Azure, Data Factory, Databricks, Event Hubs, BigQuery</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,19 +741,19 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d883fd388e687a</t>
+          <t>https://www.indeed.com/viewjob?jk=98e9bc7cd1938bfd</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer - AI Practice Team</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>American Bureau of Shipping (ABS)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -762,11 +762,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Azure, Data Factory, Databricks, Event Hubs, BigQuery</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98e9bc7cd1938bfd</t>
+          <t>https://www.indeed.com/viewjob?jk=7167050c109be2d4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6c4839e7fe64d8e</t>
+          <t>https://www.indeed.com/viewjob?jk=862a4a8989448fa0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Infrastructure</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ALTRUIST</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc6ad57eba624292</t>
+          <t>https://www.indeed.com/viewjob?jk=07e542bb4713fad0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Infrastructure</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ALTRUIST</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,19 +881,19 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15325ad687b27337</t>
+          <t>https://www.indeed.com/viewjob?jk=2c88dff775194e30</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -902,11 +902,11 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17c87f0de0ddb952</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ced45fe117deb8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Backend Software Engineer III - API Platform</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, API Gateway, RDS, Databricks, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd1c3ba542522bad</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc8e0c810b3e7cd</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0997a11d6aaf4e73</t>
+          <t>https://www.indeed.com/viewjob?jk=7791942c877daada</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Blockchain Java Backend Engineer</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e49019e3e57d794c</t>
+          <t>https://www.indeed.com/viewjob?jk=b6b39b9b56abc0bd</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer II,</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4edb591674d441f</t>
+          <t>https://www.indeed.com/viewjob?jk=648774ee33ca3b76</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cc63cdd2328277c</t>
+          <t>https://www.indeed.com/viewjob?jk=a93ca1ad887e17f0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer, AI Analytics</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Residex, LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b994e1736909aed</t>
+          <t>https://www.indeed.com/viewjob?jk=d963e90dfb3fa4d6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Cloud Software Engineer</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ELLKAY, LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Elmwood Park, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28b63f4ef510667a</t>
+          <t>https://www.indeed.com/viewjob?jk=783ac47e6d62e414</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Associate/Consultant Engineer - Remote</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rancho BioSciences</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72630d316687619c</t>
+          <t>https://www.indeed.com/viewjob?jk=e511c7108cd6e82d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>17.4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b12dfc8a5459a4f</t>
+          <t>https://www.indeed.com/viewjob?jk=2a6a2ad30fc1236d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>17.4</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b08c3dc1b325be49</t>
+          <t>https://www.indeed.com/viewjob?jk=e2d42f6d55a07b48</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>17.4</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d49d017dead0cec</t>
+          <t>https://www.indeed.com/viewjob?jk=c423f392a018bf22</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ncontracts</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>17.4</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da52963e4860aaaa</t>
+          <t>https://www.indeed.com/viewjob?jk=cb49af32ea451f63</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer - Kafka Connect</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CloudRay Inc</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>17.4</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5df3111682f7946</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7468c4fe6bdb23</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Cloud Architect - SI Partners</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>17.4</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Azure, Data Factory, GCP, Spark, Scala, Snowflake, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba51b24a2f032664</t>
+          <t>https://www.indeed.com/viewjob?jk=3a3485c3c6153843</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer - Remote</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>17.4</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80460d4e824e28cc</t>
+          <t>https://www.indeed.com/viewjob?jk=ef4166ba4aa9b5a3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Associate/Consultant Engineer - Remote</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Rancho BioSciences</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>17.4</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd467efc7d909226</t>
+          <t>https://www.indeed.com/viewjob?jk=91d6e4beb774dd25</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer + Snowflake (On-Site)</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>17.4</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e9f31119d31013</t>
+          <t>https://www.indeed.com/viewjob?jk=adcf2824745a050e</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PDM Implementation Data Architect</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>17.4</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3576de9e88dd4c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=64b296145590b995</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>17.4</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a53eba2ddb1389c4</t>
+          <t>https://www.indeed.com/viewjob?jk=8c4169879098b22b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>17.4</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,67 +1616,67 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a6c4ab9efc012e</t>
+          <t>https://www.indeed.com/viewjob?jk=44e1222f0eb14744</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ROLLER</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>17.4</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb709659d664135</t>
+          <t>https://www.indeed.com/viewjob?jk=37bd1a8719f0aafc</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Google Cloud Network Engineer</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>17.4</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c97eb9417ef8ebcf</t>
+          <t>https://www.indeed.com/viewjob?jk=e151b2c0a32e2723</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer, CDC</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DRT Strategies, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>17.4</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Scala, ETL, Power BI, Tableau, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a223a368864e5d1b</t>
+          <t>https://www.indeed.com/viewjob?jk=c07dcca1b609463e</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cloud Identity Architect</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>17.4</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,102 +1756,102 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdd1e41d5949d150</t>
+          <t>https://www.indeed.com/viewjob?jk=c721bd4ca7bdffe1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Java / IBM ACE Developer</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>17.4</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70a91ea32c4e2e98</t>
+          <t>https://www.indeed.com/viewjob?jk=e8e182c6058fd2a4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ivo</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>17.4</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bc5aaef611937ad</t>
+          <t>https://www.indeed.com/viewjob?jk=4997f8f92f05b9d2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ai Vantage</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>17.4</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87747bfcd30cdbc2</t>
+          <t>https://www.indeed.com/viewjob?jk=2a56481df82d7aa6</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>System Integration Test Engineer</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BGIT India Private Limited</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hudson, NH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>17.4</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=426d1d0d6a93918c</t>
+          <t>https://www.indeed.com/viewjob?jk=fb00c80fb9cb9b65</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>17.4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7c80e2086f0d108</t>
+          <t>https://www.indeed.com/viewjob?jk=3fd1863254c88e5d</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ETL Testing with Azure Databricks in Healthcare</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>17.4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Scala, Oracle</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9af37a4075a8760f</t>
+          <t>https://www.indeed.com/viewjob?jk=a6c4839e7fe64d8e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Senior Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ALTRUIST</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>17.4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=662840de4364e997</t>
+          <t>https://www.indeed.com/viewjob?jk=cc6ad57eba624292</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer II - Scala</t>
+          <t>Senior Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ALTRUIST</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>17.4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,67 +2036,67 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d148fa8c6ae39fd8</t>
+          <t>https://www.indeed.com/viewjob?jk=15325ad687b27337</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-2</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>16.7</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f9103ddd4f544e</t>
+          <t>https://www.indeed.com/viewjob?jk=17c87f0de0ddb952</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>Backend Software Engineer III - API Platform</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>16.7</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, API Gateway, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,67 +2106,67 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d602908669423e</t>
+          <t>https://www.indeed.com/viewjob?jk=fd1c3ba542522bad</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>Software Engineer II,</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, ECS, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10de5f0ca2f7673d</t>
+          <t>https://www.indeed.com/viewjob?jk=b4edb591674d441f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>Blockchain Java Backend Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6750fd9ad4e72e</t>
+          <t>https://www.indeed.com/viewjob?jk=e49019e3e57d794c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45db6ac50eb5587</t>
+          <t>https://www.indeed.com/viewjob?jk=0997a11d6aaf4e73</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>15.3</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1c0f7e27e90a87e</t>
+          <t>https://www.indeed.com/viewjob?jk=4cc63cdd2328277c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>Software Engineer, AI Analytics</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Residex, LLC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>15.3</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4dc81e5cd9b6b72</t>
+          <t>https://www.indeed.com/viewjob?jk=3b994e1736909aed</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>Sr. Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>ELLKAY, LLC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Elmwood Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>15.3</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Athena, IAM, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14fea47c1dbfabac</t>
+          <t>https://www.indeed.com/viewjob?jk=28b63f4ef510667a</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>Associate/Consultant Engineer - Remote</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Rancho BioSciences</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>15.3</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02d7bcc2bd0697b0</t>
+          <t>https://www.indeed.com/viewjob?jk=72630d316687619c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,67 +2386,67 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50e0ff85e5f89851</t>
+          <t>https://www.indeed.com/viewjob?jk=2b12dfc8a5459a4f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Risk Data AI/ML Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=979402388d34b409</t>
+          <t>https://www.indeed.com/viewjob?jk=7d49d017dead0cec</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Databricks AI Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Powerplan</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5753d39b44c782</t>
+          <t>https://www.indeed.com/viewjob?jk=b08c3dc1b325be49</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ELLKAY, LLC</t>
+          <t>Ncontracts</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Elmwood Park, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Streams/Tasks</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7bfd917914d4728</t>
+          <t>https://www.indeed.com/viewjob?jk=da52963e4860aaaa</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer</t>
+          <t>Data Engineer - Kafka Connect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CloudRay Inc</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, S3, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9886d247b0ec7a02</t>
+          <t>https://www.indeed.com/viewjob?jk=d5df3111682f7946</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Platform-DevOps Engineer</t>
+          <t>Associate/Consultant Engineer - Remote</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NXLog</t>
+          <t>Rancho BioSciences</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e7328772f0c8abe</t>
+          <t>https://www.indeed.com/viewjob?jk=cd467efc7d909226</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Network IoT Engineer</t>
+          <t>Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da29d3af250447a</t>
+          <t>https://www.indeed.com/viewjob?jk=80460d4e824e28cc</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Cloud Data Engineer + Snowflake (On-Site)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT, MLflow</t>
+          <t>AWS, Glue, EMR, RDS, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fc978b16714d0d2</t>
+          <t>https://www.indeed.com/viewjob?jk=58e9f31119d31013</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>PDM Implementation Data Architect</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9649d08cb62a9ac0</t>
+          <t>https://www.indeed.com/viewjob?jk=3576de9e88dd4c5c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Santa Barbara, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52fbd92226aade92</t>
+          <t>https://www.indeed.com/viewjob?jk=a53eba2ddb1389c4</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,67 +2736,67 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e77317858ff838d</t>
+          <t>https://www.indeed.com/viewjob?jk=39a6c4ab9efc012e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>ROLLER</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9737f288d965528f</t>
+          <t>https://www.indeed.com/viewjob?jk=afb709659d664135</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Google Cloud Network Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,67 +2806,67 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7dfde3b442bd5c7</t>
+          <t>https://www.indeed.com/viewjob?jk=c97eb9417ef8ebcf</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Data Engineer, CDC</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>DRT Strategies, Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Clarksville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, EMR, RDS, Azure, Scala, ETL, Power BI, Tableau, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503ceed67966f48a</t>
+          <t>https://www.indeed.com/viewjob?jk=a223a368864e5d1b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Cloud Identity Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>DatamanUSA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, PostgreSQL, Dimensional Modeling, Star Schema, Snowflake Schema</t>
+          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,67 +2876,67 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9672d81f2806d2a2</t>
+          <t>https://www.indeed.com/viewjob?jk=fdd1e41d5949d150</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cloud Identity Architect</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ivo</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, Google Cloud Platform, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b1a799d8b14436a</t>
+          <t>https://www.indeed.com/viewjob?jk=8bc5aaef611937ad</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ABCorp NA Inc.</t>
+          <t>Ai Vantage</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d8f6d93b707b783</t>
+          <t>https://www.indeed.com/viewjob?jk=87747bfcd30cdbc2</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>System Integration Test Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>BGIT India Private Limited</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Hudson, NH, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, Kafka, Dimensional Modeling, ETL, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503c92a0918e2779</t>
+          <t>https://www.indeed.com/viewjob?jk=426d1d0d6a93918c</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Engineering Java/Python</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
+          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dfc1c1ddf5b07e8</t>
+          <t>https://www.indeed.com/viewjob?jk=a7c80e2086f0d108</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>ETL Testing with Azure Databricks in Healthcare</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,67 +3051,67 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab7b07d708701fa</t>
+          <t>https://www.indeed.com/viewjob?jk=9af37a4075a8760f</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend) - Global Dining</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f71d52efce43e2</t>
+          <t>https://www.indeed.com/viewjob?jk=662840de4364e997</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Platform</t>
+          <t>Software Engineer II - Scala</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Middesk</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Spark, Data Modeling, Terraform, Kubernetes, Airflow, Git</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=514717df8eb087ca</t>
+          <t>https://www.indeed.com/viewjob?jk=d148fa8c6ae39fd8</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Database Reliability Engineer (Oracle &amp; Automation Focus)</t>
+          <t>Data Platform Engineer-2</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BILL</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Oracle, DynamoDB, NoSQL, Splunk, CI/CD, Terraform, Git</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=104eb630cab2bc86</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f9103ddd4f544e</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>API Developer Jr.</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>MKS2 Technologies</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, MySQL, MongoDB, DynamoDB, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=976d4320b891418b</t>
+          <t>https://www.indeed.com/viewjob?jk=75d602908669423e</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>API Developer, Mid</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>MKS2 Technologies</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, MySQL, MongoDB, DynamoDB, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=982682f617c5fe52</t>
+          <t>https://www.indeed.com/viewjob?jk=10de5f0ca2f7673d</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2698e1f59bd5def7</t>
+          <t>https://www.indeed.com/viewjob?jk=8e6750fd9ad4e72e</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d0bc94cbe8822db</t>
+          <t>https://www.indeed.com/viewjob?jk=c45db6ac50eb5587</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Paterson, NJ, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75f6d90e6b234f60</t>
+          <t>https://www.indeed.com/viewjob?jk=d1c0f7e27e90a87e</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e53f9ddcb5f4c2b9</t>
+          <t>https://www.indeed.com/viewjob?jk=a4dc81e5cd9b6b72</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44fb3987d11d1123</t>
+          <t>https://www.indeed.com/viewjob?jk=14fea47c1dbfabac</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf4b62fe049b84e</t>
+          <t>https://www.indeed.com/viewjob?jk=02d7bcc2bd0697b0</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Risk Developer (Python/Azure)</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,67 +3471,67 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7762d03304071b69</t>
+          <t>https://www.indeed.com/viewjob?jk=50e0ff85e5f89851</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Risk Data AI/ML Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>hatch IT</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, ETL, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b260e746e7b9c233</t>
+          <t>https://www.indeed.com/viewjob?jk=979402388d34b409</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE)</t>
+          <t>Senior Databricks AI Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>hatch IT</t>
+          <t>Powerplan</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c08c735142c13e1b</t>
+          <t>https://www.indeed.com/viewjob?jk=3b5753d39b44c782</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>ELLKAY, LLC</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Elmwood Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>AWS, EMR, S3, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Streams/Tasks</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ca41478bb936cd</t>
+          <t>https://www.indeed.com/viewjob?jk=c7bfd917914d4728</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>.NET Angular Reporting Developer</t>
+          <t>Sr DevOPS Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, Star Schema, ETL, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21a948f0ac42414</t>
+          <t>https://www.indeed.com/viewjob?jk=9886d247b0ec7a02</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Engineer(61249-1)</t>
+          <t>Platform-DevOps Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Vytwo Technologies</t>
+          <t>NXLog</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Prosper, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, Airflow</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5fdd13d31dd0aa1</t>
+          <t>https://www.indeed.com/viewjob?jk=6e7328772f0c8abe</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Entry-Level Data Engineer</t>
+          <t>Network IoT Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd80dc2e6636141e</t>
+          <t>https://www.indeed.com/viewjob?jk=0da29d3af250447a</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b5cdc524b199967</t>
+          <t>https://www.indeed.com/viewjob?jk=7fc978b16714d0d2</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Kapitus</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31099f3a1c434171</t>
+          <t>https://www.indeed.com/viewjob?jk=9649d08cb62a9ac0</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PEARLY</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Santa Barbara, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,67 +3786,67 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fd50cad36943ce</t>
+          <t>https://www.indeed.com/viewjob?jk=52fbd92226aade92</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Azure Stack Data Engineer</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>AAON</t>
+          <t>PEARLY</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Data Modeling, ETL, Power BI, CI/CD, Docker</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20dcbc83d5643838</t>
+          <t>https://www.indeed.com/viewjob?jk=3e77317858ff838d</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>DOCSIS Testing Engineer</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PEARLY</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, NoSQL, ETL, ELT, Splunk, CI/CD, Docker</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e134c7566cf151c</t>
+          <t>https://www.indeed.com/viewjob?jk=9737f288d965528f</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SSO Administrator</t>
+          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ABCorp NA Inc.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b109c86f55c8c21f</t>
+          <t>https://www.indeed.com/viewjob?jk=5d8f6d93b707b783</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=843b039e4e75f61f</t>
+          <t>https://www.indeed.com/viewjob?jk=b7dfde3b442bd5c7</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Clarksville, TN, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ead7f0da7c5db1</t>
+          <t>https://www.indeed.com/viewjob?jk=503ceed67966f48a</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, Kafka, Dimensional Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae8a17a1c6f39e3</t>
+          <t>https://www.indeed.com/viewjob?jk=503c92a0918e2779</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Software Engineer III - Data Engineering Java/Python</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,102 +4031,102 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5c91aac0db662ae</t>
+          <t>https://www.indeed.com/viewjob?jk=6dfc1c1ddf5b07e8</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (FDE)</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ISHIR</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ecc0cd2b5a2111</t>
+          <t>https://www.indeed.com/viewjob?jk=cab7b07d708701fa</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
+          <t>Software Engineer (Backend) - Global Dining</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=151fe9868f44f2f1</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f71d52efce43e2</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,42 +4136,1022 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=739e08afe4ba1176</t>
+          <t>https://www.indeed.com/viewjob?jk=110f275787ec7bdb</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
+          <t>Senior Data Engineer - Data Governance</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Alter Domus</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, Glue, S3, IAM, RDS, Databricks, Unity Catalog, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c3d83b504ed46b0c</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Software Engineer, Data Platform</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Middesk</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, RDS, Azure, Spark, Data Modeling, Terraform, Kubernetes, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=514717df8eb087ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Skechers</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Hermosa Beach, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4bf4b62fe049b84e</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Reporting Engineer</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Surgery Partners</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57ca41478bb936cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Senior Risk Developer (Python/Azure)</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Sumitomo Group</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7762d03304071b69</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>hatch IT</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, ETL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b260e746e7b9c233</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer (SRE)</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>hatch IT</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, ECS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Datadog</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c08c735142c13e1b</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>.NET Angular Reporting Developer</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>S3, RDS, Azure, Scala, SQL Server, Star Schema, ETL, Power BI, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f21a948f0ac42414</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>NavitasPartners</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2698e1f59bd5def7</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>NavitasPartners</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Long Island City, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d0bc94cbe8822db</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>NavitasPartners</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Paterson, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=75f6d90e6b234f60</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>NavitasPartners</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Yonkers, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e53f9ddcb5f4c2b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>NavitasPartners</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=44fb3987d11d1123</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer(61249-1)</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Vytwo Technologies</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Prosper, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, Airflow</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b5fdd13d31dd0aa1</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Entry-Level Data Engineer</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Warren, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dd80dc2e6636141e</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Lyric</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b5cdc524b199967</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>DevSecOps Engineer III</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Kapitus</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, AWS CodePipeline</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31099f3a1c434171</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Azure Network Engineer</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=29fd50cad36943ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Azure Stack Data Engineer</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>AAON</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Tulsa, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Data Modeling, ETL, Power BI, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=20dcbc83d5643838</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>SSO Administrator</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b109c86f55c8c21f</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Reporting Engineer</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Surgery Partners</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=739e08afe4ba1176</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Senior Engineer - .NET</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=843b039e4e75f61f</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Chevy Chase, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1ead7f0da7c5db1</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ae8a17a1c6f39e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Senior Engineer - .NET</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Chevy Chase, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e5c91aac0db662ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>CrowdStrike</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=151fe9868f44f2f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer (FDE)</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>ISHIR</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15ecc0cd2b5a2111</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
           <t>IT PROFESSIONAL-APPLICATIONS (Database Administrator) (HEC)</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B134" t="inlineStr">
         <is>
           <t>City of Houston, TX</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C134" t="inlineStr">
         <is>
           <t>Houston, TX, US USA</t>
         </is>
       </c>
-      <c r="D107" t="n">
+      <c r="D134" t="n">
         <v>10.4</v>
       </c>
-      <c r="E107" t="inlineStr">
+      <c r="E134" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=e1c369e1e8241c9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>DOCSIS Testing Engineer</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, Scala, NoSQL, ETL, ELT, Splunk, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0e134c7566cf151c</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-04.xlsx
+++ b/results/job_matches_2026-03-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G135"/>
+  <dimension ref="A1:G139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2078,25 +2078,25 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Backend Software Engineer III - API Platform</t>
+          <t>Blockchain Java Backend Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, API Gateway, RDS, Databricks, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd1c3ba542522bad</t>
+          <t>https://www.indeed.com/viewjob?jk=e49019e3e57d794c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer II,</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4edb591674d441f</t>
+          <t>https://www.indeed.com/viewjob?jk=0997a11d6aaf4e73</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Blockchain Java Backend Engineer</t>
+          <t>Software Engineer II,</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Redshift, ECS, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e49019e3e57d794c</t>
+          <t>https://www.indeed.com/viewjob?jk=b4edb591674d441f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer II,</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,17 +2201,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Redshift, ECS, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0997a11d6aaf4e73</t>
+          <t>https://www.indeed.com/viewjob?jk=28ab3491bb9f5589</t>
         </is>
       </c>
     </row>
@@ -2393,17 +2393,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d49d017dead0cec</t>
+          <t>https://www.indeed.com/viewjob?jk=b08c3dc1b325be49</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b08c3dc1b325be49</t>
+          <t>https://www.indeed.com/viewjob?jk=7d49d017dead0cec</t>
         </is>
       </c>
     </row>
@@ -2533,17 +2533,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Associate/Consultant Engineer - Remote</t>
+          <t>Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Rancho BioSciences</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd467efc7d909226</t>
+          <t>https://www.indeed.com/viewjob?jk=80460d4e824e28cc</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer - Remote</t>
+          <t>Associate/Consultant Engineer - Remote</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Rancho BioSciences</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80460d4e824e28cc</t>
+          <t>https://www.indeed.com/viewjob?jk=cd467efc7d909226</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2848,17 +2848,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cloud Identity Architect</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ivo</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdd1e41d5949d150</t>
+          <t>https://www.indeed.com/viewjob?jk=8bc5aaef611937ad</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Cloud Identity Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ivo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,17 +2901,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bc5aaef611937ad</t>
+          <t>https://www.indeed.com/viewjob?jk=fdd1e41d5949d150</t>
         </is>
       </c>
     </row>
@@ -3478,17 +3478,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Risk Data AI/ML Engineer</t>
+          <t>Senior Software Engineer II - AI/ML</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=979402388d34b409</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0bc9a390582054</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Databricks AI Engineer</t>
+          <t>Risk Data AI/ML Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Powerplan</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,17 +3531,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5753d39b44c782</t>
+          <t>https://www.indeed.com/viewjob?jk=979402388d34b409</t>
         </is>
       </c>
     </row>
@@ -3653,25 +3653,25 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Network IoT Engineer</t>
+          <t>Senior Databricks AI Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Powerplan</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,14 +3681,14 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da29d3af250447a</t>
+          <t>https://www.indeed.com/viewjob?jk=3b5753d39b44c782</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Network IoT Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT, MLflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fc978b16714d0d2</t>
+          <t>https://www.indeed.com/viewjob?jk=0da29d3af250447a</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9649d08cb62a9ac0</t>
+          <t>https://www.indeed.com/viewjob?jk=7fc978b16714d0d2</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Santa Barbara, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52fbd92226aade92</t>
+          <t>https://www.indeed.com/viewjob?jk=9649d08cb62a9ac0</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Santa Barbara, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e77317858ff838d</t>
+          <t>https://www.indeed.com/viewjob?jk=52fbd92226aade92</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9737f288d965528f</t>
+          <t>https://www.indeed.com/viewjob?jk=3e77317858ff838d</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ABCorp NA Inc.</t>
+          <t>PEARLY</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d8f6d93b707b783</t>
+          <t>https://www.indeed.com/viewjob?jk=9737f288d965528f</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Sr. Software Developer/Programmer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Davis, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Oracle, CI/CD, GitHub Actions, Docker, Kubernetes, SonarQube, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7dfde3b442bd5c7</t>
+          <t>https://www.indeed.com/viewjob?jk=9ce420e446403a9d</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Clarksville, TN, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503ceed67966f48a</t>
+          <t>https://www.indeed.com/viewjob?jk=b7dfde3b442bd5c7</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Clarksville, TN, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, Kafka, Dimensional Modeling, ETL, Airflow</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503c92a0918e2779</t>
+          <t>https://www.indeed.com/viewjob?jk=503ceed67966f48a</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Engineering Java/Python</t>
+          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>ABCorp NA Inc.</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dfc1c1ddf5b07e8</t>
+          <t>https://www.indeed.com/viewjob?jk=5d8f6d93b707b783</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
+          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, Kafka, Dimensional Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab7b07d708701fa</t>
+          <t>https://www.indeed.com/viewjob?jk=503c92a0918e2779</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend) - Global Dining</t>
+          <t>Software Engineer III - Data Engineering Java/Python</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f71d52efce43e2</t>
+          <t>https://www.indeed.com/viewjob?jk=6dfc1c1ddf5b07e8</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,19 +4136,19 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=110f275787ec7bdb</t>
+          <t>https://www.indeed.com/viewjob?jk=cab7b07d708701fa</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Governance</t>
+          <t>Software Engineer (Backend) - Global Dining</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Alter Domus</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Databricks, Unity Catalog, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d83b504ed46b0c</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f71d52efce43e2</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Platform</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Middesk</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Spark, Data Modeling, Terraform, Kubernetes, Airflow, Git</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=514717df8eb087ca</t>
+          <t>https://www.indeed.com/viewjob?jk=110f275787ec7bdb</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Data Engineer - Data Governance</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Alter Domus</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
+          <t>AWS, Glue, S3, IAM, RDS, Databricks, Unity Catalog, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf4b62fe049b84e</t>
+          <t>https://www.indeed.com/viewjob?jk=c3d83b504ed46b0c</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>Middesk</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>AWS, Lambda, RDS, Azure, Spark, Data Modeling, Terraform, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ca41478bb936cd</t>
+          <t>https://www.indeed.com/viewjob?jk=514717df8eb087ca</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Risk Developer (Python/Azure)</t>
+          <t>Sr. Software Engineer, Data, Autonomy</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, MLflow, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7762d03304071b69</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3560765ed8e488</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Risk Developer (Python/Azure)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>hatch IT</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, ETL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,14 +4346,14 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b260e746e7b9c233</t>
+          <t>https://www.indeed.com/viewjob?jk=7762d03304071b69</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Datadog</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c08c735142c13e1b</t>
+          <t>https://www.indeed.com/viewjob?jk=b260e746e7b9c233</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>.NET Angular Reporting Developer</t>
+          <t>Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>hatch IT</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, Star Schema, ETL, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, ECS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21a948f0ac42414</t>
+          <t>https://www.indeed.com/viewjob?jk=c08c735142c13e1b</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2698e1f59bd5def7</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf4b62fe049b84e</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d0bc94cbe8822db</t>
+          <t>https://www.indeed.com/viewjob?jk=57ca41478bb936cd</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
+          <t>.NET Angular Reporting Developer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Paterson, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, Star Schema, ETL, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75f6d90e6b234f60</t>
+          <t>https://www.indeed.com/viewjob?jk=f21a948f0ac42414</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e53f9ddcb5f4c2b9</t>
+          <t>https://www.indeed.com/viewjob?jk=2698e1f59bd5def7</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,32 +4591,32 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44fb3987d11d1123</t>
+          <t>https://www.indeed.com/viewjob?jk=4d0bc94cbe8822db</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Data Engineer(61249-1)</t>
+          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Vytwo Technologies</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Prosper, TX, US USA</t>
+          <t>Paterson, NJ, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, Airflow</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,32 +4626,32 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5fdd13d31dd0aa1</t>
+          <t>https://www.indeed.com/viewjob?jk=75f6d90e6b234f60</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Entry-Level Data Engineer</t>
+          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,32 +4661,32 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd80dc2e6636141e</t>
+          <t>https://www.indeed.com/viewjob?jk=e53f9ddcb5f4c2b9</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b5cdc524b199967</t>
+          <t>https://www.indeed.com/viewjob?jk=44fb3987d11d1123</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer III</t>
+          <t>Senior Data Engineer(61249-1)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Kapitus</t>
+          <t>Vytwo Technologies</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Prosper, TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, Airflow</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31099f3a1c434171</t>
+          <t>https://www.indeed.com/viewjob?jk=b5fdd13d31dd0aa1</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Entry-Level Data Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fd50cad36943ce</t>
+          <t>https://www.indeed.com/viewjob?jk=dd80dc2e6636141e</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Azure Stack Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>AAON</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Data Modeling, ETL, Power BI, CI/CD, Docker</t>
+          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20dcbc83d5643838</t>
+          <t>https://www.indeed.com/viewjob?jk=8b5cdc524b199967</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>SSO Administrator</t>
+          <t>DevSecOps Engineer III</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Kapitus</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b109c86f55c8c21f</t>
+          <t>https://www.indeed.com/viewjob?jk=31099f3a1c434171</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
+          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=739e08afe4ba1176</t>
+          <t>https://www.indeed.com/viewjob?jk=29fd50cad36943ce</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Azure Stack Data Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>AAON</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Data Modeling, ETL, Power BI, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=843b039e4e75f61f</t>
+          <t>https://www.indeed.com/viewjob?jk=20dcbc83d5643838</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Sr. Data Engineer, Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,24 +4931,24 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, Databricks, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ead7f0da7c5db1</t>
+          <t>https://www.indeed.com/viewjob?jk=b74ac1e46b3dfa89</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,14 +4976,14 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae8a17a1c6f39e3</t>
+          <t>https://www.indeed.com/viewjob?jk=843b039e4e75f61f</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5c91aac0db662ae</t>
+          <t>https://www.indeed.com/viewjob?jk=c1ead7f0da7c5db1</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=151fe9868f44f2f1</t>
+          <t>https://www.indeed.com/viewjob?jk=1ae8a17a1c6f39e3</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (FDE)</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>ISHIR</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ecc0cd2b5a2111</t>
+          <t>https://www.indeed.com/viewjob?jk=e5c91aac0db662ae</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>IT PROFESSIONAL-APPLICATIONS (Database Administrator) (HEC)</t>
+          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>City of Houston, TX</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,14 +5116,14 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c369e1e8241c9f</t>
+          <t>https://www.indeed.com/viewjob?jk=151fe9868f44f2f1</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>DOCSIS Testing Engineer</t>
+          <t>SSO Administrator</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5141,17 +5141,157 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
+          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b109c86f55c8c21f</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Reporting Engineer</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Surgery Partners</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=739e08afe4ba1176</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>IT PROFESSIONAL-APPLICATIONS (Database Administrator) (HEC)</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>City of Houston, TX</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1c369e1e8241c9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>DOCSIS Testing Engineer</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
           <t>AWS, Azure, Google Cloud Platform, Scala, NoSQL, ETL, ELT, Splunk, CI/CD, Docker</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=0e134c7566cf151c</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer (FDE)</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>ISHIR</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15ecc0cd2b5a2111</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-04.xlsx
+++ b/results/job_matches_2026-03-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G139"/>
+  <dimension ref="A1:G138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,52 +678,52 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III: DevOps</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Quilt</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d883fd388e687a</t>
+          <t>https://www.indeed.com/viewjob?jk=bc952e4224a3aa24</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer - AI Practice Team</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>American Bureau of Shipping (ABS)</t>
+          <t>Quilt</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Azure, Data Factory, Databricks, Event Hubs, BigQuery</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,19 +741,19 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98e9bc7cd1938bfd</t>
+          <t>https://www.indeed.com/viewjob?jk=27d883fd388e687a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Data Engineer - AI Practice Team</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>American Bureau of Shipping (ABS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -762,11 +762,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Azure, Data Factory, Databricks, Event Hubs, BigQuery</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7167050c109be2d4</t>
+          <t>https://www.indeed.com/viewjob?jk=98e9bc7cd1938bfd</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=862a4a8989448fa0</t>
+          <t>https://www.indeed.com/viewjob?jk=7167050c109be2d4</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07e542bb4713fad0</t>
+          <t>https://www.indeed.com/viewjob?jk=862a4a8989448fa0</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c88dff775194e30</t>
+          <t>https://www.indeed.com/viewjob?jk=07e542bb4713fad0</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ced45fe117deb8</t>
+          <t>https://www.indeed.com/viewjob?jk=2c88dff775194e30</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc8e0c810b3e7cd</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ced45fe117deb8</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7791942c877daada</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc8e0c810b3e7cd</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6b39b9b56abc0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=7791942c877daada</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648774ee33ca3b76</t>
+          <t>https://www.indeed.com/viewjob?jk=b6b39b9b56abc0bd</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a93ca1ad887e17f0</t>
+          <t>https://www.indeed.com/viewjob?jk=648774ee33ca3b76</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d963e90dfb3fa4d6</t>
+          <t>https://www.indeed.com/viewjob?jk=a93ca1ad887e17f0</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783ac47e6d62e414</t>
+          <t>https://www.indeed.com/viewjob?jk=d963e90dfb3fa4d6</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e511c7108cd6e82d</t>
+          <t>https://www.indeed.com/viewjob?jk=783ac47e6d62e414</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a6a2ad30fc1236d</t>
+          <t>https://www.indeed.com/viewjob?jk=e511c7108cd6e82d</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2d42f6d55a07b48</t>
+          <t>https://www.indeed.com/viewjob?jk=2a6a2ad30fc1236d</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c423f392a018bf22</t>
+          <t>https://www.indeed.com/viewjob?jk=e2d42f6d55a07b48</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb49af32ea451f63</t>
+          <t>https://www.indeed.com/viewjob?jk=c423f392a018bf22</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7468c4fe6bdb23</t>
+          <t>https://www.indeed.com/viewjob?jk=cb49af32ea451f63</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a3485c3c6153843</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7468c4fe6bdb23</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef4166ba4aa9b5a3</t>
+          <t>https://www.indeed.com/viewjob?jk=3a3485c3c6153843</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91d6e4beb774dd25</t>
+          <t>https://www.indeed.com/viewjob?jk=ef4166ba4aa9b5a3</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcf2824745a050e</t>
+          <t>https://www.indeed.com/viewjob?jk=91d6e4beb774dd25</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b296145590b995</t>
+          <t>https://www.indeed.com/viewjob?jk=adcf2824745a050e</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c4169879098b22b</t>
+          <t>https://www.indeed.com/viewjob?jk=64b296145590b995</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44e1222f0eb14744</t>
+          <t>https://www.indeed.com/viewjob?jk=8c4169879098b22b</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37bd1a8719f0aafc</t>
+          <t>https://www.indeed.com/viewjob?jk=44e1222f0eb14744</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e151b2c0a32e2723</t>
+          <t>https://www.indeed.com/viewjob?jk=37bd1a8719f0aafc</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c07dcca1b609463e</t>
+          <t>https://www.indeed.com/viewjob?jk=e151b2c0a32e2723</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c721bd4ca7bdffe1</t>
+          <t>https://www.indeed.com/viewjob?jk=c07dcca1b609463e</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8e182c6058fd2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=c721bd4ca7bdffe1</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4997f8f92f05b9d2</t>
+          <t>https://www.indeed.com/viewjob?jk=e8e182c6058fd2a4</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a56481df82d7aa6</t>
+          <t>https://www.indeed.com/viewjob?jk=4997f8f92f05b9d2</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb00c80fb9cb9b65</t>
+          <t>https://www.indeed.com/viewjob?jk=2a56481df82d7aa6</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fd1863254c88e5d</t>
+          <t>https://www.indeed.com/viewjob?jk=fb00c80fb9cb9b65</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6c4839e7fe64d8e</t>
+          <t>https://www.indeed.com/viewjob?jk=3fd1863254c88e5d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Infrastructure</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ALTRUIST</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc6ad57eba624292</t>
+          <t>https://www.indeed.com/viewjob?jk=a6c4839e7fe64d8e</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15325ad687b27337</t>
+          <t>https://www.indeed.com/viewjob?jk=cc6ad57eba624292</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>ALTRUIST</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17c87f0de0ddb952</t>
+          <t>https://www.indeed.com/viewjob?jk=15325ad687b27337</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Blockchain Java Backend Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e49019e3e57d794c</t>
+          <t>https://www.indeed.com/viewjob?jk=17c87f0de0ddb952</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Blockchain Java Backend Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0997a11d6aaf4e73</t>
+          <t>https://www.indeed.com/viewjob?jk=e49019e3e57d794c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer II,</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,17 +2166,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4edb591674d441f</t>
+          <t>https://www.indeed.com/viewjob?jk=0997a11d6aaf4e73</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,59 +2211,59 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28ab3491bb9f5589</t>
+          <t>https://www.indeed.com/viewjob?jk=b4edb591674d441f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II,</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Redshift, ECS, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cc63cdd2328277c</t>
+          <t>https://www.indeed.com/viewjob?jk=28ab3491bb9f5589</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer, AI Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Residex, LLC</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b994e1736909aed</t>
+          <t>https://www.indeed.com/viewjob?jk=4cc63cdd2328277c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Cloud Software Engineer</t>
+          <t>Software Engineer, AI Analytics</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ELLKAY, LLC</t>
+          <t>Residex, LLC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Elmwood Park, NJ, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28b63f4ef510667a</t>
+          <t>https://www.indeed.com/viewjob?jk=3b994e1736909aed</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Associate/Consultant Engineer - Remote</t>
+          <t>Sr. Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Rancho BioSciences</t>
+          <t>ELLKAY, LLC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Elmwood Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Athena, IAM, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72630d316687619c</t>
+          <t>https://www.indeed.com/viewjob?jk=28b63f4ef510667a</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Associate/Consultant Engineer - Remote</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Rancho BioSciences</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b12dfc8a5459a4f</t>
+          <t>https://www.indeed.com/viewjob?jk=72630d316687619c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b08c3dc1b325be49</t>
+          <t>https://www.indeed.com/viewjob?jk=2b12dfc8a5459a4f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d49d017dead0cec</t>
+          <t>https://www.indeed.com/viewjob?jk=b08c3dc1b325be49</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ncontracts</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da52963e4860aaaa</t>
+          <t>https://www.indeed.com/viewjob?jk=7d49d017dead0cec</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer - Kafka Connect</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CloudRay Inc</t>
+          <t>Ncontracts</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5df3111682f7946</t>
+          <t>https://www.indeed.com/viewjob?jk=da52963e4860aaaa</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer - Remote</t>
+          <t>Data Engineer - Kafka Connect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CloudRay Inc</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
+          <t>AWS, S3, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80460d4e824e28cc</t>
+          <t>https://www.indeed.com/viewjob?jk=d5df3111682f7946</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Associate/Consultant Engineer - Remote</t>
+          <t>Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Rancho BioSciences</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd467efc7d909226</t>
+          <t>https://www.indeed.com/viewjob?jk=80460d4e824e28cc</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer + Snowflake (On-Site)</t>
+          <t>Associate/Consultant Engineer - Remote</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Rancho BioSciences</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e9f31119d31013</t>
+          <t>https://www.indeed.com/viewjob?jk=cd467efc7d909226</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PDM Implementation Data Architect</t>
+          <t>Cloud Data Engineer + Snowflake (On-Site)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, RDS, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3576de9e88dd4c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=58e9f31119d31013</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>PDM Implementation Data Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a53eba2ddb1389c4</t>
+          <t>https://www.indeed.com/viewjob?jk=3576de9e88dd4c5c</t>
         </is>
       </c>
     </row>
@@ -2918,17 +2918,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>System Integration Test Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ai Vantage</t>
+          <t>BGIT India Private Limited</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Hudson, NH, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87747bfcd30cdbc2</t>
+          <t>https://www.indeed.com/viewjob?jk=426d1d0d6a93918c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>System Integration Test Engineer</t>
+          <t>ETL Testing with Azure Databricks in Healthcare</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BGIT India Private Limited</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hudson, NH, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=426d1d0d6a93918c</t>
+          <t>https://www.indeed.com/viewjob?jk=9af37a4075a8760f</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7c80e2086f0d108</t>
+          <t>https://www.indeed.com/viewjob?jk=662840de4364e997</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ETL Testing with Azure Databricks in Healthcare</t>
+          <t>Software Engineer II - Scala</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Scala, Oracle</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9af37a4075a8760f</t>
+          <t>https://www.indeed.com/viewjob?jk=d148fa8c6ae39fd8</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Data Platform Engineer-2</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=662840de4364e997</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f9103ddd4f544e</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer II - Scala</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d148fa8c6ae39fd8</t>
+          <t>https://www.indeed.com/viewjob?jk=75d602908669423e</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-2</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,17 +3146,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f9103ddd4f544e</t>
+          <t>https://www.indeed.com/viewjob?jk=10de5f0ca2f7673d</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d602908669423e</t>
+          <t>https://www.indeed.com/viewjob?jk=8e6750fd9ad4e72e</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10de5f0ca2f7673d</t>
+          <t>https://www.indeed.com/viewjob?jk=c45db6ac50eb5587</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6750fd9ad4e72e</t>
+          <t>https://www.indeed.com/viewjob?jk=d1c0f7e27e90a87e</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45db6ac50eb5587</t>
+          <t>https://www.indeed.com/viewjob?jk=a4dc81e5cd9b6b72</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1c0f7e27e90a87e</t>
+          <t>https://www.indeed.com/viewjob?jk=14fea47c1dbfabac</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4dc81e5cd9b6b72</t>
+          <t>https://www.indeed.com/viewjob?jk=02d7bcc2bd0697b0</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14fea47c1dbfabac</t>
+          <t>https://www.indeed.com/viewjob?jk=50e0ff85e5f89851</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>Senior Software Engineer II - AI/ML</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02d7bcc2bd0697b0</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0bc9a390582054</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>Risk Data AI/ML Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50e0ff85e5f89851</t>
+          <t>https://www.indeed.com/viewjob?jk=979402388d34b409</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - AI/ML</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>ELLKAY, LLC</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Elmwood Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, EMR, S3, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Streams/Tasks</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0bc9a390582054</t>
+          <t>https://www.indeed.com/viewjob?jk=c7bfd917914d4728</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Risk Data AI/ML Engineer</t>
+          <t>Sr DevOPS Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=979402388d34b409</t>
+          <t>https://www.indeed.com/viewjob?jk=9886d247b0ec7a02</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Platform-DevOps Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ELLKAY, LLC</t>
+          <t>NXLog</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Elmwood Park, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Streams/Tasks</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7bfd917914d4728</t>
+          <t>https://www.indeed.com/viewjob?jk=6e7328772f0c8abe</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer</t>
+          <t>Senior Databricks AI Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Powerplan</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9886d247b0ec7a02</t>
+          <t>https://www.indeed.com/viewjob?jk=3b5753d39b44c782</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Platform-DevOps Engineer</t>
+          <t>Network IoT Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>NXLog</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e7328772f0c8abe</t>
+          <t>https://www.indeed.com/viewjob?jk=0da29d3af250447a</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Databricks AI Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Powerplan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5753d39b44c782</t>
+          <t>https://www.indeed.com/viewjob?jk=7fc978b16714d0d2</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Network IoT Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da29d3af250447a</t>
+          <t>https://www.indeed.com/viewjob?jk=9649d08cb62a9ac0</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Waters</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Milford, MA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fc978b16714d0d2</t>
+          <t>https://www.indeed.com/viewjob?jk=1975adb5bfc7de33</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>PEARLY</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Santa Barbara, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9649d08cb62a9ac0</t>
+          <t>https://www.indeed.com/viewjob?jk=52fbd92226aade92</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Santa Barbara, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52fbd92226aade92</t>
+          <t>https://www.indeed.com/viewjob?jk=3e77317858ff838d</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e77317858ff838d</t>
+          <t>https://www.indeed.com/viewjob?jk=9737f288d965528f</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Sr. Software Developer/Programmer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Davis, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Scala, Oracle, CI/CD, GitHub Actions, Docker, Kubernetes, SonarQube, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9737f288d965528f</t>
+          <t>https://www.indeed.com/viewjob?jk=9ce420e446403a9d</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Sr. Software Developer/Programmer</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Davis, CA, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, CI/CD, GitHub Actions, Docker, Kubernetes, SonarQube, Git</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ce420e446403a9d</t>
+          <t>https://www.indeed.com/viewjob?jk=b7dfde3b442bd5c7</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Clarksville, TN, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7dfde3b442bd5c7</t>
+          <t>https://www.indeed.com/viewjob?jk=503ceed67966f48a</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>ABCorp NA Inc.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Clarksville, TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503ceed67966f48a</t>
+          <t>https://www.indeed.com/viewjob?jk=5d8f6d93b707b783</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ABCorp NA Inc.</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, Kafka, Dimensional Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d8f6d93b707b783</t>
+          <t>https://www.indeed.com/viewjob?jk=503c92a0918e2779</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Software Engineer III - Data Engineering Java/Python</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, Kafka, Dimensional Modeling, ETL, Airflow</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503c92a0918e2779</t>
+          <t>https://www.indeed.com/viewjob?jk=6dfc1c1ddf5b07e8</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Engineering Java/Python</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dfc1c1ddf5b07e8</t>
+          <t>https://www.indeed.com/viewjob?jk=cab7b07d708701fa</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>Software Engineer (Backend) - Global Dining</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab7b07d708701fa</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f71d52efce43e2</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend) - Global Dining</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f71d52efce43e2</t>
+          <t>https://www.indeed.com/viewjob?jk=110f275787ec7bdb</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior Data Engineer - Data Governance</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Alter Domus</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Glue, S3, IAM, RDS, Databricks, Unity Catalog, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=110f275787ec7bdb</t>
+          <t>https://www.indeed.com/viewjob?jk=c3d83b504ed46b0c</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Governance</t>
+          <t>Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Alter Domus</t>
+          <t>Middesk</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Databricks, Unity Catalog, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, Spark, Data Modeling, Terraform, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d83b504ed46b0c</t>
+          <t>https://www.indeed.com/viewjob?jk=514717df8eb087ca</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Platform</t>
+          <t>Sr. Software Engineer, Data, Autonomy</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Middesk</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Spark, Data Modeling, Terraform, Kubernetes, Airflow, Git</t>
+          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=514717df8eb087ca</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3560765ed8e488</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Data, Autonomy</t>
+          <t>Senior Risk Developer (Python/Azure)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, DynamoDB, CI/CD</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3560765ed8e488</t>
+          <t>https://www.indeed.com/viewjob?jk=7762d03304071b69</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Risk Developer (Python/Azure)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>hatch IT</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, MLflow, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,14 +4346,14 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7762d03304071b69</t>
+          <t>https://www.indeed.com/viewjob?jk=b260e746e7b9c233</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, ETL, CI/CD, Terraform</t>
+          <t>AWS, ECS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b260e746e7b9c233</t>
+          <t>https://www.indeed.com/viewjob?jk=c08c735142c13e1b</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>hatch IT</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Datadog</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c08c735142c13e1b</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf4b62fe049b84e</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf4b62fe049b84e</t>
+          <t>https://www.indeed.com/viewjob?jk=57ca41478bb936cd</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>.NET Angular Reporting Developer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, Star Schema, ETL, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ca41478bb936cd</t>
+          <t>https://www.indeed.com/viewjob?jk=f21a948f0ac42414</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>.NET Angular Reporting Developer</t>
+          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, Star Schema, ETL, Power BI, CI/CD, Azure DevOps</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21a948f0ac42414</t>
+          <t>https://www.indeed.com/viewjob?jk=2698e1f59bd5def7</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2698e1f59bd5def7</t>
+          <t>https://www.indeed.com/viewjob?jk=4d0bc94cbe8822db</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Paterson, NJ, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d0bc94cbe8822db</t>
+          <t>https://www.indeed.com/viewjob?jk=75f6d90e6b234f60</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Paterson, NJ, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75f6d90e6b234f60</t>
+          <t>https://www.indeed.com/viewjob?jk=e53f9ddcb5f4c2b9</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,32 +4661,32 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e53f9ddcb5f4c2b9</t>
+          <t>https://www.indeed.com/viewjob?jk=44fb3987d11d1123</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
+          <t>Senior Data Engineer(61249-1)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Vytwo Technologies</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Prosper, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, Airflow</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44fb3987d11d1123</t>
+          <t>https://www.indeed.com/viewjob?jk=b5fdd13d31dd0aa1</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Data Engineer(61249-1)</t>
+          <t>Entry-Level Data Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Vytwo Technologies</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Prosper, TX, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5fdd13d31dd0aa1</t>
+          <t>https://www.indeed.com/viewjob?jk=dd80dc2e6636141e</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Entry-Level Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd80dc2e6636141e</t>
+          <t>https://www.indeed.com/viewjob?jk=8b5cdc524b199967</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevSecOps Engineer III</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>Kapitus</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b5cdc524b199967</t>
+          <t>https://www.indeed.com/viewjob?jk=31099f3a1c434171</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer III</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Kapitus</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31099f3a1c434171</t>
+          <t>https://www.indeed.com/viewjob?jk=29fd50cad36943ce</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Azure Stack Data Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AAON</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Data Modeling, ETL, Power BI, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fd50cad36943ce</t>
+          <t>https://www.indeed.com/viewjob?jk=20dcbc83d5643838</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Azure Stack Data Engineer</t>
+          <t>Sr. Data Engineer, Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>AAON</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Data Modeling, ETL, Power BI, CI/CD, Docker</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, Databricks, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20dcbc83d5643838</t>
+          <t>https://www.indeed.com/viewjob?jk=b74ac1e46b3dfa89</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Enterprise Data &amp; Analytics</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,24 +4931,24 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, Databricks, Data Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b74ac1e46b3dfa89</t>
+          <t>https://www.indeed.com/viewjob?jk=843b039e4e75f61f</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=843b039e4e75f61f</t>
+          <t>https://www.indeed.com/viewjob?jk=c1ead7f0da7c5db1</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,14 +5011,14 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ead7f0da7c5db1</t>
+          <t>https://www.indeed.com/viewjob?jk=1ae8a17a1c6f39e3</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae8a17a1c6f39e3</t>
+          <t>https://www.indeed.com/viewjob?jk=e5c91aac0db662ae</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5c91aac0db662ae</t>
+          <t>https://www.indeed.com/viewjob?jk=151fe9868f44f2f1</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
+          <t>SSO Administrator</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=151fe9868f44f2f1</t>
+          <t>https://www.indeed.com/viewjob?jk=b109c86f55c8c21f</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>SSO Administrator</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
+          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b109c86f55c8c21f</t>
+          <t>https://www.indeed.com/viewjob?jk=739e08afe4ba1176</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>ISHIR</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,17 +5176,17 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=739e08afe4ba1176</t>
+          <t>https://www.indeed.com/viewjob?jk=15ecc0cd2b5a2111</t>
         </is>
       </c>
     </row>
@@ -5257,41 +5257,6 @@
       <c r="G138" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=0e134c7566cf151c</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Forward Deployed Engineer (FDE)</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>ISHIR</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=15ecc0cd2b5a2111</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-04.xlsx
+++ b/results/job_matches_2026-03-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G138"/>
+  <dimension ref="A1:G140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1973,17 +1973,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>ALTRUIST</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6c4839e7fe64d8e</t>
+          <t>https://www.indeed.com/viewjob?jk=b2b2e3b90367f3b4</t>
         </is>
       </c>
     </row>
@@ -2031,29 +2031,29 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc6ad57eba624292</t>
+          <t>https://www.indeed.com/viewjob?jk=15721c69bc524693</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Infrastructure</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ALTRUIST</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15325ad687b27337</t>
+          <t>https://www.indeed.com/viewjob?jk=a6c4839e7fe64d8e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>ALTRUIST</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17c87f0de0ddb952</t>
+          <t>https://www.indeed.com/viewjob?jk=cc6ad57eba624292</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Blockchain Java Backend Engineer</t>
+          <t>Senior Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>ALTRUIST</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e49019e3e57d794c</t>
+          <t>https://www.indeed.com/viewjob?jk=15325ad687b27337</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0997a11d6aaf4e73</t>
+          <t>https://www.indeed.com/viewjob?jk=17c87f0de0ddb952</t>
         </is>
       </c>
     </row>
@@ -2253,25 +2253,25 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Blockchain Java Backend Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cc63cdd2328277c</t>
+          <t>https://www.indeed.com/viewjob?jk=e49019e3e57d794c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer, AI Analytics</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Residex, LLC</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b994e1736909aed</t>
+          <t>https://www.indeed.com/viewjob?jk=0997a11d6aaf4e73</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Cloud Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ELLKAY, LLC</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Elmwood Park, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28b63f4ef510667a</t>
+          <t>https://www.indeed.com/viewjob?jk=4cc63cdd2328277c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Associate/Consultant Engineer - Remote</t>
+          <t>Software Engineer, AI Analytics</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Rancho BioSciences</t>
+          <t>Residex, LLC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72630d316687619c</t>
+          <t>https://www.indeed.com/viewjob?jk=3b994e1736909aed</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Sr. Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>ELLKAY, LLC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Elmwood Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
+          <t>AWS, Athena, IAM, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b12dfc8a5459a4f</t>
+          <t>https://www.indeed.com/viewjob?jk=28b63f4ef510667a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Associate/Consultant Engineer - Remote</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Rancho BioSciences</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b08c3dc1b325be49</t>
+          <t>https://www.indeed.com/viewjob?jk=72630d316687619c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d49d017dead0cec</t>
+          <t>https://www.indeed.com/viewjob?jk=2b12dfc8a5459a4f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ncontracts</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da52963e4860aaaa</t>
+          <t>https://www.indeed.com/viewjob?jk=7d49d017dead0cec</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer - Kafka Connect</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CloudRay Inc</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5df3111682f7946</t>
+          <t>https://www.indeed.com/viewjob?jk=b08c3dc1b325be49</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer - Remote</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Ncontracts</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80460d4e824e28cc</t>
+          <t>https://www.indeed.com/viewjob?jk=da52963e4860aaaa</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Associate/Consultant Engineer - Remote</t>
+          <t>Data Engineer - Kafka Connect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Rancho BioSciences</t>
+          <t>CloudRay Inc</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, S3, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd467efc7d909226</t>
+          <t>https://www.indeed.com/viewjob?jk=d5df3111682f7946</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer + Snowflake (On-Site)</t>
+          <t>Associate/Consultant Engineer - Remote</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Rancho BioSciences</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e9f31119d31013</t>
+          <t>https://www.indeed.com/viewjob?jk=cd467efc7d909226</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PDM Implementation Data Architect</t>
+          <t>Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Spark, PySpark</t>
+          <t>AWS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3576de9e88dd4c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=80460d4e824e28cc</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Cloud Data Engineer + Snowflake (On-Site)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
+          <t>AWS, Glue, EMR, RDS, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a6c4ab9efc012e</t>
+          <t>https://www.indeed.com/viewjob?jk=58e9f31119d31013</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>PDM Implementation Data Architect</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ROLLER</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb709659d664135</t>
+          <t>https://www.indeed.com/viewjob?jk=3576de9e88dd4c5c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Google Cloud Network Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c97eb9417ef8ebcf</t>
+          <t>https://www.indeed.com/viewjob?jk=39a6c4ab9efc012e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer, CDC</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>DRT Strategies, Inc.</t>
+          <t>ROLLER</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Scala, ETL, Power BI, Tableau, CI/CD, Docker</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a223a368864e5d1b</t>
+          <t>https://www.indeed.com/viewjob?jk=afb709659d664135</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Google Cloud Network Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ivo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bc5aaef611937ad</t>
+          <t>https://www.indeed.com/viewjob?jk=c97eb9417ef8ebcf</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cloud Identity Architect</t>
+          <t>Data Engineer, CDC</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>DRT Strategies, Inc.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
+          <t>AWS, EMR, RDS, Azure, Scala, ETL, Power BI, Tableau, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdd1e41d5949d150</t>
+          <t>https://www.indeed.com/viewjob?jk=a223a368864e5d1b</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>System Integration Test Engineer</t>
+          <t>Cloud Identity Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BGIT India Private Limited</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hudson, NH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,67 +2946,67 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=426d1d0d6a93918c</t>
+          <t>https://www.indeed.com/viewjob?jk=fdd1e41d5949d150</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ETL Testing with Azure Databricks in Healthcare</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>ivo</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Scala, Oracle</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9af37a4075a8760f</t>
+          <t>https://www.indeed.com/viewjob?jk=8bc5aaef611937ad</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>System Integration Test Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BGIT India Private Limited</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Hudson, NH, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=662840de4364e997</t>
+          <t>https://www.indeed.com/viewjob?jk=426d1d0d6a93918c</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer II - Scala</t>
+          <t>ETL Testing with Azure Databricks in Healthcare</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d148fa8c6ae39fd8</t>
+          <t>https://www.indeed.com/viewjob?jk=9af37a4075a8760f</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-2</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f9103ddd4f544e</t>
+          <t>https://www.indeed.com/viewjob?jk=662840de4364e997</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>Software Engineer II - Scala</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d602908669423e</t>
+          <t>https://www.indeed.com/viewjob?jk=d148fa8c6ae39fd8</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>Data Platform Engineer-2</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,17 +3146,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10de5f0ca2f7673d</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f9103ddd4f544e</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6750fd9ad4e72e</t>
+          <t>https://www.indeed.com/viewjob?jk=75d602908669423e</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45db6ac50eb5587</t>
+          <t>https://www.indeed.com/viewjob?jk=10de5f0ca2f7673d</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1c0f7e27e90a87e</t>
+          <t>https://www.indeed.com/viewjob?jk=8e6750fd9ad4e72e</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4dc81e5cd9b6b72</t>
+          <t>https://www.indeed.com/viewjob?jk=c45db6ac50eb5587</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14fea47c1dbfabac</t>
+          <t>https://www.indeed.com/viewjob?jk=d1c0f7e27e90a87e</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02d7bcc2bd0697b0</t>
+          <t>https://www.indeed.com/viewjob?jk=a4dc81e5cd9b6b72</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50e0ff85e5f89851</t>
+          <t>https://www.indeed.com/viewjob?jk=14fea47c1dbfabac</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - AI/ML</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0bc9a390582054</t>
+          <t>https://www.indeed.com/viewjob?jk=02d7bcc2bd0697b0</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Risk Data AI/ML Engineer</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=979402388d34b409</t>
+          <t>https://www.indeed.com/viewjob?jk=50e0ff85e5f89851</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer II - AI/ML</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ELLKAY, LLC</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Elmwood Park, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Streams/Tasks</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7bfd917914d4728</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0bc9a390582054</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer</t>
+          <t>Risk Data AI/ML Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9886d247b0ec7a02</t>
+          <t>https://www.indeed.com/viewjob?jk=979402388d34b409</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Platform-DevOps Engineer</t>
+          <t>Senior Databricks AI Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>NXLog</t>
+          <t>Powerplan</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e7328772f0c8abe</t>
+          <t>https://www.indeed.com/viewjob?jk=3b5753d39b44c782</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Databricks AI Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Powerplan</t>
+          <t>ELLKAY, LLC</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Elmwood Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake</t>
+          <t>AWS, EMR, S3, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Streams/Tasks</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5753d39b44c782</t>
+          <t>https://www.indeed.com/viewjob?jk=c7bfd917914d4728</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Network IoT Engineer</t>
+          <t>Sr DevOPS Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da29d3af250447a</t>
+          <t>https://www.indeed.com/viewjob?jk=9886d247b0ec7a02</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Platform-DevOps Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NXLog</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT, MLflow</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fc978b16714d0d2</t>
+          <t>https://www.indeed.com/viewjob?jk=6e7328772f0c8abe</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Network IoT Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9649d08cb62a9ac0</t>
+          <t>https://www.indeed.com/viewjob?jk=0da29d3af250447a</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Waters</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Milford, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1975adb5bfc7de33</t>
+          <t>https://www.indeed.com/viewjob?jk=7fc978b16714d0d2</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Santa Barbara, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52fbd92226aade92</t>
+          <t>https://www.indeed.com/viewjob?jk=9649d08cb62a9ac0</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>Waters</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Milford, MA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e77317858ff838d</t>
+          <t>https://www.indeed.com/viewjob?jk=1975adb5bfc7de33</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Santa Barbara, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9737f288d965528f</t>
+          <t>https://www.indeed.com/viewjob?jk=52fbd92226aade92</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sr. Software Developer/Programmer</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>PEARLY</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Davis, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, CI/CD, GitHub Actions, Docker, Kubernetes, SonarQube, Git</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ce420e446403a9d</t>
+          <t>https://www.indeed.com/viewjob?jk=3e77317858ff838d</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>PEARLY</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7dfde3b442bd5c7</t>
+          <t>https://www.indeed.com/viewjob?jk=9737f288d965528f</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Sr. Software Developer/Programmer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Clarksville, TN, US USA</t>
+          <t>Davis, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Oracle, CI/CD, GitHub Actions, Docker, Kubernetes, SonarQube, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503ceed67966f48a</t>
+          <t>https://www.indeed.com/viewjob?jk=9ce420e446403a9d</t>
         </is>
       </c>
     </row>
@@ -4003,25 +4003,25 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, Kafka, Dimensional Modeling, ETL, Airflow</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503c92a0918e2779</t>
+          <t>https://www.indeed.com/viewjob?jk=b7dfde3b442bd5c7</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Engineering Java/Python</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Clarksville, TN, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dfc1c1ddf5b07e8</t>
+          <t>https://www.indeed.com/viewjob?jk=503ceed67966f48a</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
+          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, Kafka, Dimensional Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab7b07d708701fa</t>
+          <t>https://www.indeed.com/viewjob?jk=503c92a0918e2779</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend) - Global Dining</t>
+          <t>Software Engineer III - Data Engineering Java/Python</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f71d52efce43e2</t>
+          <t>https://www.indeed.com/viewjob?jk=6dfc1c1ddf5b07e8</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,19 +4171,19 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=110f275787ec7bdb</t>
+          <t>https://www.indeed.com/viewjob?jk=cab7b07d708701fa</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Governance</t>
+          <t>Software Engineer (Backend) - Global Dining</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Alter Domus</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Databricks, Unity Catalog, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d83b504ed46b0c</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f71d52efce43e2</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Platform</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Middesk</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Spark, Data Modeling, Terraform, Kubernetes, Airflow, Git</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=514717df8eb087ca</t>
+          <t>https://www.indeed.com/viewjob?jk=110f275787ec7bdb</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Data, Autonomy</t>
+          <t>Senior Data Engineer - Data Governance</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Alter Domus</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, Glue, S3, IAM, RDS, Databricks, Unity Catalog, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3560765ed8e488</t>
+          <t>https://www.indeed.com/viewjob?jk=c3d83b504ed46b0c</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Risk Developer (Python/Azure)</t>
+          <t>Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Middesk</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, MLflow, CI/CD</t>
+          <t>AWS, Lambda, RDS, Azure, Spark, Data Modeling, Terraform, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7762d03304071b69</t>
+          <t>https://www.indeed.com/viewjob?jk=514717df8eb087ca</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Engineer, Data, Autonomy</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>hatch IT</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, ETL, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b260e746e7b9c233</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3560765ed8e488</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>hatch IT</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Datadog</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c08c735142c13e1b</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf4b62fe049b84e</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf4b62fe049b84e</t>
+          <t>https://www.indeed.com/viewjob?jk=57ca41478bb936cd</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>Senior Risk Developer (Python/Azure)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ca41478bb936cd</t>
+          <t>https://www.indeed.com/viewjob?jk=7762d03304071b69</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>.NET Angular Reporting Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>hatch IT</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, Star Schema, ETL, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21a948f0ac42414</t>
+          <t>https://www.indeed.com/viewjob?jk=b260e746e7b9c233</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
+          <t>Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>hatch IT</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>AWS, ECS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2698e1f59bd5def7</t>
+          <t>https://www.indeed.com/viewjob?jk=c08c735142c13e1b</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
+          <t>.NET Angular Reporting Developer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, Star Schema, ETL, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d0bc94cbe8822db</t>
+          <t>https://www.indeed.com/viewjob?jk=f21a948f0ac42414</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Paterson, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75f6d90e6b234f60</t>
+          <t>https://www.indeed.com/viewjob?jk=2698e1f59bd5def7</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e53f9ddcb5f4c2b9</t>
+          <t>https://www.indeed.com/viewjob?jk=4d0bc94cbe8822db</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Paterson, NJ, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,32 +4661,32 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44fb3987d11d1123</t>
+          <t>https://www.indeed.com/viewjob?jk=75f6d90e6b234f60</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Data Engineer(61249-1)</t>
+          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Vytwo Technologies</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Prosper, TX, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, Airflow</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,32 +4696,32 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5fdd13d31dd0aa1</t>
+          <t>https://www.indeed.com/viewjob?jk=e53f9ddcb5f4c2b9</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Entry-Level Data Engineer</t>
+          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd80dc2e6636141e</t>
+          <t>https://www.indeed.com/viewjob?jk=44fb3987d11d1123</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer(61249-1)</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>Vytwo Technologies</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Prosper, TX, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, Airflow</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b5cdc524b199967</t>
+          <t>https://www.indeed.com/viewjob?jk=b5fdd13d31dd0aa1</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer III</t>
+          <t>Entry-Level Data Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Kapitus</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31099f3a1c434171</t>
+          <t>https://www.indeed.com/viewjob?jk=dd80dc2e6636141e</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
+          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fd50cad36943ce</t>
+          <t>https://www.indeed.com/viewjob?jk=8b5cdc524b199967</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Azure Stack Data Engineer</t>
+          <t>DevSecOps Engineer III</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>AAON</t>
+          <t>Kapitus</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Data Modeling, ETL, Power BI, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20dcbc83d5643838</t>
+          <t>https://www.indeed.com/viewjob?jk=31099f3a1c434171</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Enterprise Data &amp; Analytics</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, Databricks, Data Modeling, ELT, dbt</t>
+          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b74ac1e46b3dfa89</t>
+          <t>https://www.indeed.com/viewjob?jk=29fd50cad36943ce</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Azure Stack Data Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>AAON</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Data Modeling, ETL, Power BI, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=843b039e4e75f61f</t>
+          <t>https://www.indeed.com/viewjob?jk=20dcbc83d5643838</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Sr. Data Engineer, Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, Databricks, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ead7f0da7c5db1</t>
+          <t>https://www.indeed.com/viewjob?jk=b74ac1e46b3dfa89</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>SSO Administrator</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae8a17a1c6f39e3</t>
+          <t>https://www.indeed.com/viewjob?jk=b109c86f55c8c21f</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5c91aac0db662ae</t>
+          <t>https://www.indeed.com/viewjob?jk=739e08afe4ba1176</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=151fe9868f44f2f1</t>
+          <t>https://www.indeed.com/viewjob?jk=843b039e4e75f61f</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SSO Administrator</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b109c86f55c8c21f</t>
+          <t>https://www.indeed.com/viewjob?jk=c1ead7f0da7c5db1</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=739e08afe4ba1176</t>
+          <t>https://www.indeed.com/viewjob?jk=1ae8a17a1c6f39e3</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (FDE)</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>ISHIR</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ecc0cd2b5a2111</t>
+          <t>https://www.indeed.com/viewjob?jk=e5c91aac0db662ae</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>IT PROFESSIONAL-APPLICATIONS (Database Administrator) (HEC)</t>
+          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>City of Houston, TX</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c369e1e8241c9f</t>
+          <t>https://www.indeed.com/viewjob?jk=151fe9868f44f2f1</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>DOCSIS Testing Engineer</t>
+          <t>IT PROFESSIONAL-APPLICATIONS (Database Administrator) (HEC)</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>City of Houston, TX</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,17 +5246,87 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1c369e1e8241c9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>DOCSIS Testing Engineer</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
           <t>AWS, Azure, Google Cloud Platform, Scala, NoSQL, ETL, ELT, Splunk, CI/CD, Docker</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=0e134c7566cf151c</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer (FDE)</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>ISHIR</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15ecc0cd2b5a2111</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-04.xlsx
+++ b/results/job_matches_2026-03-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G140"/>
+  <dimension ref="A1:G143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2568,17 +2568,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ncontracts</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,17 +2586,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da52963e4860aaaa</t>
+          <t>https://www.indeed.com/viewjob?jk=bf6f08ab2860bc5c</t>
         </is>
       </c>
     </row>
@@ -2638,17 +2638,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Associate/Consultant Engineer - Remote</t>
+          <t>LMS Administrator</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Rancho BioSciences</t>
+          <t>Blue Wing Technical</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Decatur, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd467efc7d909226</t>
+          <t>https://www.indeed.com/viewjob?jk=6ea5eba4ba63388f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer - Remote</t>
+          <t>Associate/Consultant Engineer - Remote</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Rancho BioSciences</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80460d4e824e28cc</t>
+          <t>https://www.indeed.com/viewjob?jk=cd467efc7d909226</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer + Snowflake (On-Site)</t>
+          <t>Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e9f31119d31013</t>
+          <t>https://www.indeed.com/viewjob?jk=80460d4e824e28cc</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PDM Implementation Data Architect</t>
+          <t>Incremental CRM - Data Developer 1</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Spark, PySpark</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Databricks, Scala, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3576de9e88dd4c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=3c7931e975a12585</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Cloud Data Engineer + Snowflake (On-Site)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
+          <t>AWS, Glue, EMR, RDS, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a6c4ab9efc012e</t>
+          <t>https://www.indeed.com/viewjob?jk=58e9f31119d31013</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>PDM Implementation Data Architect</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ROLLER</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb709659d664135</t>
+          <t>https://www.indeed.com/viewjob?jk=3576de9e88dd4c5c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Google Cloud Network Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c97eb9417ef8ebcf</t>
+          <t>https://www.indeed.com/viewjob?jk=39a6c4ab9efc012e</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer, CDC</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>DRT Strategies, Inc.</t>
+          <t>ROLLER</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,24 +2901,24 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Scala, ETL, Power BI, Tableau, CI/CD, Docker</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a223a368864e5d1b</t>
+          <t>https://www.indeed.com/viewjob?jk=afb709659d664135</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Cloud Identity Architect</t>
+          <t>Google Cloud Network Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdd1e41d5949d150</t>
+          <t>https://www.indeed.com/viewjob?jk=c97eb9417ef8ebcf</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Data Engineer, CDC</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ivo</t>
+          <t>DRT Strategies, Inc.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, EMR, RDS, Azure, Scala, ETL, Power BI, Tableau, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bc5aaef611937ad</t>
+          <t>https://www.indeed.com/viewjob?jk=a223a368864e5d1b</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>System Integration Test Engineer</t>
+          <t>Cloud Identity Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BGIT India Private Limited</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hudson, NH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,102 +3016,102 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=426d1d0d6a93918c</t>
+          <t>https://www.indeed.com/viewjob?jk=fdd1e41d5949d150</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ETL Testing with Azure Databricks in Healthcare</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>ivo</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Scala, Oracle</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9af37a4075a8760f</t>
+          <t>https://www.indeed.com/viewjob?jk=8bc5aaef611937ad</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=662840de4364e997</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd0439895496e24</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer II - Scala</t>
+          <t>System Integration Test Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BGIT India Private Limited</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hudson, NH, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d148fa8c6ae39fd8</t>
+          <t>https://www.indeed.com/viewjob?jk=426d1d0d6a93918c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-2</t>
+          <t>ETL Testing with Azure Databricks in Healthcare</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f9103ddd4f544e</t>
+          <t>https://www.indeed.com/viewjob?jk=9af37a4075a8760f</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d602908669423e</t>
+          <t>https://www.indeed.com/viewjob?jk=662840de4364e997</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>Software Engineer II - Scala</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10de5f0ca2f7673d</t>
+          <t>https://www.indeed.com/viewjob?jk=d148fa8c6ae39fd8</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>Data Platform Engineer-2</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,17 +3251,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6750fd9ad4e72e</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f9103ddd4f544e</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45db6ac50eb5587</t>
+          <t>https://www.indeed.com/viewjob?jk=75d602908669423e</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1c0f7e27e90a87e</t>
+          <t>https://www.indeed.com/viewjob?jk=10de5f0ca2f7673d</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4dc81e5cd9b6b72</t>
+          <t>https://www.indeed.com/viewjob?jk=8e6750fd9ad4e72e</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14fea47c1dbfabac</t>
+          <t>https://www.indeed.com/viewjob?jk=c45db6ac50eb5587</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02d7bcc2bd0697b0</t>
+          <t>https://www.indeed.com/viewjob?jk=d1c0f7e27e90a87e</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50e0ff85e5f89851</t>
+          <t>https://www.indeed.com/viewjob?jk=a4dc81e5cd9b6b72</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - AI/ML</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0bc9a390582054</t>
+          <t>https://www.indeed.com/viewjob?jk=14fea47c1dbfabac</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Risk Data AI/ML Engineer</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=979402388d34b409</t>
+          <t>https://www.indeed.com/viewjob?jk=02d7bcc2bd0697b0</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Databricks AI Engineer</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Powerplan</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5753d39b44c782</t>
+          <t>https://www.indeed.com/viewjob?jk=50e0ff85e5f89851</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer II - AI/ML</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ELLKAY, LLC</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Elmwood Park, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Streams/Tasks</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7bfd917914d4728</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0bc9a390582054</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer</t>
+          <t>Risk Data AI/ML Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9886d247b0ec7a02</t>
+          <t>https://www.indeed.com/viewjob?jk=979402388d34b409</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Platform-DevOps Engineer</t>
+          <t>Senior Databricks AI Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>NXLog</t>
+          <t>Powerplan</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e7328772f0c8abe</t>
+          <t>https://www.indeed.com/viewjob?jk=3b5753d39b44c782</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Network IoT Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ELLKAY, LLC</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Elmwood Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, EMR, S3, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Streams/Tasks</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da29d3af250447a</t>
+          <t>https://www.indeed.com/viewjob?jk=c7bfd917914d4728</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Sr DevOPS Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT, MLflow</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fc978b16714d0d2</t>
+          <t>https://www.indeed.com/viewjob?jk=9886d247b0ec7a02</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Platform-DevOps Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>NXLog</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9649d08cb62a9ac0</t>
+          <t>https://www.indeed.com/viewjob?jk=6e7328772f0c8abe</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Network IoT Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Waters</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Milford, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1975adb5bfc7de33</t>
+          <t>https://www.indeed.com/viewjob?jk=0da29d3af250447a</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Santa Barbara, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52fbd92226aade92</t>
+          <t>https://www.indeed.com/viewjob?jk=7fc978b16714d0d2</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e77317858ff838d</t>
+          <t>https://www.indeed.com/viewjob?jk=9649d08cb62a9ac0</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>Waters</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Milford, MA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9737f288d965528f</t>
+          <t>https://www.indeed.com/viewjob?jk=1975adb5bfc7de33</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sr. Software Developer/Programmer</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>PEARLY</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Davis, CA, US USA</t>
+          <t>Santa Barbara, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, CI/CD, GitHub Actions, Docker, Kubernetes, SonarQube, Git</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ce420e446403a9d</t>
+          <t>https://www.indeed.com/viewjob?jk=52fbd92226aade92</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ABCorp NA Inc.</t>
+          <t>PEARLY</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d8f6d93b707b783</t>
+          <t>https://www.indeed.com/viewjob?jk=3e77317858ff838d</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>PEARLY</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7dfde3b442bd5c7</t>
+          <t>https://www.indeed.com/viewjob?jk=9737f288d965528f</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Sr. Software Developer/Programmer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Clarksville, TN, US USA</t>
+          <t>Davis, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Oracle, CI/CD, GitHub Actions, Docker, Kubernetes, SonarQube, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503ceed67966f48a</t>
+          <t>https://www.indeed.com/viewjob?jk=9ce420e446403a9d</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>ABCorp NA Inc.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, Kafka, Dimensional Modeling, ETL, Airflow</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503c92a0918e2779</t>
+          <t>https://www.indeed.com/viewjob?jk=5d8f6d93b707b783</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Engineering Java/Python</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dfc1c1ddf5b07e8</t>
+          <t>https://www.indeed.com/viewjob?jk=b7dfde3b442bd5c7</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Clarksville, TN, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab7b07d708701fa</t>
+          <t>https://www.indeed.com/viewjob?jk=503ceed67966f48a</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend) - Global Dining</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, Kafka, Dimensional Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f71d52efce43e2</t>
+          <t>https://www.indeed.com/viewjob?jk=503c92a0918e2779</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Software Engineer III - Data Engineering Java/Python</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=110f275787ec7bdb</t>
+          <t>https://www.indeed.com/viewjob?jk=6dfc1c1ddf5b07e8</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Governance</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Alter Domus</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Databricks, Unity Catalog, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d83b504ed46b0c</t>
+          <t>https://www.indeed.com/viewjob?jk=cab7b07d708701fa</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Platform</t>
+          <t>Software Engineer (Backend) - Global Dining</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Middesk</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Spark, Data Modeling, Terraform, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=514717df8eb087ca</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f71d52efce43e2</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Data, Autonomy</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, DynamoDB, CI/CD</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3560765ed8e488</t>
+          <t>https://www.indeed.com/viewjob?jk=110f275787ec7bdb</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Data Engineer - Data Governance</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Alter Domus</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
+          <t>AWS, Glue, S3, IAM, RDS, Databricks, Unity Catalog, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf4b62fe049b84e</t>
+          <t>https://www.indeed.com/viewjob?jk=c3d83b504ed46b0c</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>Middesk</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>AWS, Lambda, RDS, Azure, Spark, Data Modeling, Terraform, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ca41478bb936cd</t>
+          <t>https://www.indeed.com/viewjob?jk=514717df8eb087ca</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Risk Developer (Python/Azure)</t>
+          <t>Sr. Software Engineer, Data, Autonomy</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, MLflow, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7762d03304071b69</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3560765ed8e488</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>hatch IT</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, ETL, CI/CD, Terraform</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b260e746e7b9c233</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf4b62fe049b84e</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE)</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>hatch IT</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c08c735142c13e1b</t>
+          <t>https://www.indeed.com/viewjob?jk=57ca41478bb936cd</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>.NET Angular Reporting Developer</t>
+          <t>Senior Risk Developer (Python/Azure)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, Star Schema, ETL, Power BI, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21a948f0ac42414</t>
+          <t>https://www.indeed.com/viewjob?jk=7762d03304071b69</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>hatch IT</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2698e1f59bd5def7</t>
+          <t>https://www.indeed.com/viewjob?jk=b260e746e7b9c233</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
+          <t>Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>hatch IT</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>AWS, ECS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d0bc94cbe8822db</t>
+          <t>https://www.indeed.com/viewjob?jk=c08c735142c13e1b</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
+          <t>.NET Angular Reporting Developer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Paterson, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, Star Schema, ETL, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75f6d90e6b234f60</t>
+          <t>https://www.indeed.com/viewjob?jk=f21a948f0ac42414</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e53f9ddcb5f4c2b9</t>
+          <t>https://www.indeed.com/viewjob?jk=2698e1f59bd5def7</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,32 +4731,32 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44fb3987d11d1123</t>
+          <t>https://www.indeed.com/viewjob?jk=4d0bc94cbe8822db</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Data Engineer(61249-1)</t>
+          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Vytwo Technologies</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Prosper, TX, US USA</t>
+          <t>Paterson, NJ, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, Airflow</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,32 +4766,32 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5fdd13d31dd0aa1</t>
+          <t>https://www.indeed.com/viewjob?jk=75f6d90e6b234f60</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Entry-Level Data Engineer</t>
+          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,32 +4801,32 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd80dc2e6636141e</t>
+          <t>https://www.indeed.com/viewjob?jk=e53f9ddcb5f4c2b9</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b5cdc524b199967</t>
+          <t>https://www.indeed.com/viewjob?jk=44fb3987d11d1123</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer III</t>
+          <t>Senior Data Engineer(61249-1)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Kapitus</t>
+          <t>Vytwo Technologies</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Prosper, TX, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, Airflow</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31099f3a1c434171</t>
+          <t>https://www.indeed.com/viewjob?jk=b5fdd13d31dd0aa1</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Entry-Level Data Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fd50cad36943ce</t>
+          <t>https://www.indeed.com/viewjob?jk=dd80dc2e6636141e</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Azure Stack Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>AAON</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Data Modeling, ETL, Power BI, CI/CD, Docker</t>
+          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20dcbc83d5643838</t>
+          <t>https://www.indeed.com/viewjob?jk=8b5cdc524b199967</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Enterprise Data &amp; Analytics</t>
+          <t>DevSecOps Engineer III</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Kapitus</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,24 +4966,24 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, Databricks, Data Modeling, ELT, dbt</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b74ac1e46b3dfa89</t>
+          <t>https://www.indeed.com/viewjob?jk=31099f3a1c434171</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SSO Administrator</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
+          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b109c86f55c8c21f</t>
+          <t>https://www.indeed.com/viewjob?jk=29fd50cad36943ce</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>Azure Stack Data Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>AAON</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Data Modeling, ETL, Power BI, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=739e08afe4ba1176</t>
+          <t>https://www.indeed.com/viewjob?jk=20dcbc83d5643838</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Sr. Data Engineer, Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, Databricks, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=843b039e4e75f61f</t>
+          <t>https://www.indeed.com/viewjob?jk=b74ac1e46b3dfa89</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>SSO Administrator</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ead7f0da7c5db1</t>
+          <t>https://www.indeed.com/viewjob?jk=b109c86f55c8c21f</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae8a17a1c6f39e3</t>
+          <t>https://www.indeed.com/viewjob?jk=739e08afe4ba1176</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5c91aac0db662ae</t>
+          <t>https://www.indeed.com/viewjob?jk=843b039e4e75f61f</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=151fe9868f44f2f1</t>
+          <t>https://www.indeed.com/viewjob?jk=c1ead7f0da7c5db1</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>IT PROFESSIONAL-APPLICATIONS (Database Administrator) (HEC)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>City of Houston, TX</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c369e1e8241c9f</t>
+          <t>https://www.indeed.com/viewjob?jk=1ae8a17a1c6f39e3</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>DOCSIS Testing Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, NoSQL, ETL, ELT, Splunk, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e134c7566cf151c</t>
+          <t>https://www.indeed.com/viewjob?jk=e5c91aac0db662ae</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (FDE)</t>
+          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>ISHIR</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,17 +5316,122 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=151fe9868f44f2f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer (FDE)</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>ISHIR</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
           <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr">
+      <c r="F141" t="inlineStr">
         <is>
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr">
+      <c r="G141" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=15ecc0cd2b5a2111</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>IT PROFESSIONAL-APPLICATIONS (Database Administrator) (HEC)</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>City of Houston, TX</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1c369e1e8241c9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>DOCSIS Testing Engineer</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, Scala, NoSQL, ETL, ELT, Splunk, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0e134c7566cf151c</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-04.xlsx
+++ b/results/job_matches_2026-03-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G143"/>
+  <dimension ref="A1:G142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2953,17 +2953,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer, CDC</t>
+          <t>Cloud Identity Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>DRT Strategies, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Scala, ETL, Power BI, Tableau, CI/CD, Docker</t>
+          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a223a368864e5d1b</t>
+          <t>https://www.indeed.com/viewjob?jk=fdd1e41d5949d150</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Cloud Identity Architect</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ivo</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdd1e41d5949d150</t>
+          <t>https://www.indeed.com/viewjob?jk=8bc5aaef611937ad</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>System Integration Test Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ivo</t>
+          <t>BGIT India Private Limited</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Hudson, NH, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,77 +3041,77 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bc5aaef611937ad</t>
+          <t>https://www.indeed.com/viewjob?jk=426d1d0d6a93918c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>ETL Testing with Azure Databricks in Healthcare</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd0439895496e24</t>
+          <t>https://www.indeed.com/viewjob?jk=9af37a4075a8760f</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>System Integration Test Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BGIT India Private Limited</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hudson, NH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=426d1d0d6a93918c</t>
+          <t>https://www.indeed.com/viewjob?jk=662840de4364e997</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ETL Testing with Azure Databricks in Healthcare</t>
+          <t>Software Engineer II - Scala</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Scala, Oracle</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9af37a4075a8760f</t>
+          <t>https://www.indeed.com/viewjob?jk=d148fa8c6ae39fd8</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Data Platform Engineer-2</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=662840de4364e997</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f9103ddd4f544e</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer II - Scala</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d148fa8c6ae39fd8</t>
+          <t>https://www.indeed.com/viewjob?jk=75d602908669423e</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-2</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,17 +3251,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f9103ddd4f544e</t>
+          <t>https://www.indeed.com/viewjob?jk=10de5f0ca2f7673d</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d602908669423e</t>
+          <t>https://www.indeed.com/viewjob?jk=8e6750fd9ad4e72e</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10de5f0ca2f7673d</t>
+          <t>https://www.indeed.com/viewjob?jk=c45db6ac50eb5587</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6750fd9ad4e72e</t>
+          <t>https://www.indeed.com/viewjob?jk=d1c0f7e27e90a87e</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45db6ac50eb5587</t>
+          <t>https://www.indeed.com/viewjob?jk=a4dc81e5cd9b6b72</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1c0f7e27e90a87e</t>
+          <t>https://www.indeed.com/viewjob?jk=14fea47c1dbfabac</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4dc81e5cd9b6b72</t>
+          <t>https://www.indeed.com/viewjob?jk=02d7bcc2bd0697b0</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14fea47c1dbfabac</t>
+          <t>https://www.indeed.com/viewjob?jk=50e0ff85e5f89851</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>Senior Software Engineer II - AI/ML</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02d7bcc2bd0697b0</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0bc9a390582054</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>Risk Data AI/ML Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50e0ff85e5f89851</t>
+          <t>https://www.indeed.com/viewjob?jk=979402388d34b409</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - AI/ML</t>
+          <t>Senior Databricks AI Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>Powerplan</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0bc9a390582054</t>
+          <t>https://www.indeed.com/viewjob?jk=3b5753d39b44c782</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Risk Data AI/ML Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>ELLKAY, LLC</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Elmwood Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, EMR, S3, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Streams/Tasks</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=979402388d34b409</t>
+          <t>https://www.indeed.com/viewjob?jk=c7bfd917914d4728</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Databricks AI Engineer</t>
+          <t>Sr DevOPS Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Powerplan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5753d39b44c782</t>
+          <t>https://www.indeed.com/viewjob?jk=9886d247b0ec7a02</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Platform-DevOps Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ELLKAY, LLC</t>
+          <t>NXLog</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Elmwood Park, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Streams/Tasks</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7bfd917914d4728</t>
+          <t>https://www.indeed.com/viewjob?jk=6e7328772f0c8abe</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer</t>
+          <t>Network IoT Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9886d247b0ec7a02</t>
+          <t>https://www.indeed.com/viewjob?jk=0da29d3af250447a</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Platform-DevOps Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>NXLog</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e7328772f0c8abe</t>
+          <t>https://www.indeed.com/viewjob?jk=7fc978b16714d0d2</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Network IoT Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da29d3af250447a</t>
+          <t>https://www.indeed.com/viewjob?jk=9649d08cb62a9ac0</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Waters</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Milford, MA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fc978b16714d0d2</t>
+          <t>https://www.indeed.com/viewjob?jk=1975adb5bfc7de33</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>PEARLY</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Santa Barbara, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9649d08cb62a9ac0</t>
+          <t>https://www.indeed.com/viewjob?jk=52fbd92226aade92</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Waters</t>
+          <t>PEARLY</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Milford, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1975adb5bfc7de33</t>
+          <t>https://www.indeed.com/viewjob?jk=3e77317858ff838d</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Santa Barbara, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52fbd92226aade92</t>
+          <t>https://www.indeed.com/viewjob?jk=9737f288d965528f</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Sr. Software Developer/Programmer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Davis, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Scala, Oracle, CI/CD, GitHub Actions, Docker, Kubernetes, SonarQube, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e77317858ff838d</t>
+          <t>https://www.indeed.com/viewjob?jk=9ce420e446403a9d</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>ABCorp NA Inc.</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9737f288d965528f</t>
+          <t>https://www.indeed.com/viewjob?jk=5d8f6d93b707b783</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sr. Software Developer/Programmer</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Davis, CA, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, CI/CD, GitHub Actions, Docker, Kubernetes, SonarQube, Git</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ce420e446403a9d</t>
+          <t>https://www.indeed.com/viewjob?jk=b7dfde3b442bd5c7</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ABCorp NA Inc.</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Clarksville, TN, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d8f6d93b707b783</t>
+          <t>https://www.indeed.com/viewjob?jk=503ceed67966f48a</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>Rogue Community College</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7dfde3b442bd5c7</t>
+          <t>https://www.indeed.com/viewjob?jk=7f9335cc41b5edf2</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Clarksville, TN, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, Kafka, Dimensional Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503ceed67966f48a</t>
+          <t>https://www.indeed.com/viewjob?jk=503c92a0918e2779</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Software Engineer III - Data Engineering Java/Python</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, Kafka, Dimensional Modeling, ETL, Airflow</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503c92a0918e2779</t>
+          <t>https://www.indeed.com/viewjob?jk=6dfc1c1ddf5b07e8</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Engineering Java/Python</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dfc1c1ddf5b07e8</t>
+          <t>https://www.indeed.com/viewjob?jk=cab7b07d708701fa</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>Software Engineer (Backend) - Global Dining</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab7b07d708701fa</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f71d52efce43e2</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend) - Global Dining</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f71d52efce43e2</t>
+          <t>https://www.indeed.com/viewjob?jk=110f275787ec7bdb</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior Data Engineer - Data Governance</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Alter Domus</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Glue, S3, IAM, RDS, Databricks, Unity Catalog, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=110f275787ec7bdb</t>
+          <t>https://www.indeed.com/viewjob?jk=c3d83b504ed46b0c</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Governance</t>
+          <t>Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Alter Domus</t>
+          <t>Middesk</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Databricks, Unity Catalog, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, Spark, Data Modeling, Terraform, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d83b504ed46b0c</t>
+          <t>https://www.indeed.com/viewjob?jk=514717df8eb087ca</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Platform</t>
+          <t>Sr. Software Engineer, Data, Autonomy</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Middesk</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Spark, Data Modeling, Terraform, Kubernetes, Airflow, Git</t>
+          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=514717df8eb087ca</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3560765ed8e488</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Data, Autonomy</t>
+          <t>Senior Risk Developer (Python/Azure)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,17 +4441,17 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, DynamoDB, CI/CD</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3560765ed8e488</t>
+          <t>https://www.indeed.com/viewjob?jk=7762d03304071b69</t>
         </is>
       </c>
     </row>
@@ -4528,17 +4528,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Risk Developer (Python/Azure)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>hatch IT</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, MLflow, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,14 +4556,14 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7762d03304071b69</t>
+          <t>https://www.indeed.com/viewjob?jk=b260e746e7b9c233</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, ETL, CI/CD, Terraform</t>
+          <t>AWS, ECS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b260e746e7b9c233</t>
+          <t>https://www.indeed.com/viewjob?jk=c08c735142c13e1b</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE)</t>
+          <t>.NET Angular Reporting Developer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>hatch IT</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Datadog</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, Star Schema, ETL, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c08c735142c13e1b</t>
+          <t>https://www.indeed.com/viewjob?jk=f21a948f0ac42414</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>.NET Angular Reporting Developer</t>
+          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, Star Schema, ETL, Power BI, CI/CD, Azure DevOps</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21a948f0ac42414</t>
+          <t>https://www.indeed.com/viewjob?jk=2698e1f59bd5def7</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2698e1f59bd5def7</t>
+          <t>https://www.indeed.com/viewjob?jk=4d0bc94cbe8822db</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Paterson, NJ, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d0bc94cbe8822db</t>
+          <t>https://www.indeed.com/viewjob?jk=75f6d90e6b234f60</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Paterson, NJ, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75f6d90e6b234f60</t>
+          <t>https://www.indeed.com/viewjob?jk=e53f9ddcb5f4c2b9</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,32 +4801,32 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e53f9ddcb5f4c2b9</t>
+          <t>https://www.indeed.com/viewjob?jk=44fb3987d11d1123</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
+          <t>Senior Data Engineer(61249-1)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Vytwo Technologies</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Prosper, TX, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, Airflow</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44fb3987d11d1123</t>
+          <t>https://www.indeed.com/viewjob?jk=b5fdd13d31dd0aa1</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Data Engineer(61249-1)</t>
+          <t>Entry-Level Data Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Vytwo Technologies</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Prosper, TX, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5fdd13d31dd0aa1</t>
+          <t>https://www.indeed.com/viewjob?jk=dd80dc2e6636141e</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Entry-Level Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd80dc2e6636141e</t>
+          <t>https://www.indeed.com/viewjob?jk=8b5cdc524b199967</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevSecOps Engineer III</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>Kapitus</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b5cdc524b199967</t>
+          <t>https://www.indeed.com/viewjob?jk=31099f3a1c434171</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer III</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Kapitus</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31099f3a1c434171</t>
+          <t>https://www.indeed.com/viewjob?jk=29fd50cad36943ce</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Azure Stack Data Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AAON</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Data Modeling, ETL, Power BI, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fd50cad36943ce</t>
+          <t>https://www.indeed.com/viewjob?jk=20dcbc83d5643838</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Azure Stack Data Engineer</t>
+          <t>Sr. Data Engineer, Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>AAON</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Data Modeling, ETL, Power BI, CI/CD, Docker</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, Databricks, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20dcbc83d5643838</t>
+          <t>https://www.indeed.com/viewjob?jk=b74ac1e46b3dfa89</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Enterprise Data &amp; Analytics</t>
+          <t>Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>ISHIR</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,17 +5071,17 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, Databricks, Data Modeling, ELT, dbt</t>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b74ac1e46b3dfa89</t>
+          <t>https://www.indeed.com/viewjob?jk=15ecc0cd2b5a2111</t>
         </is>
       </c>
     </row>
@@ -5333,17 +5333,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (FDE)</t>
+          <t>IT PROFESSIONAL-APPLICATIONS (Database Administrator) (HEC)</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>ISHIR</t>
+          <t>City of Houston, TX</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,34 +5351,34 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ecc0cd2b5a2111</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c369e1e8241c9f</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>IT PROFESSIONAL-APPLICATIONS (Database Administrator) (HEC)</t>
+          <t>DOCSIS Testing Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>City of Houston, TX</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, NoSQL, ETL, ELT, Splunk, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5395,41 +5395,6 @@
         </is>
       </c>
       <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c369e1e8241c9f</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>DOCSIS Testing Engineer</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, NoSQL, ETL, ELT, Splunk, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=0e134c7566cf151c</t>
         </is>

--- a/results/job_matches_2026-03-04.xlsx
+++ b/results/job_matches_2026-03-04.xlsx
@@ -2328,7 +2328,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cc63cdd2328277c</t>
+          <t>https://www.indeed.com/viewjob?jk=9188fd233f524c42</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer, AI Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Residex, LLC</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b994e1736909aed</t>
+          <t>https://www.indeed.com/viewjob?jk=4cc63cdd2328277c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. Cloud Software Engineer</t>
+          <t>Software Engineer, AI Analytics</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ELLKAY, LLC</t>
+          <t>Residex, LLC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Elmwood Park, NJ, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28b63f4ef510667a</t>
+          <t>https://www.indeed.com/viewjob?jk=3b994e1736909aed</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Associate/Consultant Engineer - Remote</t>
+          <t>Sr. Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Rancho BioSciences</t>
+          <t>ELLKAY, LLC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Elmwood Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Athena, IAM, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72630d316687619c</t>
+          <t>https://www.indeed.com/viewjob?jk=28b63f4ef510667a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Associate/Consultant Engineer - Remote</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Rancho BioSciences</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b12dfc8a5459a4f</t>
+          <t>https://www.indeed.com/viewjob?jk=72630d316687619c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d49d017dead0cec</t>
+          <t>https://www.indeed.com/viewjob?jk=2b12dfc8a5459a4f</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,59 +2561,59 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b08c3dc1b325be49</t>
+          <t>https://www.indeed.com/viewjob?jk=7d49d017dead0cec</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf6f08ab2860bc5c</t>
+          <t>https://www.indeed.com/viewjob?jk=b08c3dc1b325be49</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer - Kafka Connect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CloudRay Inc</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, MySQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5df3111682f7946</t>
+          <t>https://www.indeed.com/viewjob?jk=bf6f08ab2860bc5c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>LMS Administrator</t>
+          <t>Data Engineer - Kafka Connect</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Blue Wing Technical</t>
+          <t>CloudRay Inc</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Decatur, GA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, S3, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ea5eba4ba63388f</t>
+          <t>https://www.indeed.com/viewjob?jk=d5df3111682f7946</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Associate/Consultant Engineer - Remote</t>
+          <t>LMS Administrator</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Rancho BioSciences</t>
+          <t>Blue Wing Technical</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Decatur, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd467efc7d909226</t>
+          <t>https://www.indeed.com/viewjob?jk=6ea5eba4ba63388f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer - Remote</t>
+          <t>Associate/Consultant Engineer - Remote</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Rancho BioSciences</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80460d4e824e28cc</t>
+          <t>https://www.indeed.com/viewjob?jk=cd467efc7d909226</t>
         </is>
       </c>
     </row>
@@ -2778,25 +2778,25 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer + Snowflake (On-Site)</t>
+          <t>Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e9f31119d31013</t>
+          <t>https://www.indeed.com/viewjob?jk=80460d4e824e28cc</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PDM Implementation Data Architect</t>
+          <t>Cloud Data Engineer + Snowflake (On-Site)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, RDS, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3576de9e88dd4c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=58e9f31119d31013</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>PDM Implementation Data Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a6c4ab9efc012e</t>
+          <t>https://www.indeed.com/viewjob?jk=3576de9e88dd4c5c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ROLLER</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb709659d664135</t>
+          <t>https://www.indeed.com/viewjob?jk=39a6c4ab9efc012e</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Google Cloud Network Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ROLLER</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,24 +2936,24 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c97eb9417ef8ebcf</t>
+          <t>https://www.indeed.com/viewjob?jk=afb709659d664135</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Cloud Identity Architect</t>
+          <t>Google Cloud Network Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdd1e41d5949d150</t>
+          <t>https://www.indeed.com/viewjob?jk=c97eb9417ef8ebcf</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Cloud Identity Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ivo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,17 +3006,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bc5aaef611937ad</t>
+          <t>https://www.indeed.com/viewjob?jk=fdd1e41d5949d150</t>
         </is>
       </c>
     </row>
@@ -3058,52 +3058,52 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ETL Testing with Azure Databricks in Healthcare</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>ivo</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Scala, Oracle</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9af37a4075a8760f</t>
+          <t>https://www.indeed.com/viewjob?jk=8bc5aaef611937ad</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>ETL Testing with Azure Databricks in Healthcare</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=662840de4364e997</t>
+          <t>https://www.indeed.com/viewjob?jk=9af37a4075a8760f</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer II - Scala</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d148fa8c6ae39fd8</t>
+          <t>https://www.indeed.com/viewjob?jk=662840de4364e997</t>
         </is>
       </c>
     </row>
@@ -3723,17 +3723,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Network IoT Engineer</t>
+          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,14 +3751,14 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da29d3af250447a</t>
+          <t>https://www.indeed.com/viewjob?jk=e1b9bbef981d9232</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Network IoT Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT, MLflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fc978b16714d0d2</t>
+          <t>https://www.indeed.com/viewjob?jk=0da29d3af250447a</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9649d08cb62a9ac0</t>
+          <t>https://www.indeed.com/viewjob?jk=7fc978b16714d0d2</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Waters</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Milford, MA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1975adb5bfc7de33</t>
+          <t>https://www.indeed.com/viewjob?jk=9649d08cb62a9ac0</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>Waters</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Santa Barbara, CA, US USA</t>
+          <t>Milford, MA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52fbd92226aade92</t>
+          <t>https://www.indeed.com/viewjob?jk=1975adb5bfc7de33</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Santa Barbara, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e77317858ff838d</t>
+          <t>https://www.indeed.com/viewjob?jk=52fbd92226aade92</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9737f288d965528f</t>
+          <t>https://www.indeed.com/viewjob?jk=3e77317858ff838d</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sr. Software Developer/Programmer</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>PEARLY</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Davis, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, CI/CD, GitHub Actions, Docker, Kubernetes, SonarQube, Git</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ce420e446403a9d</t>
+          <t>https://www.indeed.com/viewjob?jk=9737f288d965528f</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
+          <t>Sr. Software Developer/Programmer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ABCorp NA Inc.</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Davis, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Scala, Oracle, CI/CD, GitHub Actions, Docker, Kubernetes, SonarQube, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d8f6d93b707b783</t>
+          <t>https://www.indeed.com/viewjob?jk=9ce420e446403a9d</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>ABCorp NA Inc.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7dfde3b442bd5c7</t>
+          <t>https://www.indeed.com/viewjob?jk=5d8f6d93b707b783</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>Rogue Community College</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Clarksville, TN, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503ceed67966f48a</t>
+          <t>https://www.indeed.com/viewjob?jk=7f9335cc41b5edf2</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Rogue Community College</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Power BI</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f9335cc41b5edf2</t>
+          <t>https://www.indeed.com/viewjob?jk=b7dfde3b442bd5c7</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Clarksville, TN, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, Kafka, Dimensional Modeling, ETL, Airflow</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503c92a0918e2779</t>
+          <t>https://www.indeed.com/viewjob?jk=503ceed67966f48a</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Engineering Java/Python</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
+          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, Kafka, Dimensional Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dfc1c1ddf5b07e8</t>
+          <t>https://www.indeed.com/viewjob?jk=503c92a0918e2779</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>Software Engineer III - Data Engineering Java/Python</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab7b07d708701fa</t>
+          <t>https://www.indeed.com/viewjob?jk=6dfc1c1ddf5b07e8</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend) - Global Dining</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f71d52efce43e2</t>
+          <t>https://www.indeed.com/viewjob?jk=cab7b07d708701fa</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Software Engineer (Backend) - Global Dining</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=110f275787ec7bdb</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f71d52efce43e2</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Governance</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Alter Domus</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Databricks, Unity Catalog, Scala, ETL, ELT</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d83b504ed46b0c</t>
+          <t>https://www.indeed.com/viewjob?jk=110f275787ec7bdb</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Platform</t>
+          <t>Senior Data Engineer - Data Governance</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Middesk</t>
+          <t>Alter Domus</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Spark, Data Modeling, Terraform, Kubernetes, Airflow, Git</t>
+          <t>AWS, Glue, S3, IAM, RDS, Databricks, Unity Catalog, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=514717df8eb087ca</t>
+          <t>https://www.indeed.com/viewjob?jk=c3d83b504ed46b0c</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Data, Autonomy</t>
+          <t>Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Middesk</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, RDS, Azure, Spark, Data Modeling, Terraform, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3560765ed8e488</t>
+          <t>https://www.indeed.com/viewjob?jk=514717df8eb087ca</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Risk Developer (Python/Azure)</t>
+          <t>Sr. Software Engineer, Data, Autonomy</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, MLflow, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7762d03304071b69</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3560765ed8e488</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Risk Developer (Python/Azure)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf4b62fe049b84e</t>
+          <t>https://www.indeed.com/viewjob?jk=7762d03304071b69</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ca41478bb936cd</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf4b62fe049b84e</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>hatch IT</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, ETL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b260e746e7b9c233</t>
+          <t>https://www.indeed.com/viewjob?jk=57ca41478bb936cd</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE)</t>
+          <t>.NET Angular Reporting Developer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>hatch IT</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Datadog</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, Star Schema, ETL, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c08c735142c13e1b</t>
+          <t>https://www.indeed.com/viewjob?jk=f21a948f0ac42414</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>.NET Angular Reporting Developer</t>
+          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, Star Schema, ETL, Power BI, CI/CD, Azure DevOps</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21a948f0ac42414</t>
+          <t>https://www.indeed.com/viewjob?jk=2698e1f59bd5def7</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2698e1f59bd5def7</t>
+          <t>https://www.indeed.com/viewjob?jk=4d0bc94cbe8822db</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Paterson, NJ, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d0bc94cbe8822db</t>
+          <t>https://www.indeed.com/viewjob?jk=75f6d90e6b234f60</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Paterson, NJ, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75f6d90e6b234f60</t>
+          <t>https://www.indeed.com/viewjob?jk=e53f9ddcb5f4c2b9</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e53f9ddcb5f4c2b9</t>
+          <t>https://www.indeed.com/viewjob?jk=44fb3987d11d1123</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>hatch IT</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,32 +4801,32 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44fb3987d11d1123</t>
+          <t>https://www.indeed.com/viewjob?jk=b260e746e7b9c233</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Data Engineer(61249-1)</t>
+          <t>Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Vytwo Technologies</t>
+          <t>hatch IT</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Prosper, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, Airflow</t>
+          <t>AWS, ECS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5fdd13d31dd0aa1</t>
+          <t>https://www.indeed.com/viewjob?jk=c08c735142c13e1b</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Entry-Level Data Engineer</t>
+          <t>Senior Data Engineer(61249-1)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Vytwo Technologies</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Prosper, TX, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, Airflow</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd80dc2e6636141e</t>
+          <t>https://www.indeed.com/viewjob?jk=b5fdd13d31dd0aa1</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Entry-Level Data Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b5cdc524b199967</t>
+          <t>https://www.indeed.com/viewjob?jk=dd80dc2e6636141e</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Kapitus</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31099f3a1c434171</t>
+          <t>https://www.indeed.com/viewjob?jk=8b5cdc524b199967</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>DevSecOps Engineer III</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Kapitus</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fd50cad36943ce</t>
+          <t>https://www.indeed.com/viewjob?jk=31099f3a1c434171</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Azure Stack Data Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>AAON</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,17 +5001,17 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Data Modeling, ETL, Power BI, CI/CD, Docker</t>
+          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20dcbc83d5643838</t>
+          <t>https://www.indeed.com/viewjob?jk=29fd50cad36943ce</t>
         </is>
       </c>
     </row>
@@ -5158,17 +5158,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>IT PROFESSIONAL-APPLICATIONS (Database Administrator) (HEC)</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>City of Houston, TX</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=843b039e4e75f61f</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c369e1e8241c9f</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>DOCSIS Testing Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, NoSQL, ETL, ELT, Splunk, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,14 +5221,14 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ead7f0da7c5db1</t>
+          <t>https://www.indeed.com/viewjob?jk=0e134c7566cf151c</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,14 +5256,14 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae8a17a1c6f39e3</t>
+          <t>https://www.indeed.com/viewjob?jk=843b039e4e75f61f</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5c91aac0db662ae</t>
+          <t>https://www.indeed.com/viewjob?jk=c1ead7f0da7c5db1</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=151fe9868f44f2f1</t>
+          <t>https://www.indeed.com/viewjob?jk=1ae8a17a1c6f39e3</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>IT PROFESSIONAL-APPLICATIONS (Database Administrator) (HEC)</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>City of Houston, TX</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c369e1e8241c9f</t>
+          <t>https://www.indeed.com/viewjob?jk=e5c91aac0db662ae</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>DOCSIS Testing Engineer</t>
+          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, NoSQL, ETL, ELT, Splunk, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e134c7566cf151c</t>
+          <t>https://www.indeed.com/viewjob?jk=151fe9868f44f2f1</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-04.xlsx
+++ b/results/job_matches_2026-03-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G142"/>
+  <dimension ref="A1:G140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer/Python Developer</t>
+          <t>Full Stack Engineer (React + Node.js)-4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zifo</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3419a1d7b4acb559</t>
+          <t>https://www.indeed.com/viewjob?jk=e082e26fc29250a3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (React + Node.js)-4</t>
+          <t>Data Engineer/Python Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Zifo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e082e26fc29250a3</t>
+          <t>https://www.indeed.com/viewjob?jk=3419a1d7b4acb559</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer, Client Authentication</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Quilt</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>IAM, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d883fd388e687a</t>
+          <t>https://www.indeed.com/viewjob?jk=a908b362cb914674</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer - AI Practice Team</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>American Bureau of Shipping (ABS)</t>
+          <t>Quilt</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Azure, Data Factory, Databricks, Event Hubs, BigQuery</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,19 +776,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98e9bc7cd1938bfd</t>
+          <t>https://www.indeed.com/viewjob?jk=27d883fd388e687a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Data Engineer - AI Practice Team</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>American Bureau of Shipping (ABS)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Azure, Data Factory, Databricks, Event Hubs, BigQuery</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7167050c109be2d4</t>
+          <t>https://www.indeed.com/viewjob?jk=98e9bc7cd1938bfd</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=862a4a8989448fa0</t>
+          <t>https://www.indeed.com/viewjob?jk=7167050c109be2d4</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07e542bb4713fad0</t>
+          <t>https://www.indeed.com/viewjob?jk=862a4a8989448fa0</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c88dff775194e30</t>
+          <t>https://www.indeed.com/viewjob?jk=07e542bb4713fad0</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ced45fe117deb8</t>
+          <t>https://www.indeed.com/viewjob?jk=2c88dff775194e30</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc8e0c810b3e7cd</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ced45fe117deb8</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7791942c877daada</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc8e0c810b3e7cd</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6b39b9b56abc0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=7791942c877daada</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648774ee33ca3b76</t>
+          <t>https://www.indeed.com/viewjob?jk=b6b39b9b56abc0bd</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a93ca1ad887e17f0</t>
+          <t>https://www.indeed.com/viewjob?jk=648774ee33ca3b76</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d963e90dfb3fa4d6</t>
+          <t>https://www.indeed.com/viewjob?jk=a93ca1ad887e17f0</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783ac47e6d62e414</t>
+          <t>https://www.indeed.com/viewjob?jk=d963e90dfb3fa4d6</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e511c7108cd6e82d</t>
+          <t>https://www.indeed.com/viewjob?jk=783ac47e6d62e414</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a6a2ad30fc1236d</t>
+          <t>https://www.indeed.com/viewjob?jk=e511c7108cd6e82d</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2d42f6d55a07b48</t>
+          <t>https://www.indeed.com/viewjob?jk=2a6a2ad30fc1236d</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c423f392a018bf22</t>
+          <t>https://www.indeed.com/viewjob?jk=e2d42f6d55a07b48</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb49af32ea451f63</t>
+          <t>https://www.indeed.com/viewjob?jk=c423f392a018bf22</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7468c4fe6bdb23</t>
+          <t>https://www.indeed.com/viewjob?jk=cb49af32ea451f63</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a3485c3c6153843</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7468c4fe6bdb23</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef4166ba4aa9b5a3</t>
+          <t>https://www.indeed.com/viewjob?jk=3a3485c3c6153843</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91d6e4beb774dd25</t>
+          <t>https://www.indeed.com/viewjob?jk=ef4166ba4aa9b5a3</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcf2824745a050e</t>
+          <t>https://www.indeed.com/viewjob?jk=91d6e4beb774dd25</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b296145590b995</t>
+          <t>https://www.indeed.com/viewjob?jk=adcf2824745a050e</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c4169879098b22b</t>
+          <t>https://www.indeed.com/viewjob?jk=64b296145590b995</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44e1222f0eb14744</t>
+          <t>https://www.indeed.com/viewjob?jk=8c4169879098b22b</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37bd1a8719f0aafc</t>
+          <t>https://www.indeed.com/viewjob?jk=44e1222f0eb14744</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e151b2c0a32e2723</t>
+          <t>https://www.indeed.com/viewjob?jk=37bd1a8719f0aafc</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c07dcca1b609463e</t>
+          <t>https://www.indeed.com/viewjob?jk=e151b2c0a32e2723</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c721bd4ca7bdffe1</t>
+          <t>https://www.indeed.com/viewjob?jk=c07dcca1b609463e</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8e182c6058fd2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=c721bd4ca7bdffe1</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4997f8f92f05b9d2</t>
+          <t>https://www.indeed.com/viewjob?jk=e8e182c6058fd2a4</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a56481df82d7aa6</t>
+          <t>https://www.indeed.com/viewjob?jk=4997f8f92f05b9d2</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb00c80fb9cb9b65</t>
+          <t>https://www.indeed.com/viewjob?jk=2a56481df82d7aa6</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fd1863254c88e5d</t>
+          <t>https://www.indeed.com/viewjob?jk=fb00c80fb9cb9b65</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Infrastructure</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ALTRUIST</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2b2e3b90367f3b4</t>
+          <t>https://www.indeed.com/viewjob?jk=3fd1863254c88e5d</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15721c69bc524693</t>
+          <t>https://www.indeed.com/viewjob?jk=b2b2e3b90367f3b4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>ALTRUIST</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6c4839e7fe64d8e</t>
+          <t>https://www.indeed.com/viewjob?jk=15721c69bc524693</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Infrastructure</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ALTRUIST</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc6ad57eba624292</t>
+          <t>https://www.indeed.com/viewjob?jk=a6c4839e7fe64d8e</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15325ad687b27337</t>
+          <t>https://www.indeed.com/viewjob?jk=cc6ad57eba624292</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>ALTRUIST</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,59 +2176,59 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17c87f0de0ddb952</t>
+          <t>https://www.indeed.com/viewjob?jk=15325ad687b27337</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer II,</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4edb591674d441f</t>
+          <t>https://www.indeed.com/viewjob?jk=17c87f0de0ddb952</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer II,</t>
+          <t>Blockchain Java Backend Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28ab3491bb9f5589</t>
+          <t>https://www.indeed.com/viewjob?jk=e49019e3e57d794c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Blockchain Java Backend Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e49019e3e57d794c</t>
+          <t>https://www.indeed.com/viewjob?jk=0997a11d6aaf4e73</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer II,</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,52 +2306,52 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Redshift, ECS, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0997a11d6aaf4e73</t>
+          <t>https://www.indeed.com/viewjob?jk=b4edb591674d441f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II,</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Redshift, ECS, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9188fd233f524c42</t>
+          <t>https://www.indeed.com/viewjob?jk=28ab3491bb9f5589</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cc63cdd2328277c</t>
+          <t>https://www.indeed.com/viewjob?jk=9188fd233f524c42</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer, AI Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Residex, LLC</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b994e1736909aed</t>
+          <t>https://www.indeed.com/viewjob?jk=4cc63cdd2328277c</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. Cloud Software Engineer</t>
+          <t>Software Engineer, AI Analytics</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ELLKAY, LLC</t>
+          <t>Residex, LLC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Elmwood Park, NJ, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28b63f4ef510667a</t>
+          <t>https://www.indeed.com/viewjob?jk=3b994e1736909aed</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Associate/Consultant Engineer - Remote</t>
+          <t>Sr. Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Rancho BioSciences</t>
+          <t>ELLKAY, LLC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Elmwood Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Athena, IAM, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72630d316687619c</t>
+          <t>https://www.indeed.com/viewjob?jk=28b63f4ef510667a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Associate/Consultant Engineer - Remote</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Rancho BioSciences</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b12dfc8a5459a4f</t>
+          <t>https://www.indeed.com/viewjob?jk=72630d316687619c</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Engineer - DevOps/ DataOps</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, DataOps, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d49d017dead0cec</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ed15cfc823b0b7</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,67 +2596,67 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b08c3dc1b325be49</t>
+          <t>https://www.indeed.com/viewjob?jk=2b12dfc8a5459a4f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf6f08ab2860bc5c</t>
+          <t>https://www.indeed.com/viewjob?jk=b08c3dc1b325be49</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer - Kafka Connect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CloudRay Inc</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5df3111682f7946</t>
+          <t>https://www.indeed.com/viewjob?jk=7d49d017dead0cec</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>LMS Administrator</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Blue Wing Technical</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Decatur, GA, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ea5eba4ba63388f</t>
+          <t>https://www.indeed.com/viewjob?jk=bf6f08ab2860bc5c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Associate/Consultant Engineer - Remote</t>
+          <t>Data Engineer - Kafka Connect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Rancho BioSciences</t>
+          <t>CloudRay Inc</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, S3, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd467efc7d909226</t>
+          <t>https://www.indeed.com/viewjob?jk=d5df3111682f7946</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Incremental CRM - Data Developer 1</t>
+          <t>Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Databricks, Scala, SQL Server, ETL</t>
+          <t>AWS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c7931e975a12585</t>
+          <t>https://www.indeed.com/viewjob?jk=80460d4e824e28cc</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer - Remote</t>
+          <t>Associate/Consultant Engineer - Remote</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Rancho BioSciences</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80460d4e824e28cc</t>
+          <t>https://www.indeed.com/viewjob?jk=cd467efc7d909226</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer + Snowflake (On-Site)</t>
+          <t>Incremental CRM - Data Developer 1</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Databricks, Scala, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e9f31119d31013</t>
+          <t>https://www.indeed.com/viewjob?jk=3c7931e975a12585</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PDM Implementation Data Architect</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Spark, PySpark</t>
+          <t>AWS, Kinesis, IAM, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3576de9e88dd4c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=a021dbda97cc3405</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Cloud Data Engineer + Snowflake (On-Site)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
+          <t>AWS, Glue, EMR, RDS, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a6c4ab9efc012e</t>
+          <t>https://www.indeed.com/viewjob?jk=58e9f31119d31013</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ROLLER</t>
+          <t>Hitachi Digital Services</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb709659d664135</t>
+          <t>https://www.indeed.com/viewjob?jk=33510d4bb406c6e2</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Google Cloud Network Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ROLLER</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c97eb9417ef8ebcf</t>
+          <t>https://www.indeed.com/viewjob?jk=afb709659d664135</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Cloud Identity Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdd1e41d5949d150</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7ddc3760328a54</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>System Integration Test Engineer</t>
+          <t>Google Cloud Network Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BGIT India Private Limited</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hudson, NH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=426d1d0d6a93918c</t>
+          <t>https://www.indeed.com/viewjob?jk=c97eb9417ef8ebcf</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ivo</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,59 +3076,59 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bc5aaef611937ad</t>
+          <t>https://www.indeed.com/viewjob?jk=39a6c4ab9efc012e</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ETL Testing with Azure Databricks in Healthcare</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>ivo</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Scala, Oracle</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9af37a4075a8760f</t>
+          <t>https://www.indeed.com/viewjob?jk=8bc5aaef611937ad</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Cloud Identity Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3142,11 +3142,11 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT</t>
+          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,59 +3156,59 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=662840de4364e997</t>
+          <t>https://www.indeed.com/viewjob?jk=fdd1e41d5949d150</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-2</t>
+          <t>System Integration Test Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>BGIT India Private Limited</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Hudson, NH, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f9103ddd4f544e</t>
+          <t>https://www.indeed.com/viewjob?jk=426d1d0d6a93918c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Halo Creative &amp; Media LLP</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d602908669423e</t>
+          <t>https://www.indeed.com/viewjob?jk=371d6385735b0f59</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>Data Platform Engineer-2</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,17 +3251,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10de5f0ca2f7673d</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f9103ddd4f544e</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6750fd9ad4e72e</t>
+          <t>https://www.indeed.com/viewjob?jk=75d602908669423e</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45db6ac50eb5587</t>
+          <t>https://www.indeed.com/viewjob?jk=10de5f0ca2f7673d</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1c0f7e27e90a87e</t>
+          <t>https://www.indeed.com/viewjob?jk=8e6750fd9ad4e72e</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4dc81e5cd9b6b72</t>
+          <t>https://www.indeed.com/viewjob?jk=c45db6ac50eb5587</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14fea47c1dbfabac</t>
+          <t>https://www.indeed.com/viewjob?jk=d1c0f7e27e90a87e</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02d7bcc2bd0697b0</t>
+          <t>https://www.indeed.com/viewjob?jk=a4dc81e5cd9b6b72</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50e0ff85e5f89851</t>
+          <t>https://www.indeed.com/viewjob?jk=14fea47c1dbfabac</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - AI/ML</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0bc9a390582054</t>
+          <t>https://www.indeed.com/viewjob?jk=02d7bcc2bd0697b0</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Risk Data AI/ML Engineer</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=979402388d34b409</t>
+          <t>https://www.indeed.com/viewjob?jk=50e0ff85e5f89851</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Databricks AI Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Powerplan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5753d39b44c782</t>
+          <t>https://www.indeed.com/viewjob?jk=662840de4364e997</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer II - AI/ML</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ELLKAY, LLC</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Elmwood Park, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Streams/Tasks</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7bfd917914d4728</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0bc9a390582054</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>ELLKAY, LLC</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Elmwood Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, EMR, S3, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Streams/Tasks</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9886d247b0ec7a02</t>
+          <t>https://www.indeed.com/viewjob?jk=c7bfd917914d4728</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Platform-DevOps Engineer</t>
+          <t>Sr DevOPS Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>NXLog</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,67 +3716,67 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e7328772f0c8abe</t>
+          <t>https://www.indeed.com/viewjob?jk=9886d247b0ec7a02</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
+          <t>Risk Data AI/ML Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1b9bbef981d9232</t>
+          <t>https://www.indeed.com/viewjob?jk=979402388d34b409</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Network IoT Engineer</t>
+          <t>Senior Databricks AI Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Powerplan</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da29d3af250447a</t>
+          <t>https://www.indeed.com/viewjob?jk=3b5753d39b44c782</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>ETL Testing with Azure Databricks in Healthcare</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT, MLflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fc978b16714d0d2</t>
+          <t>https://www.indeed.com/viewjob?jk=9af37a4075a8760f</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9649d08cb62a9ac0</t>
+          <t>https://www.indeed.com/viewjob?jk=e1b9bbef981d9232</t>
         </is>
       </c>
     </row>
@@ -4003,17 +4003,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Sr. Software Developer/Programmer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Davis, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, CI/CD, GitHub Actions, Docker, Kubernetes, SonarQube, Git</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ce420e446403a9d</t>
+          <t>https://www.indeed.com/viewjob?jk=7fc978b16714d0d2</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ABCorp NA Inc.</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d8f6d93b707b783</t>
+          <t>https://www.indeed.com/viewjob?jk=b7dfde3b442bd5c7</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Rogue Community College</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Clarksville, TN, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Power BI</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f9335cc41b5edf2</t>
+          <t>https://www.indeed.com/viewjob?jk=503ceed67966f48a</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>ABCorp NA Inc.</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7dfde3b442bd5c7</t>
+          <t>https://www.indeed.com/viewjob?jk=5d8f6d93b707b783</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>Rogue Community College</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Clarksville, TN, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503ceed67966f48a</t>
+          <t>https://www.indeed.com/viewjob?jk=7f9335cc41b5edf2</t>
         </is>
       </c>
     </row>
@@ -4213,17 +4213,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Engineering Java/Python</t>
+          <t>Software Engineer (Backend) - Global Dining</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dfc1c1ddf5b07e8</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f71d52efce43e2</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,19 +4276,19 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab7b07d708701fa</t>
+          <t>https://www.indeed.com/viewjob?jk=110f275787ec7bdb</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend) - Global Dining</t>
+          <t>Senior Data Engineer - Data Governance</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Alter Domus</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, S3, IAM, RDS, Databricks, Unity Catalog, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f71d52efce43e2</t>
+          <t>https://www.indeed.com/viewjob?jk=c3d83b504ed46b0c</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Middesk</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, Spark, Data Modeling, Terraform, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=110f275787ec7bdb</t>
+          <t>https://www.indeed.com/viewjob?jk=514717df8eb087ca</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Governance</t>
+          <t>Software Engineer III - Data Engineering Java/Python</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Alter Domus</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Databricks, Unity Catalog, Scala, ETL, ELT</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d83b504ed46b0c</t>
+          <t>https://www.indeed.com/viewjob?jk=6dfc1c1ddf5b07e8</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Platform</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Middesk</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Spark, Data Modeling, Terraform, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=514717df8eb087ca</t>
+          <t>https://www.indeed.com/viewjob?jk=cab7b07d708701fa</t>
         </is>
       </c>
     </row>
@@ -4493,17 +4493,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>hatch IT</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf4b62fe049b84e</t>
+          <t>https://www.indeed.com/viewjob?jk=b260e746e7b9c233</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>hatch IT</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>AWS, ECS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ca41478bb936cd</t>
+          <t>https://www.indeed.com/viewjob?jk=c08c735142c13e1b</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>.NET Angular Reporting Developer</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, Star Schema, ETL, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21a948f0ac42414</t>
+          <t>https://www.indeed.com/viewjob?jk=57ca41478bb936cd</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2698e1f59bd5def7</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf4b62fe049b84e</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
+          <t>.NET Angular Reporting Developer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, Star Schema, ETL, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d0bc94cbe8822db</t>
+          <t>https://www.indeed.com/viewjob?jk=f21a948f0ac42414</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Paterson, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75f6d90e6b234f60</t>
+          <t>https://www.indeed.com/viewjob?jk=2698e1f59bd5def7</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e53f9ddcb5f4c2b9</t>
+          <t>https://www.indeed.com/viewjob?jk=4d0bc94cbe8822db</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Paterson, NJ, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44fb3987d11d1123</t>
+          <t>https://www.indeed.com/viewjob?jk=75f6d90e6b234f60</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>hatch IT</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, ETL, CI/CD, Terraform</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b260e746e7b9c233</t>
+          <t>https://www.indeed.com/viewjob?jk=e53f9ddcb5f4c2b9</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE)</t>
+          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>hatch IT</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Datadog</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c08c735142c13e1b</t>
+          <t>https://www.indeed.com/viewjob?jk=44fb3987d11d1123</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Data Engineer(61249-1)</t>
+          <t>Entry-Level Data Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Vytwo Technologies</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Prosper, TX, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5fdd13d31dd0aa1</t>
+          <t>https://www.indeed.com/viewjob?jk=dd80dc2e6636141e</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Entry-Level Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd80dc2e6636141e</t>
+          <t>https://www.indeed.com/viewjob?jk=8b5cdc524b199967</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevSecOps Engineer III</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>Kapitus</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b5cdc524b199967</t>
+          <t>https://www.indeed.com/viewjob?jk=31099f3a1c434171</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer III</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Kapitus</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31099f3a1c434171</t>
+          <t>https://www.indeed.com/viewjob?jk=29fd50cad36943ce</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Sr. Data Engineer, Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, Databricks, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fd50cad36943ce</t>
+          <t>https://www.indeed.com/viewjob?jk=b74ac1e46b3dfa89</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Enterprise Data &amp; Analytics</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, Databricks, Data Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b74ac1e46b3dfa89</t>
+          <t>https://www.indeed.com/viewjob?jk=843b039e4e75f61f</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (FDE)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>ISHIR</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ecc0cd2b5a2111</t>
+          <t>https://www.indeed.com/viewjob?jk=c1ead7f0da7c5db1</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SSO Administrator</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b109c86f55c8c21f</t>
+          <t>https://www.indeed.com/viewjob?jk=1ae8a17a1c6f39e3</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=739e08afe4ba1176</t>
+          <t>https://www.indeed.com/viewjob?jk=e5c91aac0db662ae</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>IT PROFESSIONAL-APPLICATIONS (Database Administrator) (HEC)</t>
+          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>City of Houston, TX</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c369e1e8241c9f</t>
+          <t>https://www.indeed.com/viewjob?jk=151fe9868f44f2f1</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>DOCSIS Testing Engineer</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, NoSQL, ETL, ELT, Splunk, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e134c7566cf151c</t>
+          <t>https://www.indeed.com/viewjob?jk=739e08afe4ba1176</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>SSO Administrator</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=843b039e4e75f61f</t>
+          <t>https://www.indeed.com/viewjob?jk=b109c86f55c8c21f</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>IT PROFESSIONAL-APPLICATIONS (Database Administrator) (HEC)</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>City of Houston, TX</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ead7f0da7c5db1</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c369e1e8241c9f</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>DOCSIS Testing Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, NoSQL, ETL, ELT, Splunk, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,77 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae8a17a1c6f39e3</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Senior Engineer - .NET</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e5c91aac0db662ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>CrowdStrike</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=151fe9868f44f2f1</t>
+          <t>https://www.indeed.com/viewjob?jk=0e134c7566cf151c</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-04.xlsx
+++ b/results/job_matches_2026-03-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G140"/>
+  <dimension ref="A1:G138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (React + Node.js)-4</t>
+          <t>Data Engineer/Python Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Zifo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e082e26fc29250a3</t>
+          <t>https://www.indeed.com/viewjob?jk=3419a1d7b4acb559</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer/Python Developer</t>
+          <t>Full Stack Engineer (React + Node.js)-4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Zifo</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3419a1d7b4acb559</t>
+          <t>https://www.indeed.com/viewjob?jk=e082e26fc29250a3</t>
         </is>
       </c>
     </row>
@@ -2218,17 +2218,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Blockchain Java Backend Engineer</t>
+          <t>Software Engineer II,</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Redshift, ECS, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e49019e3e57d794c</t>
+          <t>https://www.indeed.com/viewjob?jk=b4edb591674d441f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer II,</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Redshift, ECS, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0997a11d6aaf4e73</t>
+          <t>https://www.indeed.com/viewjob?jk=28ab3491bb9f5589</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer II,</t>
+          <t>Blockchain Java Backend Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4edb591674d441f</t>
+          <t>https://www.indeed.com/viewjob?jk=e49019e3e57d794c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer II,</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,17 +2341,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28ab3491bb9f5589</t>
+          <t>https://www.indeed.com/viewjob?jk=0997a11d6aaf4e73</t>
         </is>
       </c>
     </row>
@@ -2603,17 +2603,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b08c3dc1b325be49</t>
+          <t>https://www.indeed.com/viewjob?jk=7d49d017dead0cec</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d49d017dead0cec</t>
+          <t>https://www.indeed.com/viewjob?jk=b08c3dc1b325be49</t>
         </is>
       </c>
     </row>
@@ -2743,17 +2743,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer - Remote</t>
+          <t>Associate/Consultant Engineer - Remote</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Rancho BioSciences</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80460d4e824e28cc</t>
+          <t>https://www.indeed.com/viewjob?jk=cd467efc7d909226</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Associate/Consultant Engineer - Remote</t>
+          <t>Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Rancho BioSciences</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd467efc7d909226</t>
+          <t>https://www.indeed.com/viewjob?jk=80460d4e824e28cc</t>
         </is>
       </c>
     </row>
@@ -2883,17 +2883,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer + Snowflake (On-Site)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e9f31119d31013</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7ddc3760328a54</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Data Engineer + Snowflake (On-Site)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Hitachi Digital Services</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, RDS, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33510d4bb406c6e2</t>
+          <t>https://www.indeed.com/viewjob?jk=58e9f31119d31013</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>PDM Implementation Data Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ROLLER</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,17 +2971,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb709659d664135</t>
+          <t>https://www.indeed.com/viewjob?jk=3576de9e88dd4c5c</t>
         </is>
       </c>
     </row>
@@ -2993,7 +2993,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3011,29 +3011,29 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7ddc3760328a54</t>
+          <t>https://www.indeed.com/viewjob?jk=39a6c4ab9efc012e</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Google Cloud Network Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Hitachi Digital Services</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c97eb9417ef8ebcf</t>
+          <t>https://www.indeed.com/viewjob?jk=33510d4bb406c6e2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>ROLLER</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a6c4ab9efc012e</t>
+          <t>https://www.indeed.com/viewjob?jk=afb709659d664135</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Cloud Identity Architect</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ivo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bc5aaef611937ad</t>
+          <t>https://www.indeed.com/viewjob?jk=fdd1e41d5949d150</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Cloud Identity Architect</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ivo</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,17 +3146,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdd1e41d5949d150</t>
+          <t>https://www.indeed.com/viewjob?jk=8bc5aaef611937ad</t>
         </is>
       </c>
     </row>
@@ -3233,17 +3233,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-2</t>
+          <t>ETL Testing with Azure Databricks in Healthcare</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f9103ddd4f544e</t>
+          <t>https://www.indeed.com/viewjob?jk=9af37a4075a8760f</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>Data Platform Engineer-2</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,17 +3286,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d602908669423e</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f9103ddd4f544e</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10de5f0ca2f7673d</t>
+          <t>https://www.indeed.com/viewjob?jk=75d602908669423e</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6750fd9ad4e72e</t>
+          <t>https://www.indeed.com/viewjob?jk=10de5f0ca2f7673d</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45db6ac50eb5587</t>
+          <t>https://www.indeed.com/viewjob?jk=8e6750fd9ad4e72e</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1c0f7e27e90a87e</t>
+          <t>https://www.indeed.com/viewjob?jk=c45db6ac50eb5587</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4dc81e5cd9b6b72</t>
+          <t>https://www.indeed.com/viewjob?jk=d1c0f7e27e90a87e</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14fea47c1dbfabac</t>
+          <t>https://www.indeed.com/viewjob?jk=a4dc81e5cd9b6b72</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02d7bcc2bd0697b0</t>
+          <t>https://www.indeed.com/viewjob?jk=14fea47c1dbfabac</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50e0ff85e5f89851</t>
+          <t>https://www.indeed.com/viewjob?jk=02d7bcc2bd0697b0</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=662840de4364e997</t>
+          <t>https://www.indeed.com/viewjob?jk=50e0ff85e5f89851</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - AI/ML</t>
+          <t>Risk Data AI/ML Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0bc9a390582054</t>
+          <t>https://www.indeed.com/viewjob?jk=979402388d34b409</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer II - AI/ML</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ELLKAY, LLC</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Elmwood Park, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Streams/Tasks</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7bfd917914d4728</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0bc9a390582054</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer</t>
+          <t>Senior Databricks AI Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Powerplan</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9886d247b0ec7a02</t>
+          <t>https://www.indeed.com/viewjob?jk=3b5753d39b44c782</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Risk Data AI/ML Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>ELLKAY, LLC</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Elmwood Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, EMR, S3, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Streams/Tasks</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=979402388d34b409</t>
+          <t>https://www.indeed.com/viewjob?jk=c7bfd917914d4728</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Databricks AI Engineer</t>
+          <t>Sr DevOPS Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Powerplan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5753d39b44c782</t>
+          <t>https://www.indeed.com/viewjob?jk=9886d247b0ec7a02</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ETL Testing with Azure Databricks in Healthcare</t>
+          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Scala, Oracle</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9af37a4075a8760f</t>
+          <t>https://www.indeed.com/viewjob?jk=e1b9bbef981d9232</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
+          <t>Network IoT Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1b9bbef981d9232</t>
+          <t>https://www.indeed.com/viewjob?jk=0da29d3af250447a</t>
         </is>
       </c>
     </row>
@@ -4003,17 +4003,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Senior Software Engineer (Backend)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PlanHub</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT, MLflow</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, Scala, MySQL, DynamoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fc978b16714d0d2</t>
+          <t>https://www.indeed.com/viewjob?jk=b63efe5dfc4a026c</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>ABCorp NA Inc.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7dfde3b442bd5c7</t>
+          <t>https://www.indeed.com/viewjob?jk=5d8f6d93b707b783</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>Rogue Community College</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Clarksville, TN, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503ceed67966f48a</t>
+          <t>https://www.indeed.com/viewjob?jk=7f9335cc41b5edf2</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ABCorp NA Inc.</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, Kafka, Dimensional Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d8f6d93b707b783</t>
+          <t>https://www.indeed.com/viewjob?jk=503c92a0918e2779</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Software Engineer III - Data Engineering Java/Python</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Rogue Community College</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Power BI</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f9335cc41b5edf2</t>
+          <t>https://www.indeed.com/viewjob?jk=6dfc1c1ddf5b07e8</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, Kafka, Dimensional Modeling, ETL, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503c92a0918e2779</t>
+          <t>https://www.indeed.com/viewjob?jk=cab7b07d708701fa</t>
         </is>
       </c>
     </row>
@@ -4353,17 +4353,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Engineering Java/Python</t>
+          <t>Sr. Software Engineer, Data, Autonomy</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dfc1c1ddf5b07e8</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3560765ed8e488</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>Senior Risk Developer (Python/Azure)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab7b07d708701fa</t>
+          <t>https://www.indeed.com/viewjob?jk=7762d03304071b69</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Data, Autonomy</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3560765ed8e488</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf4b62fe049b84e</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Risk Developer (Python/Azure)</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7762d03304071b69</t>
+          <t>https://www.indeed.com/viewjob?jk=57ca41478bb936cd</t>
         </is>
       </c>
     </row>
@@ -4563,17 +4563,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>.NET Angular Reporting Developer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, Star Schema, ETL, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ca41478bb936cd</t>
+          <t>https://www.indeed.com/viewjob?jk=f21a948f0ac42414</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf4b62fe049b84e</t>
+          <t>https://www.indeed.com/viewjob?jk=2698e1f59bd5def7</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>.NET Angular Reporting Developer</t>
+          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, Star Schema, ETL, Power BI, CI/CD, Azure DevOps</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21a948f0ac42414</t>
+          <t>https://www.indeed.com/viewjob?jk=4d0bc94cbe8822db</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Paterson, NJ, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2698e1f59bd5def7</t>
+          <t>https://www.indeed.com/viewjob?jk=75f6d90e6b234f60</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d0bc94cbe8822db</t>
+          <t>https://www.indeed.com/viewjob?jk=e53f9ddcb5f4c2b9</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Paterson, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,32 +4766,32 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75f6d90e6b234f60</t>
+          <t>https://www.indeed.com/viewjob?jk=44fb3987d11d1123</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
+          <t>Entry-Level Data Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,32 +4801,32 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e53f9ddcb5f4c2b9</t>
+          <t>https://www.indeed.com/viewjob?jk=dd80dc2e6636141e</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44fb3987d11d1123</t>
+          <t>https://www.indeed.com/viewjob?jk=8b5cdc524b199967</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Entry-Level Data Engineer</t>
+          <t>DevSecOps Engineer III</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Kapitus</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd80dc2e6636141e</t>
+          <t>https://www.indeed.com/viewjob?jk=31099f3a1c434171</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer, Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, Databricks, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b5cdc524b199967</t>
+          <t>https://www.indeed.com/viewjob?jk=b74ac1e46b3dfa89</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer III</t>
+          <t>Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Kapitus</t>
+          <t>ISHIR</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,24 +4931,24 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31099f3a1c434171</t>
+          <t>https://www.indeed.com/viewjob?jk=15ecc0cd2b5a2111</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>SSO Administrator</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fd50cad36943ce</t>
+          <t>https://www.indeed.com/viewjob?jk=b109c86f55c8c21f</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Enterprise Data &amp; Analytics</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,17 +5001,17 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, Databricks, Data Modeling, ELT, dbt</t>
+          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b74ac1e46b3dfa89</t>
+          <t>https://www.indeed.com/viewjob?jk=739e08afe4ba1176</t>
         </is>
       </c>
     </row>
@@ -5193,17 +5193,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>IT PROFESSIONAL-APPLICATIONS (Database Administrator) (HEC)</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>City of Houston, TX</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,14 +5221,14 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=739e08afe4ba1176</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c369e1e8241c9f</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>SSO Administrator</t>
+          <t>DOCSIS Testing Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, NoSQL, ETL, ELT, Splunk, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5255,76 +5255,6 @@
         </is>
       </c>
       <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b109c86f55c8c21f</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>IT PROFESSIONAL-APPLICATIONS (Database Administrator) (HEC)</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>City of Houston, TX</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c369e1e8241c9f</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>DOCSIS Testing Engineer</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, NoSQL, ETL, ELT, Splunk, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=0e134c7566cf151c</t>
         </is>

--- a/results/job_matches_2026-03-04.xlsx
+++ b/results/job_matches_2026-03-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G138"/>
+  <dimension ref="A1:G142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer II (Hybrid Work Schedule)</t>
+          <t>Software Engineer in Test III - Data Analytics</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Quorum Business Solutions</t>
+          <t>Emburse</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.9</v>
+        <v>21.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,59 +531,59 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f1e509811f28e16</t>
+          <t>https://www.indeed.com/viewjob?jk=450782bf82b6fc2f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer in Test III - Data Analytics</t>
+          <t>Junior Oracle Apps Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Emburse</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21.5</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, ECS, RDS, Azure, Blob Storage</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=450782bf82b6fc2f</t>
+          <t>https://www.indeed.com/viewjob?jk=0adde35786282b2b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Data Engineer/Python Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Altak Group</t>
+          <t>Zifo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,34 +591,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Azure</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afe6c49fa2525821</t>
+          <t>https://www.indeed.com/viewjob?jk=3419a1d7b4acb559</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer/Python Developer</t>
+          <t>Full Stack Engineer (React + Node.js)-4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zifo</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3419a1d7b4acb559</t>
+          <t>https://www.indeed.com/viewjob?jk=e082e26fc29250a3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (React + Node.js)-4</t>
+          <t>Software Engineer III: DevOps</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e082e26fc29250a3</t>
+          <t>https://www.indeed.com/viewjob?jk=bc952e4224a3aa24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer III: DevOps</t>
+          <t>Senior Data Engineer, Client Authentication</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP, Scala</t>
+          <t>IAM, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc952e4224a3aa24</t>
+          <t>https://www.indeed.com/viewjob?jk=a908b362cb914674</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Client Authentication</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Quilt</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a908b362cb914674</t>
+          <t>https://www.indeed.com/viewjob?jk=27d883fd388e687a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - AI Practice Team</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Quilt</t>
+          <t>American Bureau of Shipping (ABS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Azure, Data Factory, Databricks, Event Hubs, BigQuery</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,19 +776,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d883fd388e687a</t>
+          <t>https://www.indeed.com/viewjob?jk=98e9bc7cd1938bfd</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer - AI Practice Team</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>American Bureau of Shipping (ABS)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Azure, Data Factory, Databricks, Event Hubs, BigQuery</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98e9bc7cd1938bfd</t>
+          <t>https://www.indeed.com/viewjob?jk=7167050c109be2d4</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7167050c109be2d4</t>
+          <t>https://www.indeed.com/viewjob?jk=862a4a8989448fa0</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=862a4a8989448fa0</t>
+          <t>https://www.indeed.com/viewjob?jk=07e542bb4713fad0</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07e542bb4713fad0</t>
+          <t>https://www.indeed.com/viewjob?jk=2c88dff775194e30</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c88dff775194e30</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ced45fe117deb8</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ced45fe117deb8</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc8e0c810b3e7cd</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc8e0c810b3e7cd</t>
+          <t>https://www.indeed.com/viewjob?jk=7791942c877daada</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7791942c877daada</t>
+          <t>https://www.indeed.com/viewjob?jk=b6b39b9b56abc0bd</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6b39b9b56abc0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=648774ee33ca3b76</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648774ee33ca3b76</t>
+          <t>https://www.indeed.com/viewjob?jk=a93ca1ad887e17f0</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a93ca1ad887e17f0</t>
+          <t>https://www.indeed.com/viewjob?jk=d963e90dfb3fa4d6</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d963e90dfb3fa4d6</t>
+          <t>https://www.indeed.com/viewjob?jk=783ac47e6d62e414</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783ac47e6d62e414</t>
+          <t>https://www.indeed.com/viewjob?jk=e511c7108cd6e82d</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e511c7108cd6e82d</t>
+          <t>https://www.indeed.com/viewjob?jk=2a6a2ad30fc1236d</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a6a2ad30fc1236d</t>
+          <t>https://www.indeed.com/viewjob?jk=e2d42f6d55a07b48</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2d42f6d55a07b48</t>
+          <t>https://www.indeed.com/viewjob?jk=c423f392a018bf22</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c423f392a018bf22</t>
+          <t>https://www.indeed.com/viewjob?jk=cb49af32ea451f63</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb49af32ea451f63</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7468c4fe6bdb23</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7468c4fe6bdb23</t>
+          <t>https://www.indeed.com/viewjob?jk=3a3485c3c6153843</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a3485c3c6153843</t>
+          <t>https://www.indeed.com/viewjob?jk=ef4166ba4aa9b5a3</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef4166ba4aa9b5a3</t>
+          <t>https://www.indeed.com/viewjob?jk=91d6e4beb774dd25</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91d6e4beb774dd25</t>
+          <t>https://www.indeed.com/viewjob?jk=adcf2824745a050e</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcf2824745a050e</t>
+          <t>https://www.indeed.com/viewjob?jk=64b296145590b995</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b296145590b995</t>
+          <t>https://www.indeed.com/viewjob?jk=8c4169879098b22b</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c4169879098b22b</t>
+          <t>https://www.indeed.com/viewjob?jk=44e1222f0eb14744</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44e1222f0eb14744</t>
+          <t>https://www.indeed.com/viewjob?jk=37bd1a8719f0aafc</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37bd1a8719f0aafc</t>
+          <t>https://www.indeed.com/viewjob?jk=e151b2c0a32e2723</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e151b2c0a32e2723</t>
+          <t>https://www.indeed.com/viewjob?jk=c07dcca1b609463e</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c07dcca1b609463e</t>
+          <t>https://www.indeed.com/viewjob?jk=c721bd4ca7bdffe1</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c721bd4ca7bdffe1</t>
+          <t>https://www.indeed.com/viewjob?jk=e8e182c6058fd2a4</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8e182c6058fd2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=4997f8f92f05b9d2</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4997f8f92f05b9d2</t>
+          <t>https://www.indeed.com/viewjob?jk=2a56481df82d7aa6</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a56481df82d7aa6</t>
+          <t>https://www.indeed.com/viewjob?jk=fb00c80fb9cb9b65</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb00c80fb9cb9b65</t>
+          <t>https://www.indeed.com/viewjob?jk=3fd1863254c88e5d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Senior Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ALTRUIST</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fd1863254c88e5d</t>
+          <t>https://www.indeed.com/viewjob?jk=b2b2e3b90367f3b4</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2b2e3b90367f3b4</t>
+          <t>https://www.indeed.com/viewjob?jk=15721c69bc524693</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Infrastructure</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ALTRUIST</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15721c69bc524693</t>
+          <t>https://www.indeed.com/viewjob?jk=a6c4839e7fe64d8e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>ALTRUIST</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6c4839e7fe64d8e</t>
+          <t>https://www.indeed.com/viewjob?jk=cc6ad57eba624292</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc6ad57eba624292</t>
+          <t>https://www.indeed.com/viewjob?jk=15325ad687b27337</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Infrastructure</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ALTRUIST</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,42 +2176,42 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15325ad687b27337</t>
+          <t>https://www.indeed.com/viewjob?jk=17c87f0de0ddb952</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II,</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark</t>
+          <t>AWS, Redshift, ECS, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17c87f0de0ddb952</t>
+          <t>https://www.indeed.com/viewjob?jk=b4edb591674d441f</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4edb591674d441f</t>
+          <t>https://www.indeed.com/viewjob?jk=28ab3491bb9f5589</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer II,</t>
+          <t>Blockchain Java Backend Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28ab3491bb9f5589</t>
+          <t>https://www.indeed.com/viewjob?jk=e49019e3e57d794c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Blockchain Java Backend Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e49019e3e57d794c</t>
+          <t>https://www.indeed.com/viewjob?jk=0997a11d6aaf4e73</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0997a11d6aaf4e73</t>
+          <t>https://www.indeed.com/viewjob?jk=9188fd233f524c42</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9188fd233f524c42</t>
+          <t>https://www.indeed.com/viewjob?jk=4cc63cdd2328277c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer, AI Analytics</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Residex, LLC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cc63cdd2328277c</t>
+          <t>https://www.indeed.com/viewjob?jk=3b994e1736909aed</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer, AI Analytics</t>
+          <t>Sr. Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Residex, LLC</t>
+          <t>ELLKAY, LLC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Elmwood Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Athena, IAM, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b994e1736909aed</t>
+          <t>https://www.indeed.com/viewjob?jk=28b63f4ef510667a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Cloud Software Engineer</t>
+          <t>Associate/Consultant Engineer - Remote</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ELLKAY, LLC</t>
+          <t>Rancho BioSciences</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Elmwood Park, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,59 +2491,59 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28b63f4ef510667a</t>
+          <t>https://www.indeed.com/viewjob?jk=72630d316687619c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Associate/Consultant Engineer - Remote</t>
+          <t>Senior Engineer - DevOps/ DataOps</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Rancho BioSciences</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, DataOps, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72630d316687619c</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ed15cfc823b0b7</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Engineer - DevOps/ DataOps</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, DataOps, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ed15cfc823b0b7</t>
+          <t>https://www.indeed.com/viewjob?jk=2b12dfc8a5459a4f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b12dfc8a5459a4f</t>
+          <t>https://www.indeed.com/viewjob?jk=7d49d017dead0cec</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,59 +2631,59 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d49d017dead0cec</t>
+          <t>https://www.indeed.com/viewjob?jk=b08c3dc1b325be49</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b08c3dc1b325be49</t>
+          <t>https://www.indeed.com/viewjob?jk=bf6f08ab2860bc5c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Incremental CRM - Data Developer 1</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Databricks, Scala, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf6f08ab2860bc5c</t>
+          <t>https://www.indeed.com/viewjob?jk=3c7931e975a12585</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer - Kafka Connect</t>
+          <t>Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CloudRay Inc</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,102 +2736,102 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5df3111682f7946</t>
+          <t>https://www.indeed.com/viewjob?jk=80460d4e824e28cc</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Associate/Consultant Engineer - Remote</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Rancho BioSciences</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Kinesis, IAM, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd467efc7d909226</t>
+          <t>https://www.indeed.com/viewjob?jk=a021dbda97cc3405</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer - Remote</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80460d4e824e28cc</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7ddc3760328a54</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Incremental CRM - Data Developer 1</t>
+          <t>Cloud Data Engineer + Snowflake (On-Site)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Databricks, Scala, SQL Server, ETL</t>
+          <t>AWS, Glue, EMR, RDS, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c7931e975a12585</t>
+          <t>https://www.indeed.com/viewjob?jk=58e9f31119d31013</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>PDM Implementation Data Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,17 +2866,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a021dbda97cc3405</t>
+          <t>https://www.indeed.com/viewjob?jk=3576de9e88dd4c5c</t>
         </is>
       </c>
     </row>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2906,29 +2906,29 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7ddc3760328a54</t>
+          <t>https://www.indeed.com/viewjob?jk=39a6c4ab9efc012e</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer + Snowflake (On-Site)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Hitachi Digital Services</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e9f31119d31013</t>
+          <t>https://www.indeed.com/viewjob?jk=33510d4bb406c6e2</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PDM Implementation Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>ROLLER</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Spark, PySpark</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3576de9e88dd4c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=afb709659d664135</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>SQL Server Database Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>IDBNY</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
+          <t>AWS, S3, RDS, Azure, Databricks, HBase, Snowflake, Oracle, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a6c4ab9efc012e</t>
+          <t>https://www.indeed.com/viewjob?jk=15c2f3c4f1ddf6ac</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Identity Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Hitachi Digital Services</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala</t>
+          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33510d4bb406c6e2</t>
+          <t>https://www.indeed.com/viewjob?jk=fdd1e41d5949d150</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>System Integration Test Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ROLLER</t>
+          <t>BGIT India Private Limited</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Hudson, NH, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb709659d664135</t>
+          <t>https://www.indeed.com/viewjob?jk=426d1d0d6a93918c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cloud Identity Architect</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ivo</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,42 +3111,42 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdd1e41d5949d150</t>
+          <t>https://www.indeed.com/viewjob?jk=8bc5aaef611937ad</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ivo</t>
+          <t>Halo Creative &amp; Media LLP</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,59 +3156,59 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bc5aaef611937ad</t>
+          <t>https://www.indeed.com/viewjob?jk=371d6385735b0f59</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>System Integration Test Engineer</t>
+          <t>Data Platform Engineer-2</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BGIT India Private Limited</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hudson, NH, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=426d1d0d6a93918c</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f9103ddd4f544e</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Halo Creative &amp; Media LLP</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371d6385735b0f59</t>
+          <t>https://www.indeed.com/viewjob?jk=75d602908669423e</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ETL Testing with Azure Databricks in Healthcare</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Scala, Oracle</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9af37a4075a8760f</t>
+          <t>https://www.indeed.com/viewjob?jk=10de5f0ca2f7673d</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-2</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,17 +3286,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f9103ddd4f544e</t>
+          <t>https://www.indeed.com/viewjob?jk=8e6750fd9ad4e72e</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d602908669423e</t>
+          <t>https://www.indeed.com/viewjob?jk=c45db6ac50eb5587</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10de5f0ca2f7673d</t>
+          <t>https://www.indeed.com/viewjob?jk=d1c0f7e27e90a87e</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6750fd9ad4e72e</t>
+          <t>https://www.indeed.com/viewjob?jk=a4dc81e5cd9b6b72</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45db6ac50eb5587</t>
+          <t>https://www.indeed.com/viewjob?jk=14fea47c1dbfabac</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1c0f7e27e90a87e</t>
+          <t>https://www.indeed.com/viewjob?jk=02d7bcc2bd0697b0</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4dc81e5cd9b6b72</t>
+          <t>https://www.indeed.com/viewjob?jk=50e0ff85e5f89851</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>UP Management LLC</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bedford, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14fea47c1dbfabac</t>
+          <t>https://www.indeed.com/viewjob?jk=2e000e4c87bc0a4b</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>Risk Data AI/ML Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02d7bcc2bd0697b0</t>
+          <t>https://www.indeed.com/viewjob?jk=979402388d34b409</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>Senior Software Engineer II - AI/ML</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50e0ff85e5f89851</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0bc9a390582054</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Risk Data AI/ML Engineer</t>
+          <t>Senior Databricks AI Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Powerplan</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=979402388d34b409</t>
+          <t>https://www.indeed.com/viewjob?jk=3b5753d39b44c782</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - AI/ML</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>ELLKAY, LLC</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Elmwood Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, EMR, S3, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Streams/Tasks</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0bc9a390582054</t>
+          <t>https://www.indeed.com/viewjob?jk=c7bfd917914d4728</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Databricks AI Engineer</t>
+          <t>Sr DevOPS Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Powerplan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5753d39b44c782</t>
+          <t>https://www.indeed.com/viewjob?jk=9886d247b0ec7a02</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ELLKAY, LLC</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Elmwood Park, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Streams/Tasks</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7bfd917914d4728</t>
+          <t>https://www.indeed.com/viewjob?jk=e1b9bbef981d9232</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer</t>
+          <t>Network IoT Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9886d247b0ec7a02</t>
+          <t>https://www.indeed.com/viewjob?jk=0da29d3af250447a</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Waters</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Milford, MA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1b9bbef981d9232</t>
+          <t>https://www.indeed.com/viewjob?jk=1975adb5bfc7de33</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Network IoT Engineer</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PEARLY</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Santa Barbara, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da29d3af250447a</t>
+          <t>https://www.indeed.com/viewjob?jk=52fbd92226aade92</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Waters</t>
+          <t>PEARLY</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Milford, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1975adb5bfc7de33</t>
+          <t>https://www.indeed.com/viewjob?jk=3e77317858ff838d</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Santa Barbara, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52fbd92226aade92</t>
+          <t>https://www.indeed.com/viewjob?jk=9737f288d965528f</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, Google Cloud Platform, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e77317858ff838d</t>
+          <t>https://www.indeed.com/viewjob?jk=be47bff9f1c0f69d</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9737f288d965528f</t>
+          <t>https://www.indeed.com/viewjob?jk=e65cdb592eb57da5</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Backend)</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PlanHub</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Clarksville, TN, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, Scala, MySQL, DynamoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b63efe5dfc4a026c</t>
+          <t>https://www.indeed.com/viewjob?jk=e1a1d694cac30055</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
+          <t>Senior Software Engineer (Backend)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ABCorp NA Inc.</t>
+          <t>PlanHub</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, Scala, MySQL, DynamoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d8f6d93b707b783</t>
+          <t>https://www.indeed.com/viewjob?jk=b63efe5dfc4a026c</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Rogue Community College</t>
+          <t>ABCorp NA Inc.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Power BI</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f9335cc41b5edf2</t>
+          <t>https://www.indeed.com/viewjob?jk=5d8f6d93b707b783</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Rogue Community College</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, Kafka, Dimensional Modeling, ETL, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503c92a0918e2779</t>
+          <t>https://www.indeed.com/viewjob?jk=7f9335cc41b5edf2</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Engineering Java/Python</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
+          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, Kafka, Dimensional Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dfc1c1ddf5b07e8</t>
+          <t>https://www.indeed.com/viewjob?jk=503c92a0918e2779</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>Software Engineer III - Data Engineering Java/Python</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab7b07d708701fa</t>
+          <t>https://www.indeed.com/viewjob?jk=6dfc1c1ddf5b07e8</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend) - Global Dining</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f71d52efce43e2</t>
+          <t>https://www.indeed.com/viewjob?jk=cab7b07d708701fa</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Software Engineer (Backend) - Global Dining</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=110f275787ec7bdb</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f71d52efce43e2</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Governance</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Alter Domus</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Databricks, Unity Catalog, Scala, ETL, ELT</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d83b504ed46b0c</t>
+          <t>https://www.indeed.com/viewjob?jk=110f275787ec7bdb</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Platform</t>
+          <t>Senior Data Engineer - Data Governance</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Middesk</t>
+          <t>Alter Domus</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Spark, Data Modeling, Terraform, Kubernetes, Airflow, Git</t>
+          <t>AWS, Glue, S3, IAM, RDS, Databricks, Unity Catalog, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=514717df8eb087ca</t>
+          <t>https://www.indeed.com/viewjob?jk=c3d83b504ed46b0c</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Data, Autonomy</t>
+          <t>Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Middesk</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, RDS, Azure, Spark, Data Modeling, Terraform, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3560765ed8e488</t>
+          <t>https://www.indeed.com/viewjob?jk=514717df8eb087ca</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Risk Developer (Python/Azure)</t>
+          <t>Sr. Software Engineer, Data, Autonomy</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, MLflow, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7762d03304071b69</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3560765ed8e488</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf4b62fe049b84e</t>
+          <t>https://www.indeed.com/viewjob?jk=176afb0ac80a4191</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ca41478bb936cd</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf4b62fe049b84e</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>hatch IT</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, ETL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b260e746e7b9c233</t>
+          <t>https://www.indeed.com/viewjob?jk=57ca41478bb936cd</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE)</t>
+          <t>Senior Risk Developer (Python/Azure)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>hatch IT</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Datadog</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c08c735142c13e1b</t>
+          <t>https://www.indeed.com/viewjob?jk=7762d03304071b69</t>
         </is>
       </c>
     </row>
@@ -4773,25 +4773,25 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Entry-Level Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>hatch IT</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,19 +4801,19 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd80dc2e6636141e</t>
+          <t>https://www.indeed.com/viewjob?jk=b260e746e7b9c233</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>hatch IT</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4822,11 +4822,11 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, ECS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b5cdc524b199967</t>
+          <t>https://www.indeed.com/viewjob?jk=c08c735142c13e1b</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer III</t>
+          <t>Microsoft Entra</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Kapitus</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31099f3a1c434171</t>
+          <t>https://www.indeed.com/viewjob?jk=f61688604ed96074</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Enterprise Data &amp; Analytics</t>
+          <t>Entry-Level Data Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, Databricks, Data Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b74ac1e46b3dfa89</t>
+          <t>https://www.indeed.com/viewjob?jk=dd80dc2e6636141e</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (FDE)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>ISHIR</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ecc0cd2b5a2111</t>
+          <t>https://www.indeed.com/viewjob?jk=8b5cdc524b199967</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>SSO Administrator</t>
+          <t>DevSecOps Engineer III</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Kapitus</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b109c86f55c8c21f</t>
+          <t>https://www.indeed.com/viewjob?jk=31099f3a1c434171</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>Sr. Data Engineer, Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, Databricks, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=739e08afe4ba1176</t>
+          <t>https://www.indeed.com/viewjob?jk=b74ac1e46b3dfa89</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>ISHIR</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=843b039e4e75f61f</t>
+          <t>https://www.indeed.com/viewjob?jk=15ecc0cd2b5a2111</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>SSO Administrator</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ead7f0da7c5db1</t>
+          <t>https://www.indeed.com/viewjob?jk=b109c86f55c8c21f</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae8a17a1c6f39e3</t>
+          <t>https://www.indeed.com/viewjob?jk=739e08afe4ba1176</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>IT PROFESSIONAL-APPLICATIONS (Database Administrator) (HEC)</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>City of Houston, TX</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5c91aac0db662ae</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c369e1e8241c9f</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
+          <t>DOCSIS Testing Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, NoSQL, ETL, ELT, Splunk, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=151fe9868f44f2f1</t>
+          <t>https://www.indeed.com/viewjob?jk=0e134c7566cf151c</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>IT PROFESSIONAL-APPLICATIONS (Database Administrator) (HEC)</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>City of Houston, TX</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c369e1e8241c9f</t>
+          <t>https://www.indeed.com/viewjob?jk=843b039e4e75f61f</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>DOCSIS Testing Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, NoSQL, ETL, ELT, Splunk, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,7 +5256,147 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e134c7566cf151c</t>
+          <t>https://www.indeed.com/viewjob?jk=c1ead7f0da7c5db1</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ae8a17a1c6f39e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Senior Engineer - .NET</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Chevy Chase, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e5c91aac0db662ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>CrowdStrike</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=151fe9868f44f2f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Identity AI / ML Engineer</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df69083a5f5407d8</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-04.xlsx
+++ b/results/job_matches_2026-03-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G142"/>
+  <dimension ref="A1:G138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Junior Oracle Apps Developer</t>
+          <t>Data Engineer/Python Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Zifo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, ECS, RDS, Azure, Blob Storage</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0adde35786282b2b</t>
+          <t>https://www.indeed.com/viewjob?jk=3419a1d7b4acb559</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer/Python Developer</t>
+          <t>Full Stack Engineer (React + Node.js)-4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zifo</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3419a1d7b4acb559</t>
+          <t>https://www.indeed.com/viewjob?jk=e082e26fc29250a3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (React + Node.js)-4</t>
+          <t>Junior Oracle Apps Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, ECS, RDS, Azure, Blob Storage</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e082e26fc29250a3</t>
+          <t>https://www.indeed.com/viewjob?jk=0adde35786282b2b</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer - AI Practice Team</t>
+          <t>Senior Data Engineer, ACVMax</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>American Bureau of Shipping (ABS)</t>
+          <t>ACV Auctions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,29 +766,29 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Azure, Data Factory, Databricks, Event Hubs, BigQuery</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98e9bc7cd1938bfd</t>
+          <t>https://www.indeed.com/viewjob?jk=6c28dd5d00192a5b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Data Engineer - AI Practice Team</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>American Bureau of Shipping (ABS)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Azure, Data Factory, Databricks, Event Hubs, BigQuery</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7167050c109be2d4</t>
+          <t>https://www.indeed.com/viewjob?jk=98e9bc7cd1938bfd</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=862a4a8989448fa0</t>
+          <t>https://www.indeed.com/viewjob?jk=7167050c109be2d4</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07e542bb4713fad0</t>
+          <t>https://www.indeed.com/viewjob?jk=862a4a8989448fa0</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c88dff775194e30</t>
+          <t>https://www.indeed.com/viewjob?jk=07e542bb4713fad0</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ced45fe117deb8</t>
+          <t>https://www.indeed.com/viewjob?jk=2c88dff775194e30</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc8e0c810b3e7cd</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ced45fe117deb8</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7791942c877daada</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc8e0c810b3e7cd</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6b39b9b56abc0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=7791942c877daada</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648774ee33ca3b76</t>
+          <t>https://www.indeed.com/viewjob?jk=b6b39b9b56abc0bd</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a93ca1ad887e17f0</t>
+          <t>https://www.indeed.com/viewjob?jk=648774ee33ca3b76</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d963e90dfb3fa4d6</t>
+          <t>https://www.indeed.com/viewjob?jk=a93ca1ad887e17f0</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783ac47e6d62e414</t>
+          <t>https://www.indeed.com/viewjob?jk=d963e90dfb3fa4d6</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e511c7108cd6e82d</t>
+          <t>https://www.indeed.com/viewjob?jk=783ac47e6d62e414</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a6a2ad30fc1236d</t>
+          <t>https://www.indeed.com/viewjob?jk=e511c7108cd6e82d</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2d42f6d55a07b48</t>
+          <t>https://www.indeed.com/viewjob?jk=2a6a2ad30fc1236d</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c423f392a018bf22</t>
+          <t>https://www.indeed.com/viewjob?jk=e2d42f6d55a07b48</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb49af32ea451f63</t>
+          <t>https://www.indeed.com/viewjob?jk=c423f392a018bf22</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7468c4fe6bdb23</t>
+          <t>https://www.indeed.com/viewjob?jk=cb49af32ea451f63</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a3485c3c6153843</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7468c4fe6bdb23</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef4166ba4aa9b5a3</t>
+          <t>https://www.indeed.com/viewjob?jk=3a3485c3c6153843</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91d6e4beb774dd25</t>
+          <t>https://www.indeed.com/viewjob?jk=ef4166ba4aa9b5a3</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcf2824745a050e</t>
+          <t>https://www.indeed.com/viewjob?jk=91d6e4beb774dd25</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b296145590b995</t>
+          <t>https://www.indeed.com/viewjob?jk=adcf2824745a050e</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c4169879098b22b</t>
+          <t>https://www.indeed.com/viewjob?jk=64b296145590b995</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44e1222f0eb14744</t>
+          <t>https://www.indeed.com/viewjob?jk=8c4169879098b22b</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37bd1a8719f0aafc</t>
+          <t>https://www.indeed.com/viewjob?jk=44e1222f0eb14744</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e151b2c0a32e2723</t>
+          <t>https://www.indeed.com/viewjob?jk=37bd1a8719f0aafc</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c07dcca1b609463e</t>
+          <t>https://www.indeed.com/viewjob?jk=e151b2c0a32e2723</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c721bd4ca7bdffe1</t>
+          <t>https://www.indeed.com/viewjob?jk=c07dcca1b609463e</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8e182c6058fd2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=c721bd4ca7bdffe1</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4997f8f92f05b9d2</t>
+          <t>https://www.indeed.com/viewjob?jk=e8e182c6058fd2a4</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a56481df82d7aa6</t>
+          <t>https://www.indeed.com/viewjob?jk=4997f8f92f05b9d2</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb00c80fb9cb9b65</t>
+          <t>https://www.indeed.com/viewjob?jk=2a56481df82d7aa6</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fd1863254c88e5d</t>
+          <t>https://www.indeed.com/viewjob?jk=fb00c80fb9cb9b65</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Infrastructure</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ALTRUIST</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2b2e3b90367f3b4</t>
+          <t>https://www.indeed.com/viewjob?jk=3fd1863254c88e5d</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15721c69bc524693</t>
+          <t>https://www.indeed.com/viewjob?jk=b2b2e3b90367f3b4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>ALTRUIST</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6c4839e7fe64d8e</t>
+          <t>https://www.indeed.com/viewjob?jk=15721c69bc524693</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Infrastructure</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ALTRUIST</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc6ad57eba624292</t>
+          <t>https://www.indeed.com/viewjob?jk=a6c4839e7fe64d8e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Infrastructure</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ALTRUIST</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15325ad687b27337</t>
+          <t>https://www.indeed.com/viewjob?jk=17c87f0de0ddb952</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II,</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark</t>
+          <t>AWS, Redshift, ECS, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17c87f0de0ddb952</t>
+          <t>https://www.indeed.com/viewjob?jk=b4edb591674d441f</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4edb591674d441f</t>
+          <t>https://www.indeed.com/viewjob?jk=28ab3491bb9f5589</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer II,</t>
+          <t>Blockchain Java Backend Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28ab3491bb9f5589</t>
+          <t>https://www.indeed.com/viewjob?jk=e49019e3e57d794c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Blockchain Java Backend Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e49019e3e57d794c</t>
+          <t>https://www.indeed.com/viewjob?jk=0997a11d6aaf4e73</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0997a11d6aaf4e73</t>
+          <t>https://www.indeed.com/viewjob?jk=9188fd233f524c42</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9188fd233f524c42</t>
+          <t>https://www.indeed.com/viewjob?jk=4cc63cdd2328277c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer, AI Analytics</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Residex, LLC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cc63cdd2328277c</t>
+          <t>https://www.indeed.com/viewjob?jk=3b994e1736909aed</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer, AI Analytics</t>
+          <t>Sr. Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Residex, LLC</t>
+          <t>ELLKAY, LLC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Elmwood Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Athena, IAM, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b994e1736909aed</t>
+          <t>https://www.indeed.com/viewjob?jk=28b63f4ef510667a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. Cloud Software Engineer</t>
+          <t>Associate/Consultant Engineer - Remote</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ELLKAY, LLC</t>
+          <t>Rancho BioSciences</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Elmwood Park, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,59 +2456,59 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28b63f4ef510667a</t>
+          <t>https://www.indeed.com/viewjob?jk=72630d316687619c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Associate/Consultant Engineer - Remote</t>
+          <t>Senior Engineer - DevOps/ DataOps</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Rancho BioSciences</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, DataOps, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72630d316687619c</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ed15cfc823b0b7</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Engineer - DevOps/ DataOps</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, DataOps, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ed15cfc823b0b7</t>
+          <t>https://www.indeed.com/viewjob?jk=7d49d017dead0cec</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,94 +2561,94 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b12dfc8a5459a4f</t>
+          <t>https://www.indeed.com/viewjob?jk=b08c3dc1b325be49</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>SRS Distribution</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d49d017dead0cec</t>
+          <t>https://www.indeed.com/viewjob?jk=4cde050af8749e53</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b08c3dc1b325be49</t>
+          <t>https://www.indeed.com/viewjob?jk=bf6f08ab2860bc5c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>Ncontracts</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf6f08ab2860bc5c</t>
+          <t>https://www.indeed.com/viewjob?jk=da52963e4860aaaa</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Incremental CRM - Data Developer 1</t>
+          <t>Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Databricks, Scala, SQL Server, ETL</t>
+          <t>AWS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c7931e975a12585</t>
+          <t>https://www.indeed.com/viewjob?jk=80460d4e824e28cc</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer - Remote</t>
+          <t>Incremental CRM - Data Developer 1</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Databricks, Scala, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80460d4e824e28cc</t>
+          <t>https://www.indeed.com/viewjob?jk=3c7931e975a12585</t>
         </is>
       </c>
     </row>
@@ -2988,17 +2988,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SQL Server Database Engineer</t>
+          <t>Data Engineer, CDC</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>IDBNY</t>
+          <t>DRT Strategies, Inc.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, HBase, Snowflake, Oracle, SQL Server, MongoDB</t>
+          <t>AWS, EMR, RDS, Azure, Scala, ETL, Power BI, Tableau, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15c2f3c4f1ddf6ac</t>
+          <t>https://www.indeed.com/viewjob?jk=a223a368864e5d1b</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Cloud Identity Architect</t>
+          <t>SQL Server Database Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>IDBNY</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Databricks, HBase, Snowflake, Oracle, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdd1e41d5949d150</t>
+          <t>https://www.indeed.com/viewjob?jk=15c2f3c4f1ddf6ac</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>System Integration Test Engineer</t>
+          <t>Cloud Identity Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BGIT India Private Limited</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Hudson, NH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=426d1d0d6a93918c</t>
+          <t>https://www.indeed.com/viewjob?jk=fdd1e41d5949d150</t>
         </is>
       </c>
     </row>
@@ -3128,87 +3128,87 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Halo Creative &amp; Media LLP</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371d6385735b0f59</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd0439895496e24</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-2</t>
+          <t>System Integration Test Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>BGIT India Private Limited</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Hudson, NH, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f9103ddd4f544e</t>
+          <t>https://www.indeed.com/viewjob?jk=426d1d0d6a93918c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Halo Creative &amp; Media LLP</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d602908669423e</t>
+          <t>https://www.indeed.com/viewjob?jk=371d6385735b0f59</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>Data Platform Engineer-2</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,17 +3251,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10de5f0ca2f7673d</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f9103ddd4f544e</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6750fd9ad4e72e</t>
+          <t>https://www.indeed.com/viewjob?jk=75d602908669423e</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45db6ac50eb5587</t>
+          <t>https://www.indeed.com/viewjob?jk=10de5f0ca2f7673d</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1c0f7e27e90a87e</t>
+          <t>https://www.indeed.com/viewjob?jk=8e6750fd9ad4e72e</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4dc81e5cd9b6b72</t>
+          <t>https://www.indeed.com/viewjob?jk=c45db6ac50eb5587</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14fea47c1dbfabac</t>
+          <t>https://www.indeed.com/viewjob?jk=d1c0f7e27e90a87e</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02d7bcc2bd0697b0</t>
+          <t>https://www.indeed.com/viewjob?jk=a4dc81e5cd9b6b72</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50e0ff85e5f89851</t>
+          <t>https://www.indeed.com/viewjob?jk=14fea47c1dbfabac</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Full Stack Web Developer</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>UP Management LLC</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Bedford, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e000e4c87bc0a4b</t>
+          <t>https://www.indeed.com/viewjob?jk=02d7bcc2bd0697b0</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Risk Data AI/ML Engineer</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=979402388d34b409</t>
+          <t>https://www.indeed.com/viewjob?jk=50e0ff85e5f89851</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - AI/ML</t>
+          <t>Risk Data AI/ML Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0bc9a390582054</t>
+          <t>https://www.indeed.com/viewjob?jk=979402388d34b409</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Databricks AI Engineer</t>
+          <t>Senior Software Engineer II - AI/ML</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Powerplan</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5753d39b44c782</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0bc9a390582054</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Databricks AI Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ELLKAY, LLC</t>
+          <t>Powerplan</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Elmwood Park, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Streams/Tasks</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7bfd917914d4728</t>
+          <t>https://www.indeed.com/viewjob?jk=3b5753d39b44c782</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>ELLKAY, LLC</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Elmwood Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, EMR, S3, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Streams/Tasks</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9886d247b0ec7a02</t>
+          <t>https://www.indeed.com/viewjob?jk=c7bfd917914d4728</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
+          <t>Sr DevOPS Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1b9bbef981d9232</t>
+          <t>https://www.indeed.com/viewjob?jk=9886d247b0ec7a02</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Network IoT Engineer</t>
+          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da29d3af250447a</t>
+          <t>https://www.indeed.com/viewjob?jk=e1b9bbef981d9232</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Network IoT Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Waters</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Milford, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1975adb5bfc7de33</t>
+          <t>https://www.indeed.com/viewjob?jk=0da29d3af250447a</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>Waters</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Santa Barbara, CA, US USA</t>
+          <t>Milford, MA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52fbd92226aade92</t>
+          <t>https://www.indeed.com/viewjob?jk=1975adb5bfc7de33</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Santa Barbara, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e77317858ff838d</t>
+          <t>https://www.indeed.com/viewjob?jk=52fbd92226aade92</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9737f288d965528f</t>
+          <t>https://www.indeed.com/viewjob?jk=3e77317858ff838d</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PEARLY</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, Google Cloud Platform, Vertex AI, Scala</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be47bff9f1c0f69d</t>
+          <t>https://www.indeed.com/viewjob?jk=9737f288d965528f</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>ABCorp NA Inc.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,17 +3986,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e65cdb592eb57da5</t>
+          <t>https://www.indeed.com/viewjob?jk=5d8f6d93b707b783</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Clarksville, TN, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1a1d694cac30055</t>
+          <t>https://www.indeed.com/viewjob?jk=e65cdb592eb57da5</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Backend)</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PlanHub</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Clarksville, TN, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, Scala, MySQL, DynamoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b63efe5dfc4a026c</t>
+          <t>https://www.indeed.com/viewjob?jk=e1a1d694cac30055</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ABCorp NA Inc.</t>
+          <t>Rogue Community College</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d8f6d93b707b783</t>
+          <t>https://www.indeed.com/viewjob?jk=7f9335cc41b5edf2</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Rogue Community College</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Power BI</t>
+          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, Kafka, Dimensional Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f9335cc41b5edf2</t>
+          <t>https://www.indeed.com/viewjob?jk=503c92a0918e2779</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Software Engineer III - Data Engineering Java/Python</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, Kafka, Dimensional Modeling, ETL, Airflow</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503c92a0918e2779</t>
+          <t>https://www.indeed.com/viewjob?jk=6dfc1c1ddf5b07e8</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Engineering Java/Python</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dfc1c1ddf5b07e8</t>
+          <t>https://www.indeed.com/viewjob?jk=cab7b07d708701fa</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>Software Engineer (Backend) - Global Dining</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab7b07d708701fa</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f71d52efce43e2</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend) - Global Dining</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>PGA TOUR Superstore</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,17 +4266,17 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f71d52efce43e2</t>
+          <t>https://www.indeed.com/viewjob?jk=73bdb2d180484ce2</t>
         </is>
       </c>
     </row>
@@ -4318,17 +4318,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Governance</t>
+          <t>Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Alter Domus</t>
+          <t>Middesk</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Databricks, Unity Catalog, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, Spark, Data Modeling, Terraform, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d83b504ed46b0c</t>
+          <t>https://www.indeed.com/viewjob?jk=514717df8eb087ca</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Platform</t>
+          <t>Sr. Software Engineer, Data, Autonomy</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Middesk</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Spark, Data Modeling, Terraform, Kubernetes, Airflow, Git</t>
+          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=514717df8eb087ca</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3560765ed8e488</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Data, Autonomy</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3560765ed8e488</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf4b62fe049b84e</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=176afb0ac80a4191</t>
+          <t>https://www.indeed.com/viewjob?jk=57ca41478bb936cd</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Risk Developer (Python/Azure)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf4b62fe049b84e</t>
+          <t>https://www.indeed.com/viewjob?jk=7762d03304071b69</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>Salesforce Architect - Senior</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>CommunityForce Inc.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>ECS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ca41478bb936cd</t>
+          <t>https://www.indeed.com/viewjob?jk=7d236cba8a6e8ae3</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Risk Developer (Python/Azure)</t>
+          <t>.NET Angular Reporting Developer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, MLflow, CI/CD</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, Star Schema, ETL, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7762d03304071b69</t>
+          <t>https://www.indeed.com/viewjob?jk=f21a948f0ac42414</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>.NET Angular Reporting Developer</t>
+          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, Star Schema, ETL, Power BI, CI/CD, Azure DevOps</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21a948f0ac42414</t>
+          <t>https://www.indeed.com/viewjob?jk=2698e1f59bd5def7</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2698e1f59bd5def7</t>
+          <t>https://www.indeed.com/viewjob?jk=4d0bc94cbe8822db</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Paterson, NJ, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d0bc94cbe8822db</t>
+          <t>https://www.indeed.com/viewjob?jk=75f6d90e6b234f60</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Paterson, NJ, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75f6d90e6b234f60</t>
+          <t>https://www.indeed.com/viewjob?jk=e53f9ddcb5f4c2b9</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,102 +4731,102 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e53f9ddcb5f4c2b9</t>
+          <t>https://www.indeed.com/viewjob?jk=44fb3987d11d1123</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Callaway Golf</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44fb3987d11d1123</t>
+          <t>https://www.indeed.com/viewjob?jk=2cf949704a694c55</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Microsoft Entra</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>hatch IT</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, ETL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b260e746e7b9c233</t>
+          <t>https://www.indeed.com/viewjob?jk=f61688604ed96074</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE)</t>
+          <t>Entry-Level Data Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>hatch IT</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c08c735142c13e1b</t>
+          <t>https://www.indeed.com/viewjob?jk=dd80dc2e6636141e</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Microsoft Entra</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f61688604ed96074</t>
+          <t>https://www.indeed.com/viewjob?jk=8b5cdc524b199967</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Entry-Level Data Engineer</t>
+          <t>DevSecOps Engineer III</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Kapitus</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd80dc2e6636141e</t>
+          <t>https://www.indeed.com/viewjob?jk=31099f3a1c434171</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>Westchester Medical Center Health Network</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Valhalla, NY, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Snowflake, SQL Server, Data Modeling, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b5cdc524b199967</t>
+          <t>https://www.indeed.com/viewjob?jk=d807a7856ebe08db</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer III</t>
+          <t>Sr. Data Engineer, Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Kapitus</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, Databricks, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31099f3a1c434171</t>
+          <t>https://www.indeed.com/viewjob?jk=b74ac1e46b3dfa89</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Enterprise Data &amp; Analytics</t>
+          <t>SSO Administrator</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, Databricks, Data Modeling, ELT, dbt</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b74ac1e46b3dfa89</t>
+          <t>https://www.indeed.com/viewjob?jk=b109c86f55c8c21f</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (FDE)</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ISHIR</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ecc0cd2b5a2111</t>
+          <t>https://www.indeed.com/viewjob?jk=739e08afe4ba1176</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SSO Administrator</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b109c86f55c8c21f</t>
+          <t>https://www.indeed.com/viewjob?jk=843b039e4e75f61f</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=739e08afe4ba1176</t>
+          <t>https://www.indeed.com/viewjob?jk=c1ead7f0da7c5db1</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>IT PROFESSIONAL-APPLICATIONS (Database Administrator) (HEC)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>City of Houston, TX</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c369e1e8241c9f</t>
+          <t>https://www.indeed.com/viewjob?jk=1ae8a17a1c6f39e3</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>DOCSIS Testing Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, NoSQL, ETL, ELT, Splunk, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e134c7566cf151c</t>
+          <t>https://www.indeed.com/viewjob?jk=e5c91aac0db662ae</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>IT PROFESSIONAL-APPLICATIONS (Database Administrator) (HEC)</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>City of Houston, TX</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=843b039e4e75f61f</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c369e1e8241c9f</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>DOCSIS Testing Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, NoSQL, ETL, ELT, Splunk, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,147 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ead7f0da7c5db1</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae8a17a1c6f39e3</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Senior Engineer - .NET</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e5c91aac0db662ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>CrowdStrike</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=151fe9868f44f2f1</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Identity AI / ML Engineer</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=df69083a5f5407d8</t>
+          <t>https://www.indeed.com/viewjob?jk=0e134c7566cf151c</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-04.xlsx
+++ b/results/job_matches_2026-03-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G138"/>
+  <dimension ref="A1:G140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer II (Hybrid Work Schedule)</t>
+          <t>Software Engineer in Test III - Data Analytics</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Quorum Software</t>
+          <t>Emburse</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.9</v>
+        <v>21.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,59 +496,59 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76a633e7c45d5fa0</t>
+          <t>https://www.indeed.com/viewjob?jk=450782bf82b6fc2f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer in Test III - Data Analytics</t>
+          <t>Data Engineer/Python Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Emburse</t>
+          <t>Zifo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.5</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=450782bf82b6fc2f</t>
+          <t>https://www.indeed.com/viewjob?jk=3419a1d7b4acb559</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer/Python Developer</t>
+          <t>Junior Oracle Apps Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Zifo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, ECS, RDS, Azure, Blob Storage</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3419a1d7b4acb559</t>
+          <t>https://www.indeed.com/viewjob?jk=0adde35786282b2b</t>
         </is>
       </c>
     </row>
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Junior Oracle Apps Developer</t>
+          <t>Software Engineer III: DevOps</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, ECS, RDS, Azure, Blob Storage</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0adde35786282b2b</t>
+          <t>https://www.indeed.com/viewjob?jk=bc952e4224a3aa24</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer III: DevOps</t>
+          <t>Senior Data Engineer, Client Authentication</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP, Scala</t>
+          <t>IAM, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc952e4224a3aa24</t>
+          <t>https://www.indeed.com/viewjob?jk=a908b362cb914674</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Client Authentication</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Quilt</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a908b362cb914674</t>
+          <t>https://www.indeed.com/viewjob?jk=27d883fd388e687a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer, ACVMax</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Quilt</t>
+          <t>ACV Auctions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d883fd388e687a</t>
+          <t>https://www.indeed.com/viewjob?jk=6c28dd5d00192a5b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, ACVMax</t>
+          <t>Data Engineer - AI Practice Team</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ACV Auctions</t>
+          <t>American Bureau of Shipping (ABS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,29 +766,29 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Azure, Data Factory, Databricks, Event Hubs, BigQuery</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c28dd5d00192a5b</t>
+          <t>https://www.indeed.com/viewjob?jk=98e9bc7cd1938bfd</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer - AI Practice Team</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>American Bureau of Shipping (ABS)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Azure, Data Factory, Databricks, Event Hubs, BigQuery</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98e9bc7cd1938bfd</t>
+          <t>https://www.indeed.com/viewjob?jk=7167050c109be2d4</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7167050c109be2d4</t>
+          <t>https://www.indeed.com/viewjob?jk=862a4a8989448fa0</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=862a4a8989448fa0</t>
+          <t>https://www.indeed.com/viewjob?jk=07e542bb4713fad0</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07e542bb4713fad0</t>
+          <t>https://www.indeed.com/viewjob?jk=2c88dff775194e30</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c88dff775194e30</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ced45fe117deb8</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ced45fe117deb8</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc8e0c810b3e7cd</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc8e0c810b3e7cd</t>
+          <t>https://www.indeed.com/viewjob?jk=7791942c877daada</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7791942c877daada</t>
+          <t>https://www.indeed.com/viewjob?jk=b6b39b9b56abc0bd</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6b39b9b56abc0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=648774ee33ca3b76</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648774ee33ca3b76</t>
+          <t>https://www.indeed.com/viewjob?jk=a93ca1ad887e17f0</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a93ca1ad887e17f0</t>
+          <t>https://www.indeed.com/viewjob?jk=d963e90dfb3fa4d6</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d963e90dfb3fa4d6</t>
+          <t>https://www.indeed.com/viewjob?jk=783ac47e6d62e414</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783ac47e6d62e414</t>
+          <t>https://www.indeed.com/viewjob?jk=e511c7108cd6e82d</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e511c7108cd6e82d</t>
+          <t>https://www.indeed.com/viewjob?jk=2a6a2ad30fc1236d</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a6a2ad30fc1236d</t>
+          <t>https://www.indeed.com/viewjob?jk=e2d42f6d55a07b48</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2d42f6d55a07b48</t>
+          <t>https://www.indeed.com/viewjob?jk=c423f392a018bf22</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c423f392a018bf22</t>
+          <t>https://www.indeed.com/viewjob?jk=cb49af32ea451f63</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb49af32ea451f63</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7468c4fe6bdb23</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7468c4fe6bdb23</t>
+          <t>https://www.indeed.com/viewjob?jk=3a3485c3c6153843</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a3485c3c6153843</t>
+          <t>https://www.indeed.com/viewjob?jk=ef4166ba4aa9b5a3</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef4166ba4aa9b5a3</t>
+          <t>https://www.indeed.com/viewjob?jk=91d6e4beb774dd25</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91d6e4beb774dd25</t>
+          <t>https://www.indeed.com/viewjob?jk=adcf2824745a050e</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcf2824745a050e</t>
+          <t>https://www.indeed.com/viewjob?jk=64b296145590b995</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b296145590b995</t>
+          <t>https://www.indeed.com/viewjob?jk=8c4169879098b22b</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c4169879098b22b</t>
+          <t>https://www.indeed.com/viewjob?jk=44e1222f0eb14744</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44e1222f0eb14744</t>
+          <t>https://www.indeed.com/viewjob?jk=37bd1a8719f0aafc</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37bd1a8719f0aafc</t>
+          <t>https://www.indeed.com/viewjob?jk=e151b2c0a32e2723</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e151b2c0a32e2723</t>
+          <t>https://www.indeed.com/viewjob?jk=c07dcca1b609463e</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c07dcca1b609463e</t>
+          <t>https://www.indeed.com/viewjob?jk=c721bd4ca7bdffe1</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c721bd4ca7bdffe1</t>
+          <t>https://www.indeed.com/viewjob?jk=e8e182c6058fd2a4</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8e182c6058fd2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=4997f8f92f05b9d2</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4997f8f92f05b9d2</t>
+          <t>https://www.indeed.com/viewjob?jk=2a56481df82d7aa6</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a56481df82d7aa6</t>
+          <t>https://www.indeed.com/viewjob?jk=fb00c80fb9cb9b65</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb00c80fb9cb9b65</t>
+          <t>https://www.indeed.com/viewjob?jk=3fd1863254c88e5d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Senior Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ALTRUIST</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fd1863254c88e5d</t>
+          <t>https://www.indeed.com/viewjob?jk=b2b2e3b90367f3b4</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2b2e3b90367f3b4</t>
+          <t>https://www.indeed.com/viewjob?jk=15721c69bc524693</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Infrastructure</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ALTRUIST</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15721c69bc524693</t>
+          <t>https://www.indeed.com/viewjob?jk=a6c4839e7fe64d8e</t>
         </is>
       </c>
     </row>
@@ -2092,11 +2092,11 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6c4839e7fe64d8e</t>
+          <t>https://www.indeed.com/viewjob?jk=17c87f0de0ddb952</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI/ML Architect with Databricks , AWS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>Vytwo Technologies</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Prosper, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark</t>
+          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17c87f0de0ddb952</t>
+          <t>https://www.indeed.com/viewjob?jk=29c402e4a2f5220b</t>
         </is>
       </c>
     </row>
@@ -2428,52 +2428,52 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Associate/Consultant Engineer - Remote</t>
+          <t>Senior Engineer - DevOps/ DataOps</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Rancho BioSciences</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, DataOps, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72630d316687619c</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ed15cfc823b0b7</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Engineer - DevOps/ DataOps</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, DataOps, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ed15cfc823b0b7</t>
+          <t>https://www.indeed.com/viewjob?jk=7d49d017dead0cec</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,59 +2526,59 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d49d017dead0cec</t>
+          <t>https://www.indeed.com/viewjob?jk=b08c3dc1b325be49</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>SRS Distribution</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b08c3dc1b325be49</t>
+          <t>https://www.indeed.com/viewjob?jk=4cde050af8749e53</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SRS Distribution</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cde050af8749e53</t>
+          <t>https://www.indeed.com/viewjob?jk=bf6f08ab2860bc5c</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>Ncontracts</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf6f08ab2860bc5c</t>
+          <t>https://www.indeed.com/viewjob?jk=da52963e4860aaaa</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Incremental CRM - Data Developer 1</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ncontracts</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Databricks, Scala, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da52963e4860aaaa</t>
+          <t>https://www.indeed.com/viewjob?jk=3c7931e975a12585</t>
         </is>
       </c>
     </row>
@@ -2708,52 +2708,52 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Incremental CRM - Data Developer 1</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Databricks, Scala, SQL Server, ETL</t>
+          <t>AWS, Kinesis, IAM, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c7931e975a12585</t>
+          <t>https://www.indeed.com/viewjob?jk=a021dbda97cc3405</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a021dbda97cc3405</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7ddc3760328a54</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Cloud Data Engineer + Snowflake (On-Site)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
+          <t>AWS, Glue, EMR, RDS, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7ddc3760328a54</t>
+          <t>https://www.indeed.com/viewjob?jk=58e9f31119d31013</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer + Snowflake (On-Site)</t>
+          <t>PDM Implementation Data Architect</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e9f31119d31013</t>
+          <t>https://www.indeed.com/viewjob?jk=3576de9e88dd4c5c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PDM Implementation Data Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Spark, PySpark</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3576de9e88dd4c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=39a6c4ab9efc012e</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Hitachi Digital Services</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a6c4ab9efc012e</t>
+          <t>https://www.indeed.com/viewjob?jk=33510d4bb406c6e2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Hitachi Digital Services</t>
+          <t>ROLLER</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33510d4bb406c6e2</t>
+          <t>https://www.indeed.com/viewjob?jk=afb709659d664135</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer, CDC</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ROLLER</t>
+          <t>DRT Strategies, Inc.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, EMR, RDS, Azure, Scala, ETL, Power BI, Tableau, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb709659d664135</t>
+          <t>https://www.indeed.com/viewjob?jk=a223a368864e5d1b</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer, CDC</t>
+          <t>SQL Server Database Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>DRT Strategies, Inc.</t>
+          <t>IDBNY</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Scala, ETL, Power BI, Tableau, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Azure, Databricks, HBase, Snowflake, Oracle, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a223a368864e5d1b</t>
+          <t>https://www.indeed.com/viewjob?jk=15c2f3c4f1ddf6ac</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SQL Server Database Engineer</t>
+          <t>Cloud Identity Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>IDBNY</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, HBase, Snowflake, Oracle, SQL Server, MongoDB</t>
+          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15c2f3c4f1ddf6ac</t>
+          <t>https://www.indeed.com/viewjob?jk=fdd1e41d5949d150</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Cloud Identity Architect</t>
+          <t>System Integration Test Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BGIT India Private Limited</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Hudson, NH, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdd1e41d5949d150</t>
+          <t>https://www.indeed.com/viewjob?jk=426d1d0d6a93918c</t>
         </is>
       </c>
     </row>
@@ -3163,52 +3163,52 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>System Integration Test Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BGIT India Private Limited</t>
+          <t>Halo Creative &amp; Media LLP</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hudson, NH, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=426d1d0d6a93918c</t>
+          <t>https://www.indeed.com/viewjob?jk=371d6385735b0f59</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Platform Engineer-2</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Halo Creative &amp; Media LLP</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371d6385735b0f59</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f9103ddd4f544e</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-2</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,17 +3251,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f9103ddd4f544e</t>
+          <t>https://www.indeed.com/viewjob?jk=75d602908669423e</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d602908669423e</t>
+          <t>https://www.indeed.com/viewjob?jk=10de5f0ca2f7673d</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10de5f0ca2f7673d</t>
+          <t>https://www.indeed.com/viewjob?jk=8e6750fd9ad4e72e</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6750fd9ad4e72e</t>
+          <t>https://www.indeed.com/viewjob?jk=c45db6ac50eb5587</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45db6ac50eb5587</t>
+          <t>https://www.indeed.com/viewjob?jk=d1c0f7e27e90a87e</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1c0f7e27e90a87e</t>
+          <t>https://www.indeed.com/viewjob?jk=a4dc81e5cd9b6b72</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4dc81e5cd9b6b72</t>
+          <t>https://www.indeed.com/viewjob?jk=14fea47c1dbfabac</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14fea47c1dbfabac</t>
+          <t>https://www.indeed.com/viewjob?jk=02d7bcc2bd0697b0</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02d7bcc2bd0697b0</t>
+          <t>https://www.indeed.com/viewjob?jk=50e0ff85e5f89851</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>Risk Data AI/ML Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50e0ff85e5f89851</t>
+          <t>https://www.indeed.com/viewjob?jk=979402388d34b409</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Risk Data AI/ML Engineer</t>
+          <t>Senior Software Engineer II - AI/ML</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=979402388d34b409</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0bc9a390582054</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - AI/ML</t>
+          <t>Senior Databricks AI Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>Powerplan</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0bc9a390582054</t>
+          <t>https://www.indeed.com/viewjob?jk=3b5753d39b44c782</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Databricks AI Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Powerplan</t>
+          <t>ELLKAY, LLC</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Elmwood Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake</t>
+          <t>AWS, EMR, S3, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Streams/Tasks</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5753d39b44c782</t>
+          <t>https://www.indeed.com/viewjob?jk=c7bfd917914d4728</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr DevOPS Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ELLKAY, LLC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Elmwood Park, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Streams/Tasks</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7bfd917914d4728</t>
+          <t>https://www.indeed.com/viewjob?jk=9886d247b0ec7a02</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer</t>
+          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9886d247b0ec7a02</t>
+          <t>https://www.indeed.com/viewjob?jk=e1b9bbef981d9232</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
+          <t>Network IoT Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1b9bbef981d9232</t>
+          <t>https://www.indeed.com/viewjob?jk=0da29d3af250447a</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Network IoT Engineer</t>
+          <t>Analytics, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,17 +3811,17 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da29d3af250447a</t>
+          <t>https://www.indeed.com/viewjob?jk=c24274a4aa989f95</t>
         </is>
       </c>
     </row>
@@ -4003,17 +4003,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>Rogue Community College</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,17 +4021,17 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e65cdb592eb57da5</t>
+          <t>https://www.indeed.com/viewjob?jk=7f9335cc41b5edf2</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Clarksville, TN, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1a1d694cac30055</t>
+          <t>https://www.indeed.com/viewjob?jk=e65cdb592eb57da5</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Rogue Community College</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Clarksville, TN, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,17 +4091,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Power BI</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f9335cc41b5edf2</t>
+          <t>https://www.indeed.com/viewjob?jk=e1a1d694cac30055</t>
         </is>
       </c>
     </row>
@@ -4248,17 +4248,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Microsoft Fabric</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>PGA TOUR Superstore</t>
+          <t>EoS Fitness</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT, Power BI</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73bdb2d180484ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=7bd7f3590528db3c</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>PGA TOUR Superstore</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=110f275787ec7bdb</t>
+          <t>https://www.indeed.com/viewjob?jk=73bdb2d180484ce2</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Platform</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Middesk</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Spark, Data Modeling, Terraform, Kubernetes, Airflow, Git</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=514717df8eb087ca</t>
+          <t>https://www.indeed.com/viewjob?jk=110f275787ec7bdb</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Data, Autonomy</t>
+          <t>Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Middesk</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, RDS, Azure, Spark, Data Modeling, Terraform, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3560765ed8e488</t>
+          <t>https://www.indeed.com/viewjob?jk=514717df8eb087ca</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Sr. Software Engineer, Data, Autonomy</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
+          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf4b62fe049b84e</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3560765ed8e488</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>Al Warren Oil Company, Inc.</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Bensenville, IL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ca41478bb936cd</t>
+          <t>https://www.indeed.com/viewjob?jk=6304fa25b90dcc51</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Risk Developer (Python/Azure)</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Al Warren Oil Company, Inc.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, MLflow, CI/CD</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7762d03304071b69</t>
+          <t>https://www.indeed.com/viewjob?jk=9a4e15b6a0305b12</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Salesforce Architect - Senior</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>CommunityForce Inc.</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d236cba8a6e8ae3</t>
+          <t>https://www.indeed.com/viewjob?jk=40b321afc8939ff9</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>.NET Angular Reporting Developer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, Star Schema, ETL, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21a948f0ac42414</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf4b62fe049b84e</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2698e1f59bd5def7</t>
+          <t>https://www.indeed.com/viewjob?jk=57ca41478bb936cd</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
+          <t>Salesforce Architect - Senior</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>CommunityForce Inc.</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>ECS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d0bc94cbe8822db</t>
+          <t>https://www.indeed.com/viewjob?jk=7d236cba8a6e8ae3</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
+          <t>.NET Angular Reporting Developer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Paterson, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, Star Schema, ETL, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75f6d90e6b234f60</t>
+          <t>https://www.indeed.com/viewjob?jk=f21a948f0ac42414</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e53f9ddcb5f4c2b9</t>
+          <t>https://www.indeed.com/viewjob?jk=2698e1f59bd5def7</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,102 +4731,102 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44fb3987d11d1123</t>
+          <t>https://www.indeed.com/viewjob?jk=4d0bc94cbe8822db</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Callaway Golf</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Paterson, NJ, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cf949704a694c55</t>
+          <t>https://www.indeed.com/viewjob?jk=75f6d90e6b234f60</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Microsoft Entra</t>
+          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f61688604ed96074</t>
+          <t>https://www.indeed.com/viewjob?jk=e53f9ddcb5f4c2b9</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Entry-Level Data Engineer</t>
+          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd80dc2e6636141e</t>
+          <t>https://www.indeed.com/viewjob?jk=44fb3987d11d1123</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>Callaway Golf</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b5cdc524b199967</t>
+          <t>https://www.indeed.com/viewjob?jk=2cf949704a694c55</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer III</t>
+          <t>Microsoft Entra</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Kapitus</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31099f3a1c434171</t>
+          <t>https://www.indeed.com/viewjob?jk=f61688604ed96074</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Entry-Level Data Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Westchester Medical Center Health Network</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Valhalla, NY, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, SQL Server, Data Modeling, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d807a7856ebe08db</t>
+          <t>https://www.indeed.com/viewjob?jk=dd80dc2e6636141e</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Enterprise Data &amp; Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, Databricks, Data Modeling, ELT, dbt</t>
+          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b74ac1e46b3dfa89</t>
+          <t>https://www.indeed.com/viewjob?jk=8b5cdc524b199967</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SSO Administrator</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Westchester Medical Center Health Network</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Valhalla, NY, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, Snowflake, SQL Server, Data Modeling, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b109c86f55c8c21f</t>
+          <t>https://www.indeed.com/viewjob?jk=d807a7856ebe08db</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>Sr. Data Engineer, Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, Databricks, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=739e08afe4ba1176</t>
+          <t>https://www.indeed.com/viewjob?jk=b74ac1e46b3dfa89</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>SSO Administrator</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=843b039e4e75f61f</t>
+          <t>https://www.indeed.com/viewjob?jk=b109c86f55c8c21f</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ead7f0da7c5db1</t>
+          <t>https://www.indeed.com/viewjob?jk=739e08afe4ba1176</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>IT PROFESSIONAL-APPLICATIONS (Database Administrator) (HEC)</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>City of Houston, TX</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae8a17a1c6f39e3</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c369e1e8241c9f</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>DOCSIS Testing Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, NoSQL, ETL, ELT, Splunk, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5c91aac0db662ae</t>
+          <t>https://www.indeed.com/viewjob?jk=0e134c7566cf151c</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>IT PROFESSIONAL-APPLICATIONS (Database Administrator) (HEC)</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>City of Houston, TX</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c369e1e8241c9f</t>
+          <t>https://www.indeed.com/viewjob?jk=843b039e4e75f61f</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>DOCSIS Testing Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, NoSQL, ETL, ELT, Splunk, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,7 +5256,77 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e134c7566cf151c</t>
+          <t>https://www.indeed.com/viewjob?jk=c1ead7f0da7c5db1</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ae8a17a1c6f39e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Senior Engineer - .NET</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Chevy Chase, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e5c91aac0db662ae</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-04.xlsx
+++ b/results/job_matches_2026-03-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G140"/>
+  <dimension ref="A1:G144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,25 +643,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Client Authentication</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Jersey Mikes Corporate</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Tinton Falls, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a908b362cb914674</t>
+          <t>https://www.indeed.com/viewjob?jk=31cf41e0387f0b72</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer, Client Authentication</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Quilt</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>IAM, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d883fd388e687a</t>
+          <t>https://www.indeed.com/viewjob?jk=a908b362cb914674</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, ACVMax</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ACV Auctions</t>
+          <t>Quilt</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c28dd5d00192a5b</t>
+          <t>https://www.indeed.com/viewjob?jk=27d883fd388e687a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer - AI Practice Team</t>
+          <t>Senior Data Engineer, ACVMax</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>American Bureau of Shipping (ABS)</t>
+          <t>ACV Auctions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,29 +766,29 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Azure, Data Factory, Databricks, Event Hubs, BigQuery</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98e9bc7cd1938bfd</t>
+          <t>https://www.indeed.com/viewjob?jk=6c28dd5d00192a5b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Data Engineer - AI Practice Team</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>American Bureau of Shipping (ABS)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Azure, Data Factory, Databricks, Event Hubs, BigQuery</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7167050c109be2d4</t>
+          <t>https://www.indeed.com/viewjob?jk=98e9bc7cd1938bfd</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=862a4a8989448fa0</t>
+          <t>https://www.indeed.com/viewjob?jk=7167050c109be2d4</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07e542bb4713fad0</t>
+          <t>https://www.indeed.com/viewjob?jk=862a4a8989448fa0</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c88dff775194e30</t>
+          <t>https://www.indeed.com/viewjob?jk=07e542bb4713fad0</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ced45fe117deb8</t>
+          <t>https://www.indeed.com/viewjob?jk=2c88dff775194e30</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc8e0c810b3e7cd</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ced45fe117deb8</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7791942c877daada</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc8e0c810b3e7cd</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6b39b9b56abc0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=7791942c877daada</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648774ee33ca3b76</t>
+          <t>https://www.indeed.com/viewjob?jk=b6b39b9b56abc0bd</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a93ca1ad887e17f0</t>
+          <t>https://www.indeed.com/viewjob?jk=648774ee33ca3b76</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d963e90dfb3fa4d6</t>
+          <t>https://www.indeed.com/viewjob?jk=a93ca1ad887e17f0</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783ac47e6d62e414</t>
+          <t>https://www.indeed.com/viewjob?jk=d963e90dfb3fa4d6</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e511c7108cd6e82d</t>
+          <t>https://www.indeed.com/viewjob?jk=783ac47e6d62e414</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a6a2ad30fc1236d</t>
+          <t>https://www.indeed.com/viewjob?jk=e511c7108cd6e82d</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2d42f6d55a07b48</t>
+          <t>https://www.indeed.com/viewjob?jk=2a6a2ad30fc1236d</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c423f392a018bf22</t>
+          <t>https://www.indeed.com/viewjob?jk=e2d42f6d55a07b48</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb49af32ea451f63</t>
+          <t>https://www.indeed.com/viewjob?jk=c423f392a018bf22</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7468c4fe6bdb23</t>
+          <t>https://www.indeed.com/viewjob?jk=cb49af32ea451f63</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a3485c3c6153843</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7468c4fe6bdb23</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef4166ba4aa9b5a3</t>
+          <t>https://www.indeed.com/viewjob?jk=3a3485c3c6153843</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91d6e4beb774dd25</t>
+          <t>https://www.indeed.com/viewjob?jk=ef4166ba4aa9b5a3</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcf2824745a050e</t>
+          <t>https://www.indeed.com/viewjob?jk=91d6e4beb774dd25</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b296145590b995</t>
+          <t>https://www.indeed.com/viewjob?jk=adcf2824745a050e</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c4169879098b22b</t>
+          <t>https://www.indeed.com/viewjob?jk=64b296145590b995</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44e1222f0eb14744</t>
+          <t>https://www.indeed.com/viewjob?jk=8c4169879098b22b</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37bd1a8719f0aafc</t>
+          <t>https://www.indeed.com/viewjob?jk=44e1222f0eb14744</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e151b2c0a32e2723</t>
+          <t>https://www.indeed.com/viewjob?jk=37bd1a8719f0aafc</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c07dcca1b609463e</t>
+          <t>https://www.indeed.com/viewjob?jk=e151b2c0a32e2723</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c721bd4ca7bdffe1</t>
+          <t>https://www.indeed.com/viewjob?jk=c07dcca1b609463e</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8e182c6058fd2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=c721bd4ca7bdffe1</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4997f8f92f05b9d2</t>
+          <t>https://www.indeed.com/viewjob?jk=e8e182c6058fd2a4</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a56481df82d7aa6</t>
+          <t>https://www.indeed.com/viewjob?jk=4997f8f92f05b9d2</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb00c80fb9cb9b65</t>
+          <t>https://www.indeed.com/viewjob?jk=2a56481df82d7aa6</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fd1863254c88e5d</t>
+          <t>https://www.indeed.com/viewjob?jk=fb00c80fb9cb9b65</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Infrastructure</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ALTRUIST</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2b2e3b90367f3b4</t>
+          <t>https://www.indeed.com/viewjob?jk=3fd1863254c88e5d</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15721c69bc524693</t>
+          <t>https://www.indeed.com/viewjob?jk=b2b2e3b90367f3b4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>ALTRUIST</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6c4839e7fe64d8e</t>
+          <t>https://www.indeed.com/viewjob?jk=15721c69bc524693</t>
         </is>
       </c>
     </row>
@@ -2092,11 +2092,11 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17c87f0de0ddb952</t>
+          <t>https://www.indeed.com/viewjob?jk=a6c4839e7fe64d8e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AI/ML Architect with Databricks , AWS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Vytwo Technologies</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Prosper, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,52 +2131,52 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29c402e4a2f5220b</t>
+          <t>https://www.indeed.com/viewjob?jk=17c87f0de0ddb952</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer II,</t>
+          <t>AI/ML Architect with Databricks , AWS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Vytwo Technologies</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Prosper, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4edb591674d441f</t>
+          <t>https://www.indeed.com/viewjob?jk=29c402e4a2f5220b</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28ab3491bb9f5589</t>
+          <t>https://www.indeed.com/viewjob?jk=b4edb591674d441f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Blockchain Java Backend Engineer</t>
+          <t>Software Engineer II,</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Redshift, ECS, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e49019e3e57d794c</t>
+          <t>https://www.indeed.com/viewjob?jk=28ab3491bb9f5589</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Blockchain Java Backend Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0997a11d6aaf4e73</t>
+          <t>https://www.indeed.com/viewjob?jk=e49019e3e57d794c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9188fd233f524c42</t>
+          <t>https://www.indeed.com/viewjob?jk=0997a11d6aaf4e73</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cc63cdd2328277c</t>
+          <t>https://www.indeed.com/viewjob?jk=9188fd233f524c42</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer, AI Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Residex, LLC</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b994e1736909aed</t>
+          <t>https://www.indeed.com/viewjob?jk=4cc63cdd2328277c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. Cloud Software Engineer</t>
+          <t>Software Engineer, AI Analytics</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ELLKAY, LLC</t>
+          <t>Residex, LLC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Elmwood Park, NJ, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,59 +2421,59 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28b63f4ef510667a</t>
+          <t>https://www.indeed.com/viewjob?jk=3b994e1736909aed</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Engineer - DevOps/ DataOps</t>
+          <t>Sr. Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>ELLKAY, LLC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Elmwood Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, DataOps, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Athena, IAM, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ed15cfc823b0b7</t>
+          <t>https://www.indeed.com/viewjob?jk=28b63f4ef510667a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Engineer - DevOps/ DataOps</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, DataOps, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d49d017dead0cec</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ed15cfc823b0b7</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,59 +2526,59 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b08c3dc1b325be49</t>
+          <t>https://www.indeed.com/viewjob?jk=7d49d017dead0cec</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SRS Distribution</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cde050af8749e53</t>
+          <t>https://www.indeed.com/viewjob?jk=b08c3dc1b325be49</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>SRS Distribution</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf6f08ab2860bc5c</t>
+          <t>https://www.indeed.com/viewjob?jk=4cde050af8749e53</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ncontracts</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da52963e4860aaaa</t>
+          <t>https://www.indeed.com/viewjob?jk=bf6f08ab2860bc5c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Incremental CRM - Data Developer 1</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Ncontracts</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Databricks, Scala, SQL Server, ETL</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c7931e975a12585</t>
+          <t>https://www.indeed.com/viewjob?jk=da52963e4860aaaa</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer - Remote</t>
+          <t>Incremental CRM - Data Developer 1</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Databricks, Scala, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,59 +2701,59 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80460d4e824e28cc</t>
+          <t>https://www.indeed.com/viewjob?jk=3c7931e975a12585</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a021dbda97cc3405</t>
+          <t>https://www.indeed.com/viewjob?jk=80460d4e824e28cc</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
+          <t>AWS, Kinesis, IAM, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7ddc3760328a54</t>
+          <t>https://www.indeed.com/viewjob?jk=a021dbda97cc3405</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer + Snowflake (On-Site)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e9f31119d31013</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7ddc3760328a54</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PDM Implementation Data Architect</t>
+          <t>Cloud Data Engineer + Snowflake (On-Site)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, RDS, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3576de9e88dd4c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=58e9f31119d31013</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>PDM Implementation Data Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a6c4ab9efc012e</t>
+          <t>https://www.indeed.com/viewjob?jk=3576de9e88dd4c5c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Hitachi Digital Services</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33510d4bb406c6e2</t>
+          <t>https://www.indeed.com/viewjob?jk=39a6c4ab9efc012e</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ROLLER</t>
+          <t>Hitachi Digital Services</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb709659d664135</t>
+          <t>https://www.indeed.com/viewjob?jk=33510d4bb406c6e2</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer, CDC</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>DRT Strategies, Inc.</t>
+          <t>ROLLER</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Scala, ETL, Power BI, Tableau, CI/CD, Docker</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a223a368864e5d1b</t>
+          <t>https://www.indeed.com/viewjob?jk=afb709659d664135</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SQL Server Database Engineer</t>
+          <t>Data Engineer, CDC</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>IDBNY</t>
+          <t>DRT Strategies, Inc.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, HBase, Snowflake, Oracle, SQL Server, MongoDB</t>
+          <t>AWS, EMR, RDS, Azure, Scala, ETL, Power BI, Tableau, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15c2f3c4f1ddf6ac</t>
+          <t>https://www.indeed.com/viewjob?jk=a223a368864e5d1b</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Cloud Identity Architect</t>
+          <t>SQL Server Database Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>IDBNY</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Databricks, HBase, Snowflake, Oracle, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdd1e41d5949d150</t>
+          <t>https://www.indeed.com/viewjob?jk=15c2f3c4f1ddf6ac</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>System Integration Test Engineer</t>
+          <t>Cloud Identity Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BGIT India Private Limited</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Hudson, NH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=426d1d0d6a93918c</t>
+          <t>https://www.indeed.com/viewjob?jk=fdd1e41d5949d150</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>System Integration Test Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ivo</t>
+          <t>BGIT India Private Limited</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Hudson, NH, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bc5aaef611937ad</t>
+          <t>https://www.indeed.com/viewjob?jk=426d1d0d6a93918c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>ivo</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,69 +3146,69 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd0439895496e24</t>
+          <t>https://www.indeed.com/viewjob?jk=8bc5aaef611937ad</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Halo Creative &amp; Media LLP</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371d6385735b0f59</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd0439895496e24</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-2</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Halo Creative &amp; Media LLP</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f9103ddd4f544e</t>
+          <t>https://www.indeed.com/viewjob?jk=371d6385735b0f59</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Seqster PDM, Inc</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d602908669423e</t>
+          <t>https://www.indeed.com/viewjob?jk=191c0857581cffe3</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>Data Platform Engineer-2</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,17 +3286,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10de5f0ca2f7673d</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f9103ddd4f544e</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6750fd9ad4e72e</t>
+          <t>https://www.indeed.com/viewjob?jk=75d602908669423e</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45db6ac50eb5587</t>
+          <t>https://www.indeed.com/viewjob?jk=10de5f0ca2f7673d</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1c0f7e27e90a87e</t>
+          <t>https://www.indeed.com/viewjob?jk=8e6750fd9ad4e72e</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4dc81e5cd9b6b72</t>
+          <t>https://www.indeed.com/viewjob?jk=c45db6ac50eb5587</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14fea47c1dbfabac</t>
+          <t>https://www.indeed.com/viewjob?jk=d1c0f7e27e90a87e</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02d7bcc2bd0697b0</t>
+          <t>https://www.indeed.com/viewjob?jk=a4dc81e5cd9b6b72</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50e0ff85e5f89851</t>
+          <t>https://www.indeed.com/viewjob?jk=14fea47c1dbfabac</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Risk Data AI/ML Engineer</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=979402388d34b409</t>
+          <t>https://www.indeed.com/viewjob?jk=02d7bcc2bd0697b0</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - AI/ML</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0bc9a390582054</t>
+          <t>https://www.indeed.com/viewjob?jk=50e0ff85e5f89851</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Databricks AI Engineer</t>
+          <t>Risk Data AI/ML Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Powerplan</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5753d39b44c782</t>
+          <t>https://www.indeed.com/viewjob?jk=979402388d34b409</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer II - AI/ML</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ELLKAY, LLC</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Elmwood Park, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Streams/Tasks</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7bfd917914d4728</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0bc9a390582054</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer</t>
+          <t>Senior Databricks AI Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Powerplan</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9886d247b0ec7a02</t>
+          <t>https://www.indeed.com/viewjob?jk=3b5753d39b44c782</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>ELLKAY, LLC</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Elmwood Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
+          <t>AWS, EMR, S3, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Streams/Tasks</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1b9bbef981d9232</t>
+          <t>https://www.indeed.com/viewjob?jk=c7bfd917914d4728</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Network IoT Engineer</t>
+          <t>Sr DevOPS Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da29d3af250447a</t>
+          <t>https://www.indeed.com/viewjob?jk=9886d247b0ec7a02</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Analytics, Full-Stack Engineer</t>
+          <t>Software Engineer - Backend/Cloud Services</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Hunter Industries</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, DynamoDB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24274a4aa989f95</t>
+          <t>https://www.indeed.com/viewjob?jk=ab5afc3cedfad680</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Waters</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Milford, MA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1975adb5bfc7de33</t>
+          <t>https://www.indeed.com/viewjob?jk=e1b9bbef981d9232</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Network IoT Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Santa Barbara, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52fbd92226aade92</t>
+          <t>https://www.indeed.com/viewjob?jk=0da29d3af250447a</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Analytics, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e77317858ff838d</t>
+          <t>https://www.indeed.com/viewjob?jk=c24274a4aa989f95</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>Waters</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Milford, MA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9737f288d965528f</t>
+          <t>https://www.indeed.com/viewjob?jk=1975adb5bfc7de33</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ABCorp NA Inc.</t>
+          <t>PEARLY</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Santa Barbara, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d8f6d93b707b783</t>
+          <t>https://www.indeed.com/viewjob?jk=52fbd92226aade92</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Rogue Community College</t>
+          <t>PEARLY</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Power BI</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f9335cc41b5edf2</t>
+          <t>https://www.indeed.com/viewjob?jk=3e77317858ff838d</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>PEARLY</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e65cdb592eb57da5</t>
+          <t>https://www.indeed.com/viewjob?jk=9737f288d965528f</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>ABCorp NA Inc.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Clarksville, TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,42 +4091,42 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1a1d694cac30055</t>
+          <t>https://www.indeed.com/viewjob?jk=5d8f6d93b707b783</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Rogue Community College</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, Kafka, Dimensional Modeling, ETL, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,94 +4136,94 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503c92a0918e2779</t>
+          <t>https://www.indeed.com/viewjob?jk=7f9335cc41b5edf2</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Engineering Java/Python</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dfc1c1ddf5b07e8</t>
+          <t>https://www.indeed.com/viewjob?jk=e65cdb592eb57da5</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Clarksville, TN, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab7b07d708701fa</t>
+          <t>https://www.indeed.com/viewjob?jk=e1a1d694cac30055</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend) - Global Dining</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, Kafka, Dimensional Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f71d52efce43e2</t>
+          <t>https://www.indeed.com/viewjob?jk=503c92a0918e2779</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Microsoft Fabric</t>
+          <t>Software Engineer III - Data Engineering Java/Python</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>EoS Fitness</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT, Power BI</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bd7f3590528db3c</t>
+          <t>https://www.indeed.com/viewjob?jk=6dfc1c1ddf5b07e8</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>PGA TOUR Superstore</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73bdb2d180484ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=cab7b07d708701fa</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Software Engineer (Backend) - Global Dining</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=110f275787ec7bdb</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f71d52efce43e2</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Platform</t>
+          <t>Senior Data Engineer - Microsoft Fabric</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Middesk</t>
+          <t>EoS Fitness</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Spark, Data Modeling, Terraform, Kubernetes, Airflow, Git</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT, Power BI</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=514717df8eb087ca</t>
+          <t>https://www.indeed.com/viewjob?jk=7bd7f3590528db3c</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Data, Autonomy</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>PGA TOUR Superstore</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3560765ed8e488</t>
+          <t>https://www.indeed.com/viewjob?jk=73bdb2d180484ce2</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Al Warren Oil Company, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bensenville, IL, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6304fa25b90dcc51</t>
+          <t>https://www.indeed.com/viewjob?jk=110f275787ec7bdb</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Al Warren Oil Company, Inc.</t>
+          <t>Middesk</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, Lambda, RDS, Azure, Spark, Data Modeling, Terraform, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a4e15b6a0305b12</t>
+          <t>https://www.indeed.com/viewjob?jk=514717df8eb087ca</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Sr. Software Engineer, Data, Autonomy</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40b321afc8939ff9</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3560765ed8e488</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Cloud Infrastructure Architect</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf4b62fe049b84e</t>
+          <t>https://www.indeed.com/viewjob?jk=518fd46821df25d8</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>Al Warren Oil Company, Inc.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Bensenville, IL, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ca41478bb936cd</t>
+          <t>https://www.indeed.com/viewjob?jk=6304fa25b90dcc51</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Salesforce Architect - Senior</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>CommunityForce Inc.</t>
+          <t>Al Warren Oil Company, Inc.</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d236cba8a6e8ae3</t>
+          <t>https://www.indeed.com/viewjob?jk=9a4e15b6a0305b12</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>.NET Angular Reporting Developer</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, Star Schema, ETL, Power BI, CI/CD, Azure DevOps</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21a948f0ac42414</t>
+          <t>https://www.indeed.com/viewjob?jk=40b321afc8939ff9</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2698e1f59bd5def7</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf4b62fe049b84e</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d0bc94cbe8822db</t>
+          <t>https://www.indeed.com/viewjob?jk=57ca41478bb936cd</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
+          <t>Salesforce Architect - Senior</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>CommunityForce Inc.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Paterson, NJ, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>ECS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75f6d90e6b234f60</t>
+          <t>https://www.indeed.com/viewjob?jk=7d236cba8a6e8ae3</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
+          <t>.NET Angular Reporting Developer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, Star Schema, ETL, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e53f9ddcb5f4c2b9</t>
+          <t>https://www.indeed.com/viewjob?jk=f21a948f0ac42414</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,102 +4836,102 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44fb3987d11d1123</t>
+          <t>https://www.indeed.com/viewjob?jk=2698e1f59bd5def7</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Callaway Golf</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cf949704a694c55</t>
+          <t>https://www.indeed.com/viewjob?jk=4d0bc94cbe8822db</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Microsoft Entra</t>
+          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Paterson, NJ, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f61688604ed96074</t>
+          <t>https://www.indeed.com/viewjob?jk=75f6d90e6b234f60</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Entry-Level Data Engineer</t>
+          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,32 +4941,32 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd80dc2e6636141e</t>
+          <t>https://www.indeed.com/viewjob?jk=e53f9ddcb5f4c2b9</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b5cdc524b199967</t>
+          <t>https://www.indeed.com/viewjob?jk=44fb3987d11d1123</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Westchester Medical Center Health Network</t>
+          <t>Callaway Golf</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Valhalla, NY, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, SQL Server, Data Modeling, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d807a7856ebe08db</t>
+          <t>https://www.indeed.com/viewjob?jk=2cf949704a694c55</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Enterprise Data &amp; Analytics</t>
+          <t>Microsoft Entra</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, Databricks, Data Modeling, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b74ac1e46b3dfa89</t>
+          <t>https://www.indeed.com/viewjob?jk=f61688604ed96074</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SSO Administrator</t>
+          <t>Entry-Level Data Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b109c86f55c8c21f</t>
+          <t>https://www.indeed.com/viewjob?jk=dd80dc2e6636141e</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
+          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=739e08afe4ba1176</t>
+          <t>https://www.indeed.com/viewjob?jk=8b5cdc524b199967</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>IT PROFESSIONAL-APPLICATIONS (Database Administrator) (HEC)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>City of Houston, TX</t>
+          <t>Westchester Medical Center Health Network</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Valhalla, NY, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,34 +5141,34 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Snowflake, SQL Server, Data Modeling, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c369e1e8241c9f</t>
+          <t>https://www.indeed.com/viewjob?jk=d807a7856ebe08db</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>DOCSIS Testing Engineer</t>
+          <t>Sr. Data Engineer, Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, NoSQL, ETL, ELT, Splunk, CI/CD, Docker</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, Databricks, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e134c7566cf151c</t>
+          <t>https://www.indeed.com/viewjob?jk=b74ac1e46b3dfa89</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>SSO Administrator</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=843b039e4e75f61f</t>
+          <t>https://www.indeed.com/viewjob?jk=b109c86f55c8c21f</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ead7f0da7c5db1</t>
+          <t>https://www.indeed.com/viewjob?jk=739e08afe4ba1176</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>IT PROFESSIONAL-APPLICATIONS (Database Administrator) (HEC)</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>City of Houston, TX</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae8a17a1c6f39e3</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c369e1e8241c9f</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>DOCSIS Testing Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,15 +5316,155 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
+          <t>AWS, Azure, Google Cloud Platform, Scala, NoSQL, ETL, ELT, Splunk, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0e134c7566cf151c</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Senior Engineer - .NET</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=843b039e4e75f61f</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Chevy Chase, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1ead7f0da7c5db1</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ae8a17a1c6f39e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Senior Engineer - .NET</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Chevy Chase, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=e5c91aac0db662ae</t>
         </is>

--- a/results/job_matches_2026-03-04.xlsx
+++ b/results/job_matches_2026-03-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G144"/>
+  <dimension ref="A1:G148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Junior Oracle Apps Developer</t>
+          <t>Full Stack Engineer (React + Node.js)-4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, ECS, RDS, Azure, Blob Storage</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0adde35786282b2b</t>
+          <t>https://www.indeed.com/viewjob?jk=e082e26fc29250a3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (React + Node.js)-4</t>
+          <t>Junior Oracle Apps Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, ECS, RDS, Azure, Blob Storage</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e082e26fc29250a3</t>
+          <t>https://www.indeed.com/viewjob?jk=0adde35786282b2b</t>
         </is>
       </c>
     </row>
@@ -2008,17 +2008,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Infrastructure</t>
+          <t>Sr. Data Platform Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ALTRUIST</t>
+          <t>Real Time Medical Systems</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2b2e3b90367f3b4</t>
+          <t>https://www.indeed.com/viewjob?jk=415686b53cfda723</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Infrastructure</t>
+          <t>Sr. Data Platform Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ALTRUIST</t>
+          <t>Real Time Medical Systems</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15721c69bc524693</t>
+          <t>https://www.indeed.com/viewjob?jk=41a92f9802d4f918</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>ALTRUIST</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,122 +2096,122 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6c4839e7fe64d8e</t>
+          <t>https://www.indeed.com/viewjob?jk=b2b2e3b90367f3b4</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>ALTRUIST</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17c87f0de0ddb952</t>
+          <t>https://www.indeed.com/viewjob?jk=15721c69bc524693</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AI/ML Architect with Databricks , AWS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Vytwo Technologies</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Prosper, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29c402e4a2f5220b</t>
+          <t>https://www.indeed.com/viewjob?jk=a6c4839e7fe64d8e</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer II,</t>
+          <t>AI/ML Architect with Databricks , AWS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Vytwo Technologies</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Prosper, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4edb591674d441f</t>
+          <t>https://www.indeed.com/viewjob?jk=29c402e4a2f5220b</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28ab3491bb9f5589</t>
+          <t>https://www.indeed.com/viewjob?jk=b4edb591674d441f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Blockchain Java Backend Engineer</t>
+          <t>Software Engineer II,</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Redshift, ECS, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e49019e3e57d794c</t>
+          <t>https://www.indeed.com/viewjob?jk=28ab3491bb9f5589</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Blockchain Java Backend Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0997a11d6aaf4e73</t>
+          <t>https://www.indeed.com/viewjob?jk=e49019e3e57d794c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9188fd233f524c42</t>
+          <t>https://www.indeed.com/viewjob?jk=0997a11d6aaf4e73</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cc63cdd2328277c</t>
+          <t>https://www.indeed.com/viewjob?jk=9188fd233f524c42</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer, AI Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Residex, LLC</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b994e1736909aed</t>
+          <t>https://www.indeed.com/viewjob?jk=4cc63cdd2328277c</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. Cloud Software Engineer</t>
+          <t>Google Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ELLKAY, LLC</t>
+          <t>NMI</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Elmwood Park, NJ, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,69 +2446,69 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28b63f4ef510667a</t>
+          <t>https://www.indeed.com/viewjob?jk=e7cac4b03aa7cfe7</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Engineer - DevOps/ DataOps</t>
+          <t>Software Engineer, AI Analytics</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>Residex, LLC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, DataOps, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ed15cfc823b0b7</t>
+          <t>https://www.indeed.com/viewjob?jk=3b994e1736909aed</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Engineer - DevOps/ DataOps</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, DataOps, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d49d017dead0cec</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ed15cfc823b0b7</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,59 +2561,59 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b08c3dc1b325be49</t>
+          <t>https://www.indeed.com/viewjob?jk=7d49d017dead0cec</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SRS Distribution</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cde050af8749e53</t>
+          <t>https://www.indeed.com/viewjob?jk=b08c3dc1b325be49</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>SRS Distribution</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf6f08ab2860bc5c</t>
+          <t>https://www.indeed.com/viewjob?jk=4cde050af8749e53</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ncontracts</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da52963e4860aaaa</t>
+          <t>https://www.indeed.com/viewjob?jk=bf6f08ab2860bc5c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Incremental CRM - Data Developer 1</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Ncontracts</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Databricks, Scala, SQL Server, ETL</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c7931e975a12585</t>
+          <t>https://www.indeed.com/viewjob?jk=da52963e4860aaaa</t>
         </is>
       </c>
     </row>
@@ -2743,52 +2743,52 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Incremental CRM - Data Developer 1</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Databricks, Scala, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a021dbda97cc3405</t>
+          <t>https://www.indeed.com/viewjob?jk=3c7931e975a12585</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
+          <t>AWS, Kinesis, IAM, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7ddc3760328a54</t>
+          <t>https://www.indeed.com/viewjob?jk=a021dbda97cc3405</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer + Snowflake (On-Site)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e9f31119d31013</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7ddc3760328a54</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PDM Implementation Data Architect</t>
+          <t>Cloud Data Engineer + Snowflake (On-Site)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, RDS, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3576de9e88dd4c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=58e9f31119d31013</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>PDM Implementation Data Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a6c4ab9efc012e</t>
+          <t>https://www.indeed.com/viewjob?jk=3576de9e88dd4c5c</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Hitachi Digital Services</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33510d4bb406c6e2</t>
+          <t>https://www.indeed.com/viewjob?jk=39a6c4ab9efc012e</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ROLLER</t>
+          <t>Hitachi Digital Services</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb709659d664135</t>
+          <t>https://www.indeed.com/viewjob?jk=33510d4bb406c6e2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer, CDC</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>DRT Strategies, Inc.</t>
+          <t>ROLLER</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Scala, ETL, Power BI, Tableau, CI/CD, Docker</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a223a368864e5d1b</t>
+          <t>https://www.indeed.com/viewjob?jk=afb709659d664135</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SQL Server Database Engineer</t>
+          <t>Data Engineer, CDC</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>IDBNY</t>
+          <t>DRT Strategies, Inc.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, HBase, Snowflake, Oracle, SQL Server, MongoDB</t>
+          <t>AWS, EMR, RDS, Azure, Scala, ETL, Power BI, Tableau, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15c2f3c4f1ddf6ac</t>
+          <t>https://www.indeed.com/viewjob?jk=a223a368864e5d1b</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Cloud Identity Architect</t>
+          <t>SQL Server Database Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>IDBNY</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Databricks, HBase, Snowflake, Oracle, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdd1e41d5949d150</t>
+          <t>https://www.indeed.com/viewjob?jk=15c2f3c4f1ddf6ac</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>System Integration Test Engineer</t>
+          <t>Cloud Identity Architect</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BGIT India Private Limited</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hudson, NH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=426d1d0d6a93918c</t>
+          <t>https://www.indeed.com/viewjob?jk=fdd1e41d5949d150</t>
         </is>
       </c>
     </row>
@@ -3198,17 +3198,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Halo Creative &amp; Media LLP</t>
+          <t>SRR Consultants</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371d6385735b0f59</t>
+          <t>https://www.indeed.com/viewjob?jk=88619a1e983eef30</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AWS DevOps Engineer</t>
+          <t>Senior Data Engineer, Data Lakehouse Infrastructure</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Seqster PDM, Inc</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=191c0857581cffe3</t>
+          <t>https://www.indeed.com/viewjob?jk=e899ea40640da235</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-2</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Halo Creative &amp; Media LLP</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f9103ddd4f544e</t>
+          <t>https://www.indeed.com/viewjob?jk=371d6385735b0f59</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Seqster PDM, Inc</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d602908669423e</t>
+          <t>https://www.indeed.com/viewjob?jk=191c0857581cffe3</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>Data Platform Engineer-2</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,17 +3356,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10de5f0ca2f7673d</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f9103ddd4f544e</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6750fd9ad4e72e</t>
+          <t>https://www.indeed.com/viewjob?jk=75d602908669423e</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45db6ac50eb5587</t>
+          <t>https://www.indeed.com/viewjob?jk=10de5f0ca2f7673d</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1c0f7e27e90a87e</t>
+          <t>https://www.indeed.com/viewjob?jk=8e6750fd9ad4e72e</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4dc81e5cd9b6b72</t>
+          <t>https://www.indeed.com/viewjob?jk=c45db6ac50eb5587</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14fea47c1dbfabac</t>
+          <t>https://www.indeed.com/viewjob?jk=d1c0f7e27e90a87e</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02d7bcc2bd0697b0</t>
+          <t>https://www.indeed.com/viewjob?jk=a4dc81e5cd9b6b72</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50e0ff85e5f89851</t>
+          <t>https://www.indeed.com/viewjob?jk=14fea47c1dbfabac</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Risk Data AI/ML Engineer</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=979402388d34b409</t>
+          <t>https://www.indeed.com/viewjob?jk=02d7bcc2bd0697b0</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - AI/ML</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0bc9a390582054</t>
+          <t>https://www.indeed.com/viewjob?jk=50e0ff85e5f89851</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Databricks AI Engineer</t>
+          <t>Risk Data AI/ML Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Powerplan</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5753d39b44c782</t>
+          <t>https://www.indeed.com/viewjob?jk=979402388d34b409</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer II - AI/ML</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ELLKAY, LLC</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Elmwood Park, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Streams/Tasks</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7bfd917914d4728</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0bc9a390582054</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer</t>
+          <t>Senior Databricks AI Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Powerplan</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9886d247b0ec7a02</t>
+          <t>https://www.indeed.com/viewjob?jk=3b5753d39b44c782</t>
         </is>
       </c>
     </row>
@@ -3898,17 +3898,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Analytics, Full-Stack Engineer</t>
+          <t>Senior Data Engineer, Data Product</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24274a4aa989f95</t>
+          <t>https://www.indeed.com/viewjob?jk=351b720407fa6f6d</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Analytics, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Waters</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Milford, MA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1975adb5bfc7de33</t>
+          <t>https://www.indeed.com/viewjob?jk=c24274a4aa989f95</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>Waters</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Santa Barbara, CA, US USA</t>
+          <t>Milford, MA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52fbd92226aade92</t>
+          <t>https://www.indeed.com/viewjob?jk=1975adb5bfc7de33</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e77317858ff838d</t>
+          <t>https://www.indeed.com/viewjob?jk=a8b55e090bbab627</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9737f288d965528f</t>
+          <t>https://www.indeed.com/viewjob?jk=e65cdb592eb57da5</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ABCorp NA Inc.</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Clarksville, TN, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,17 +4091,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d8f6d93b707b783</t>
+          <t>https://www.indeed.com/viewjob?jk=e1a1d694cac30055</t>
         </is>
       </c>
     </row>
@@ -4143,25 +4143,25 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e65cdb592eb57da5</t>
+          <t>https://www.indeed.com/viewjob?jk=8a517be0e10b2a44</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Senior Data Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Clarksville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1a1d694cac30055</t>
+          <t>https://www.indeed.com/viewjob?jk=60f6c2aecd2d1bdf</t>
         </is>
       </c>
     </row>
@@ -4353,17 +4353,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Microsoft Fabric</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>EoS Fitness</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT, Power BI</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bd7f3590528db3c</t>
+          <t>https://www.indeed.com/viewjob?jk=7f3534222ab81e17</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Microsoft Fabric</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>PGA TOUR Superstore</t>
+          <t>EoS Fitness</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT, Power BI</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73bdb2d180484ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=7bd7f3590528db3c</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>PGA TOUR Superstore</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=110f275787ec7bdb</t>
+          <t>https://www.indeed.com/viewjob?jk=73bdb2d180484ce2</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Platform</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Middesk</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Spark, Data Modeling, Terraform, Kubernetes, Airflow, Git</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=514717df8eb087ca</t>
+          <t>https://www.indeed.com/viewjob?jk=110f275787ec7bdb</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Data, Autonomy</t>
+          <t>Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Middesk</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, RDS, Azure, Spark, Data Modeling, Terraform, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3560765ed8e488</t>
+          <t>https://www.indeed.com/viewjob?jk=514717df8eb087ca</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Architect</t>
+          <t>Sr. Software Engineer, Data, Autonomy</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=518fd46821df25d8</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3560765ed8e488</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Cloud Infrastructure Architect</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Al Warren Oil Company, Inc.</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bensenville, IL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6304fa25b90dcc51</t>
+          <t>https://www.indeed.com/viewjob?jk=518fd46821df25d8</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bensenville, IL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a4e15b6a0305b12</t>
+          <t>https://www.indeed.com/viewjob?jk=6304fa25b90dcc51</t>
         </is>
       </c>
     </row>
@@ -4638,12 +4638,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>Al Warren Oil Company, Inc.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40b321afc8939ff9</t>
+          <t>https://www.indeed.com/viewjob?jk=9a4e15b6a0305b12</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf4b62fe049b84e</t>
+          <t>https://www.indeed.com/viewjob?jk=40b321afc8939ff9</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ca41478bb936cd</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf4b62fe049b84e</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Salesforce Architect - Senior</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>CommunityForce Inc.</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d236cba8a6e8ae3</t>
+          <t>https://www.indeed.com/viewjob?jk=57ca41478bb936cd</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>.NET Angular Reporting Developer</t>
+          <t>Salesforce Architect - Senior</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CommunityForce Inc.</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, Star Schema, ETL, Power BI, CI/CD, Azure DevOps</t>
+          <t>ECS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21a948f0ac42414</t>
+          <t>https://www.indeed.com/viewjob?jk=7d236cba8a6e8ae3</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
+          <t>.NET Angular Reporting Developer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, Star Schema, ETL, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2698e1f59bd5def7</t>
+          <t>https://www.indeed.com/viewjob?jk=f21a948f0ac42414</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d0bc94cbe8822db</t>
+          <t>https://www.indeed.com/viewjob?jk=2698e1f59bd5def7</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Paterson, NJ, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75f6d90e6b234f60</t>
+          <t>https://www.indeed.com/viewjob?jk=4d0bc94cbe8822db</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>Paterson, NJ, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e53f9ddcb5f4c2b9</t>
+          <t>https://www.indeed.com/viewjob?jk=75f6d90e6b234f60</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,59 +4976,59 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44fb3987d11d1123</t>
+          <t>https://www.indeed.com/viewjob?jk=e53f9ddcb5f4c2b9</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Callaway Golf</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cf949704a694c55</t>
+          <t>https://www.indeed.com/viewjob?jk=44fb3987d11d1123</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Microsoft Entra</t>
+          <t>Software Engineer - Master</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f61688604ed96074</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb1207979169793</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Entry-Level Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd80dc2e6636141e</t>
+          <t>https://www.indeed.com/viewjob?jk=dcb7ea8003fbc5dc</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>Callaway Golf</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b5cdc524b199967</t>
+          <t>https://www.indeed.com/viewjob?jk=2cf949704a694c55</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Microsoft Entra</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Westchester Medical Center Health Network</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Valhalla, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,34 +5141,34 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, SQL Server, Data Modeling, ELT, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d807a7856ebe08db</t>
+          <t>https://www.indeed.com/viewjob?jk=f61688604ed96074</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Enterprise Data &amp; Analytics</t>
+          <t>Entry-Level Data Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, Databricks, Data Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b74ac1e46b3dfa89</t>
+          <t>https://www.indeed.com/viewjob?jk=dd80dc2e6636141e</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>SSO Administrator</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
+          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b109c86f55c8c21f</t>
+          <t>https://www.indeed.com/viewjob?jk=8b5cdc524b199967</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>Westchester Medical Center Health Network</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Valhalla, NY, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,34 +5246,34 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Snowflake, SQL Server, Data Modeling, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=739e08afe4ba1176</t>
+          <t>https://www.indeed.com/viewjob?jk=d807a7856ebe08db</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>IT PROFESSIONAL-APPLICATIONS (Database Administrator) (HEC)</t>
+          <t>Sr. Data Engineer, Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>City of Houston, TX</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, Databricks, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c369e1e8241c9f</t>
+          <t>https://www.indeed.com/viewjob?jk=b74ac1e46b3dfa89</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>DOCSIS Testing Engineer</t>
+          <t>Senior Data Engineer, Attribution Expansion</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,34 +5316,34 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, NoSQL, ETL, ELT, Splunk, CI/CD, Docker</t>
+          <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e134c7566cf151c</t>
+          <t>https://www.indeed.com/viewjob?jk=539a18aebac4ef5f</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Senior Data Engineer, Attribution Expansion</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,34 +5351,34 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=843b039e4e75f61f</t>
+          <t>https://www.indeed.com/viewjob?jk=26436308d22e947d</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>SSO Administrator</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,14 +5396,14 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ead7f0da7c5db1</t>
+          <t>https://www.indeed.com/viewjob?jk=b109c86f55c8c21f</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,14 +5431,14 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae8a17a1c6f39e3</t>
+          <t>https://www.indeed.com/viewjob?jk=843b039e4e75f61f</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5456,17 +5456,157 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1ead7f0da7c5db1</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ae8a17a1c6f39e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Senior Engineer - .NET</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Chevy Chase, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=e5c91aac0db662ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>IT PROFESSIONAL-APPLICATIONS (Database Administrator) (HEC)</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>City of Houston, TX</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1c369e1e8241c9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>DOCSIS Testing Engineer</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, Scala, NoSQL, ETL, ELT, Splunk, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0e134c7566cf151c</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-04.xlsx
+++ b/results/job_matches_2026-03-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G148"/>
+  <dimension ref="A1:G150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,35 +468,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer in Test III - Data Analytics</t>
+          <t>Junior Oracle Apps Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Emburse</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.5</v>
+        <v>20.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, ECS, RDS, Azure, Blob Storage</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=450782bf82b6fc2f</t>
+          <t>https://www.indeed.com/viewjob?jk=0adde35786282b2b</t>
         </is>
       </c>
     </row>
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Junior Oracle Apps Developer</t>
+          <t>Software Engineer III: DevOps</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, ECS, RDS, Azure, Blob Storage</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0adde35786282b2b</t>
+          <t>https://www.indeed.com/viewjob?jk=bc952e4224a3aa24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer III: DevOps</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Jersey Mikes Corporate</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Tinton Falls, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc952e4224a3aa24</t>
+          <t>https://www.indeed.com/viewjob?jk=31cf41e0387f0b72</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer, Client Authentication</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jersey Mikes Corporate</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tinton Falls, NJ, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>IAM, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31cf41e0387f0b72</t>
+          <t>https://www.indeed.com/viewjob?jk=a908b362cb914674</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Client Authentication</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Quilt</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a908b362cb914674</t>
+          <t>https://www.indeed.com/viewjob?jk=27d883fd388e687a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer, ACVMax</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Quilt</t>
+          <t>ACV Auctions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d883fd388e687a</t>
+          <t>https://www.indeed.com/viewjob?jk=6c28dd5d00192a5b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, ACVMax</t>
+          <t>Data Engineer - AI Practice Team</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ACV Auctions</t>
+          <t>American Bureau of Shipping (ABS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,29 +766,29 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Azure, Data Factory, Databricks, Event Hubs, BigQuery</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c28dd5d00192a5b</t>
+          <t>https://www.indeed.com/viewjob?jk=98e9bc7cd1938bfd</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer - AI Practice Team</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>American Bureau of Shipping (ABS)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Azure, Data Factory, Databricks, Event Hubs, BigQuery</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98e9bc7cd1938bfd</t>
+          <t>https://www.indeed.com/viewjob?jk=7167050c109be2d4</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7167050c109be2d4</t>
+          <t>https://www.indeed.com/viewjob?jk=862a4a8989448fa0</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=862a4a8989448fa0</t>
+          <t>https://www.indeed.com/viewjob?jk=07e542bb4713fad0</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07e542bb4713fad0</t>
+          <t>https://www.indeed.com/viewjob?jk=2c88dff775194e30</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c88dff775194e30</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ced45fe117deb8</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ced45fe117deb8</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc8e0c810b3e7cd</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc8e0c810b3e7cd</t>
+          <t>https://www.indeed.com/viewjob?jk=7791942c877daada</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7791942c877daada</t>
+          <t>https://www.indeed.com/viewjob?jk=b6b39b9b56abc0bd</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6b39b9b56abc0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=648774ee33ca3b76</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648774ee33ca3b76</t>
+          <t>https://www.indeed.com/viewjob?jk=a93ca1ad887e17f0</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a93ca1ad887e17f0</t>
+          <t>https://www.indeed.com/viewjob?jk=d963e90dfb3fa4d6</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d963e90dfb3fa4d6</t>
+          <t>https://www.indeed.com/viewjob?jk=783ac47e6d62e414</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783ac47e6d62e414</t>
+          <t>https://www.indeed.com/viewjob?jk=e511c7108cd6e82d</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e511c7108cd6e82d</t>
+          <t>https://www.indeed.com/viewjob?jk=2a6a2ad30fc1236d</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a6a2ad30fc1236d</t>
+          <t>https://www.indeed.com/viewjob?jk=e2d42f6d55a07b48</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2d42f6d55a07b48</t>
+          <t>https://www.indeed.com/viewjob?jk=c423f392a018bf22</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c423f392a018bf22</t>
+          <t>https://www.indeed.com/viewjob?jk=cb49af32ea451f63</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb49af32ea451f63</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7468c4fe6bdb23</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7468c4fe6bdb23</t>
+          <t>https://www.indeed.com/viewjob?jk=3a3485c3c6153843</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a3485c3c6153843</t>
+          <t>https://www.indeed.com/viewjob?jk=ef4166ba4aa9b5a3</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef4166ba4aa9b5a3</t>
+          <t>https://www.indeed.com/viewjob?jk=91d6e4beb774dd25</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91d6e4beb774dd25</t>
+          <t>https://www.indeed.com/viewjob?jk=adcf2824745a050e</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcf2824745a050e</t>
+          <t>https://www.indeed.com/viewjob?jk=64b296145590b995</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b296145590b995</t>
+          <t>https://www.indeed.com/viewjob?jk=8c4169879098b22b</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c4169879098b22b</t>
+          <t>https://www.indeed.com/viewjob?jk=44e1222f0eb14744</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44e1222f0eb14744</t>
+          <t>https://www.indeed.com/viewjob?jk=37bd1a8719f0aafc</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37bd1a8719f0aafc</t>
+          <t>https://www.indeed.com/viewjob?jk=e151b2c0a32e2723</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e151b2c0a32e2723</t>
+          <t>https://www.indeed.com/viewjob?jk=c07dcca1b609463e</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c07dcca1b609463e</t>
+          <t>https://www.indeed.com/viewjob?jk=c721bd4ca7bdffe1</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c721bd4ca7bdffe1</t>
+          <t>https://www.indeed.com/viewjob?jk=e8e182c6058fd2a4</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8e182c6058fd2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=4997f8f92f05b9d2</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4997f8f92f05b9d2</t>
+          <t>https://www.indeed.com/viewjob?jk=2a56481df82d7aa6</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a56481df82d7aa6</t>
+          <t>https://www.indeed.com/viewjob?jk=fb00c80fb9cb9b65</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb00c80fb9cb9b65</t>
+          <t>https://www.indeed.com/viewjob?jk=3fd1863254c88e5d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Sr. Data Platform Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Real Time Medical Systems</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fd1863254c88e5d</t>
+          <t>https://www.indeed.com/viewjob?jk=415686b53cfda723</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=415686b53cfda723</t>
+          <t>https://www.indeed.com/viewjob?jk=41a92f9802d4f918</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Data Platform Engineer</t>
+          <t>Senior Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Real Time Medical Systems</t>
+          <t>ALTRUIST</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41a92f9802d4f918</t>
+          <t>https://www.indeed.com/viewjob?jk=b2b2e3b90367f3b4</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2b2e3b90367f3b4</t>
+          <t>https://www.indeed.com/viewjob?jk=15721c69bc524693</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Infrastructure</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ALTRUIST</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,52 +2131,52 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15721c69bc524693</t>
+          <t>https://www.indeed.com/viewjob?jk=a6c4839e7fe64d8e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI/ML Architect with Databricks , AWS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Prosper, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables</t>
+          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6c4839e7fe64d8e</t>
+          <t>https://www.indeed.com/viewjob?jk=5774b4765e1a54ce</t>
         </is>
       </c>
     </row>
@@ -2218,35 +2218,35 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer II,</t>
+          <t>aws Databricks architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Cloudious</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4edb591674d441f</t>
+          <t>https://www.indeed.com/viewjob?jk=03a1eccc5605f732</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28ab3491bb9f5589</t>
+          <t>https://www.indeed.com/viewjob?jk=b4edb591674d441f</t>
         </is>
       </c>
     </row>
@@ -2533,17 +2533,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,59 +2561,59 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d49d017dead0cec</t>
+          <t>https://www.indeed.com/viewjob?jk=b08c3dc1b325be49</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>SRS Distribution</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b08c3dc1b325be49</t>
+          <t>https://www.indeed.com/viewjob?jk=4cde050af8749e53</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>SQL Developer - Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SRS Distribution</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cde050af8749e53</t>
+          <t>https://www.indeed.com/viewjob?jk=41d495363374161e</t>
         </is>
       </c>
     </row>
@@ -2708,17 +2708,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer - Remote</t>
+          <t>Incremental CRM - Data Developer 1</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Databricks, Scala, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,59 +2736,59 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80460d4e824e28cc</t>
+          <t>https://www.indeed.com/viewjob?jk=3c7931e975a12585</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Incremental CRM - Data Developer 1</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Databricks, Scala, SQL Server, ETL</t>
+          <t>AWS, Kinesis, IAM, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c7931e975a12585</t>
+          <t>https://www.indeed.com/viewjob?jk=a021dbda97cc3405</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a021dbda97cc3405</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7ddc3760328a54</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Cloud Data Engineer + Snowflake (On-Site)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
+          <t>AWS, Glue, EMR, RDS, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7ddc3760328a54</t>
+          <t>https://www.indeed.com/viewjob?jk=58e9f31119d31013</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer + Snowflake (On-Site)</t>
+          <t>PDM Implementation Data Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e9f31119d31013</t>
+          <t>https://www.indeed.com/viewjob?jk=3576de9e88dd4c5c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PDM Implementation Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Hitachi Digital Services</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3576de9e88dd4c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=33510d4bb406c6e2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>ROLLER</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a6c4ab9efc012e</t>
+          <t>https://www.indeed.com/viewjob?jk=afb709659d664135</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer, CDC</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Hitachi Digital Services</t>
+          <t>DRT Strategies, Inc.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala</t>
+          <t>AWS, EMR, RDS, Azure, Scala, ETL, Power BI, Tableau, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33510d4bb406c6e2</t>
+          <t>https://www.indeed.com/viewjob?jk=a223a368864e5d1b</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SQL Server Database Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ROLLER</t>
+          <t>IDBNY</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Databricks, HBase, Snowflake, Oracle, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb709659d664135</t>
+          <t>https://www.indeed.com/viewjob?jk=15c2f3c4f1ddf6ac</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer, CDC</t>
+          <t>Cloud Identity Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>DRT Strategies, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Scala, ETL, Power BI, Tableau, CI/CD, Docker</t>
+          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a223a368864e5d1b</t>
+          <t>https://www.indeed.com/viewjob?jk=fdd1e41d5949d150</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SQL Server Database Engineer</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>IDBNY</t>
+          <t>ivo</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, HBase, Snowflake, Oracle, SQL Server, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15c2f3c4f1ddf6ac</t>
+          <t>https://www.indeed.com/viewjob?jk=8bc5aaef611937ad</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cloud Identity Architect</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdd1e41d5949d150</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd0439895496e24</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ivo</t>
+          <t>Recursion Technologies, Inc</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,59 +3156,59 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bc5aaef611937ad</t>
+          <t>https://www.indeed.com/viewjob?jk=6138105d361c110c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>SRR Consultants</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd0439895496e24</t>
+          <t>https://www.indeed.com/viewjob?jk=88619a1e983eef30</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer, Data Lakehouse Infrastructure</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SRR Consultants</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88619a1e983eef30</t>
+          <t>https://www.indeed.com/viewjob?jk=e899ea40640da235</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Lakehouse Infrastructure</t>
+          <t>AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Seqster PDM, Inc</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e899ea40640da235</t>
+          <t>https://www.indeed.com/viewjob?jk=191c0857581cffe3</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Platform Engineer-2</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Halo Creative &amp; Media LLP</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371d6385735b0f59</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f9103ddd4f544e</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AWS DevOps Engineer</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Seqster PDM, Inc</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=191c0857581cffe3</t>
+          <t>https://www.indeed.com/viewjob?jk=75d602908669423e</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-2</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,17 +3356,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f9103ddd4f544e</t>
+          <t>https://www.indeed.com/viewjob?jk=10de5f0ca2f7673d</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d602908669423e</t>
+          <t>https://www.indeed.com/viewjob?jk=8e6750fd9ad4e72e</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10de5f0ca2f7673d</t>
+          <t>https://www.indeed.com/viewjob?jk=c45db6ac50eb5587</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6750fd9ad4e72e</t>
+          <t>https://www.indeed.com/viewjob?jk=d1c0f7e27e90a87e</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45db6ac50eb5587</t>
+          <t>https://www.indeed.com/viewjob?jk=a4dc81e5cd9b6b72</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1c0f7e27e90a87e</t>
+          <t>https://www.indeed.com/viewjob?jk=14fea47c1dbfabac</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4dc81e5cd9b6b72</t>
+          <t>https://www.indeed.com/viewjob?jk=02d7bcc2bd0697b0</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14fea47c1dbfabac</t>
+          <t>https://www.indeed.com/viewjob?jk=50e0ff85e5f89851</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>UP Management LLC</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bedford, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02d7bcc2bd0697b0</t>
+          <t>https://www.indeed.com/viewjob?jk=2e000e4c87bc0a4b</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>Risk Data AI/ML Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50e0ff85e5f89851</t>
+          <t>https://www.indeed.com/viewjob?jk=979402388d34b409</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Risk Data AI/ML Engineer</t>
+          <t>Senior Databricks AI Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Powerplan</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,17 +3706,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=979402388d34b409</t>
+          <t>https://www.indeed.com/viewjob?jk=3b5753d39b44c782</t>
         </is>
       </c>
     </row>
@@ -3758,17 +3758,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Databricks AI Engineer</t>
+          <t>Software Engineer - Backend/Cloud Services</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Powerplan</t>
+          <t>Hunter Industries</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,69 +3776,69 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, DynamoDB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5753d39b44c782</t>
+          <t>https://www.indeed.com/viewjob?jk=ab5afc3cedfad680</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend/Cloud Services</t>
+          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Hunter Industries</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, DynamoDB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab5afc3cedfad680</t>
+          <t>https://www.indeed.com/viewjob?jk=e1b9bbef981d9232</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
+          <t>Network IoT Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1b9bbef981d9232</t>
+          <t>https://www.indeed.com/viewjob?jk=0da29d3af250447a</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Network IoT Engineer</t>
+          <t>Senior Data Engineer, Data Product</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da29d3af250447a</t>
+          <t>https://www.indeed.com/viewjob?jk=351b720407fa6f6d</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Product</t>
+          <t>Analytics, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351b720407fa6f6d</t>
+          <t>https://www.indeed.com/viewjob?jk=c24274a4aa989f95</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Analytics, Full-Stack Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Waters</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Milford, MA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24274a4aa989f95</t>
+          <t>https://www.indeed.com/viewjob?jk=1975adb5bfc7de33</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Waters</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Milford, MA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1975adb5bfc7de33</t>
+          <t>https://www.indeed.com/viewjob?jk=a8b55e090bbab627</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, Google Cloud Platform, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8b55e090bbab627</t>
+          <t>https://www.indeed.com/viewjob?jk=be47bff9f1c0f69d</t>
         </is>
       </c>
     </row>
@@ -4143,25 +4143,25 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Senior Software Engineer (Backend)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>PlanHub</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, Scala, MySQL, DynamoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,14 +4171,14 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a517be0e10b2a44</t>
+          <t>https://www.indeed.com/viewjob?jk=b63efe5dfc4a026c</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Platform</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f6c2aecd2d1bdf</t>
+          <t>https://www.indeed.com/viewjob?jk=8a517be0e10b2a44</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Data Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, Kafka, Dimensional Modeling, ETL, Airflow</t>
+          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503c92a0918e2779</t>
+          <t>https://www.indeed.com/viewjob?jk=60f6c2aecd2d1bdf</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Engineering Java/Python</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
+          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, Kafka, Dimensional Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dfc1c1ddf5b07e8</t>
+          <t>https://www.indeed.com/viewjob?jk=503c92a0918e2779</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>Software Engineer III - Data Engineering Java/Python</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab7b07d708701fa</t>
+          <t>https://www.indeed.com/viewjob?jk=6dfc1c1ddf5b07e8</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend) - Global Dining</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f71d52efce43e2</t>
+          <t>https://www.indeed.com/viewjob?jk=cab7b07d708701fa</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Software Engineer (Backend) - Global Dining</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f3534222ab81e17</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f71d52efce43e2</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Microsoft Fabric</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>EoS Fitness</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT, Power BI</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bd7f3590528db3c</t>
+          <t>https://www.indeed.com/viewjob?jk=7f3534222ab81e17</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>PGA TOUR Superstore</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73bdb2d180484ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=e5b3837921976566</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior Data Engineer - Microsoft Fabric</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>EoS Fitness</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT, Power BI</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=110f275787ec7bdb</t>
+          <t>https://www.indeed.com/viewjob?jk=7bd7f3590528db3c</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Middesk</t>
+          <t>PGA TOUR Superstore</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Spark, Data Modeling, Terraform, Kubernetes, Airflow, Git</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=514717df8eb087ca</t>
+          <t>https://www.indeed.com/viewjob?jk=73bdb2d180484ce2</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Data, Autonomy</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, DynamoDB, CI/CD</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3560765ed8e488</t>
+          <t>https://www.indeed.com/viewjob?jk=110f275787ec7bdb</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Architect</t>
+          <t>Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Middesk</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, RDS, Azure, Spark, Data Modeling, Terraform, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=518fd46821df25d8</t>
+          <t>https://www.indeed.com/viewjob?jk=514717df8eb087ca</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Sr. Software Engineer, Data, Autonomy</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Al Warren Oil Company, Inc.</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Bensenville, IL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6304fa25b90dcc51</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3560765ed8e488</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Cloud Infrastructure Architect</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Al Warren Oil Company, Inc.</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a4e15b6a0305b12</t>
+          <t>https://www.indeed.com/viewjob?jk=518fd46821df25d8</t>
         </is>
       </c>
     </row>
@@ -4673,12 +4673,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>Al Warren Oil Company, Inc.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Bensenville, IL, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40b321afc8939ff9</t>
+          <t>https://www.indeed.com/viewjob?jk=6304fa25b90dcc51</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Al Warren Oil Company, Inc.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf4b62fe049b84e</t>
+          <t>https://www.indeed.com/viewjob?jk=9a4e15b6a0305b12</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,17 +4756,17 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ca41478bb936cd</t>
+          <t>https://www.indeed.com/viewjob?jk=40b321afc8939ff9</t>
         </is>
       </c>
     </row>
@@ -4808,17 +4808,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>.NET Angular Reporting Developer</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, Star Schema, ETL, Power BI, CI/CD, Azure DevOps</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21a948f0ac42414</t>
+          <t>https://www.indeed.com/viewjob?jk=176afb0ac80a4191</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
+          <t>Senior Database Reliability Engineer (Oracle &amp; Automation Focus)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>BILL</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>AWS, ECS, RDS, Oracle, DynamoDB, NoSQL, Splunk, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2698e1f59bd5def7</t>
+          <t>https://www.indeed.com/viewjob?jk=104eb630cab2bc86</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d0bc94cbe8822db</t>
+          <t>https://www.indeed.com/viewjob?jk=57ca41478bb936cd</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Paterson, NJ, US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75f6d90e6b234f60</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf4b62fe049b84e</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
+          <t>.NET Angular Reporting Developer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, Star Schema, ETL, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,59 +4976,59 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e53f9ddcb5f4c2b9</t>
+          <t>https://www.indeed.com/viewjob?jk=f21a948f0ac42414</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
+          <t>Software Engineer - Master</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44fb3987d11d1123</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb1207979169793</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Software Engineer - Master</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb1207979169793</t>
+          <t>https://www.indeed.com/viewjob?jk=dcb7ea8003fbc5dc</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Callaway Golf</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcb7ea8003fbc5dc</t>
+          <t>https://www.indeed.com/viewjob?jk=2cf949704a694c55</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Microsoft Entra</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Callaway Golf</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cf949704a694c55</t>
+          <t>https://www.indeed.com/viewjob?jk=f61688604ed96074</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Microsoft Entra</t>
+          <t>Entry-Level Data Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,34 +5141,34 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f61688604ed96074</t>
+          <t>https://www.indeed.com/viewjob?jk=dd80dc2e6636141e</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Entry-Level Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd80dc2e6636141e</t>
+          <t>https://www.indeed.com/viewjob?jk=8b5cdc524b199967</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>Westchester Medical Center Health Network</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Valhalla, NY, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,34 +5211,34 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Snowflake, SQL Server, Data Modeling, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b5cdc524b199967</t>
+          <t>https://www.indeed.com/viewjob?jk=d807a7856ebe08db</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Data Engineer, Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Westchester Medical Center Health Network</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Valhalla, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,34 +5246,34 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, SQL Server, Data Modeling, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, Databricks, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d807a7856ebe08db</t>
+          <t>https://www.indeed.com/viewjob?jk=b74ac1e46b3dfa89</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Enterprise Data &amp; Analytics</t>
+          <t>Cyber Architecture - Sr Advisor II</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,17 +5281,17 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, Databricks, Data Modeling, ELT, dbt</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b74ac1e46b3dfa89</t>
+          <t>https://www.indeed.com/viewjob?jk=f6692a3fd9db94db</t>
         </is>
       </c>
     </row>
@@ -5368,17 +5368,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>SSO Administrator</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Proxet</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,34 +5386,34 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
+          <t>AWS, S3, ECS, RDS, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b109c86f55c8c21f</t>
+          <t>https://www.indeed.com/viewjob?jk=2c123eaea5e60741</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>SSO Administrator</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,14 +5431,14 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=843b039e4e75f61f</t>
+          <t>https://www.indeed.com/viewjob?jk=b109c86f55c8c21f</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ead7f0da7c5db1</t>
+          <t>https://www.indeed.com/viewjob?jk=843b039e4e75f61f</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,14 +5501,14 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae8a17a1c6f39e3</t>
+          <t>https://www.indeed.com/viewjob?jk=c1ead7f0da7c5db1</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5c91aac0db662ae</t>
+          <t>https://www.indeed.com/viewjob?jk=1ae8a17a1c6f39e3</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>IT PROFESSIONAL-APPLICATIONS (Database Administrator) (HEC)</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>City of Houston, TX</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c369e1e8241c9f</t>
+          <t>https://www.indeed.com/viewjob?jk=e5c91aac0db662ae</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>DOCSIS Testing Engineer</t>
+          <t>IT PROFESSIONAL-APPLICATIONS (Database Administrator) (HEC)</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>City of Houston, TX</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,17 +5596,87 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1c369e1e8241c9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>DOCSIS Testing Engineer</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
           <t>AWS, Azure, Google Cloud Platform, Scala, NoSQL, ETL, ELT, Splunk, CI/CD, Docker</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=0e134c7566cf151c</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Identity AI / ML Engineer</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df69083a5f5407d8</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-04.xlsx
+++ b/results/job_matches_2026-03-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G150"/>
+  <dimension ref="A1:G116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Junior Oracle Apps Developer</t>
+          <t>Data Engineer/Python Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Zifo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, ECS, RDS, Azure, Blob Storage</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0adde35786282b2b</t>
+          <t>https://www.indeed.com/viewjob?jk=3419a1d7b4acb559</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer/Python Developer</t>
+          <t>Junior Oracle Apps Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Zifo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, ECS, RDS, Azure, Blob Storage</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3419a1d7b4acb559</t>
+          <t>https://www.indeed.com/viewjob?jk=0adde35786282b2b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (React + Node.js)-4</t>
+          <t>Software Engineer III: DevOps</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e082e26fc29250a3</t>
+          <t>https://www.indeed.com/viewjob?jk=bc952e4224a3aa24</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer III: DevOps</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Jersey Mikes Corporate</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Tinton Falls, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc952e4224a3aa24</t>
+          <t>https://www.indeed.com/viewjob?jk=31cf41e0387f0b72</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer, Client Authentication</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Jersey Mikes Corporate</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tinton Falls, NJ, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>IAM, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31cf41e0387f0b72</t>
+          <t>https://www.indeed.com/viewjob?jk=a908b362cb914674</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Client Authentication</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Quilt</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a908b362cb914674</t>
+          <t>https://www.indeed.com/viewjob?jk=27d883fd388e687a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer, ACVMax</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Quilt</t>
+          <t>ACV Auctions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,77 +696,77 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d883fd388e687a</t>
+          <t>https://www.indeed.com/viewjob?jk=6c28dd5d00192a5b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, ACVMax</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ACV Auctions</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c28dd5d00192a5b</t>
+          <t>https://www.indeed.com/viewjob?jk=7167050c109be2d4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer - AI Practice Team</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>American Bureau of Shipping (ABS)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Azure, Data Factory, Databricks, Event Hubs, BigQuery</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98e9bc7cd1938bfd</t>
+          <t>https://www.indeed.com/viewjob?jk=862a4a8989448fa0</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7167050c109be2d4</t>
+          <t>https://www.indeed.com/viewjob?jk=07e542bb4713fad0</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=862a4a8989448fa0</t>
+          <t>https://www.indeed.com/viewjob?jk=2c88dff775194e30</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07e542bb4713fad0</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ced45fe117deb8</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c88dff775194e30</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc8e0c810b3e7cd</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ced45fe117deb8</t>
+          <t>https://www.indeed.com/viewjob?jk=7791942c877daada</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc8e0c810b3e7cd</t>
+          <t>https://www.indeed.com/viewjob?jk=b6b39b9b56abc0bd</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7791942c877daada</t>
+          <t>https://www.indeed.com/viewjob?jk=648774ee33ca3b76</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6b39b9b56abc0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=a93ca1ad887e17f0</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648774ee33ca3b76</t>
+          <t>https://www.indeed.com/viewjob?jk=d963e90dfb3fa4d6</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a93ca1ad887e17f0</t>
+          <t>https://www.indeed.com/viewjob?jk=783ac47e6d62e414</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d963e90dfb3fa4d6</t>
+          <t>https://www.indeed.com/viewjob?jk=e511c7108cd6e82d</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783ac47e6d62e414</t>
+          <t>https://www.indeed.com/viewjob?jk=2a6a2ad30fc1236d</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e511c7108cd6e82d</t>
+          <t>https://www.indeed.com/viewjob?jk=e2d42f6d55a07b48</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a6a2ad30fc1236d</t>
+          <t>https://www.indeed.com/viewjob?jk=c423f392a018bf22</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2d42f6d55a07b48</t>
+          <t>https://www.indeed.com/viewjob?jk=cb49af32ea451f63</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c423f392a018bf22</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7468c4fe6bdb23</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb49af32ea451f63</t>
+          <t>https://www.indeed.com/viewjob?jk=3a3485c3c6153843</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7468c4fe6bdb23</t>
+          <t>https://www.indeed.com/viewjob?jk=ef4166ba4aa9b5a3</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a3485c3c6153843</t>
+          <t>https://www.indeed.com/viewjob?jk=91d6e4beb774dd25</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef4166ba4aa9b5a3</t>
+          <t>https://www.indeed.com/viewjob?jk=adcf2824745a050e</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91d6e4beb774dd25</t>
+          <t>https://www.indeed.com/viewjob?jk=64b296145590b995</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcf2824745a050e</t>
+          <t>https://www.indeed.com/viewjob?jk=8c4169879098b22b</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b296145590b995</t>
+          <t>https://www.indeed.com/viewjob?jk=44e1222f0eb14744</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c4169879098b22b</t>
+          <t>https://www.indeed.com/viewjob?jk=37bd1a8719f0aafc</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44e1222f0eb14744</t>
+          <t>https://www.indeed.com/viewjob?jk=e151b2c0a32e2723</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37bd1a8719f0aafc</t>
+          <t>https://www.indeed.com/viewjob?jk=c07dcca1b609463e</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e151b2c0a32e2723</t>
+          <t>https://www.indeed.com/viewjob?jk=c721bd4ca7bdffe1</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c07dcca1b609463e</t>
+          <t>https://www.indeed.com/viewjob?jk=e8e182c6058fd2a4</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c721bd4ca7bdffe1</t>
+          <t>https://www.indeed.com/viewjob?jk=4997f8f92f05b9d2</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8e182c6058fd2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=2a56481df82d7aa6</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4997f8f92f05b9d2</t>
+          <t>https://www.indeed.com/viewjob?jk=fb00c80fb9cb9b65</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a56481df82d7aa6</t>
+          <t>https://www.indeed.com/viewjob?jk=3fd1863254c88e5d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Sr. Data Platform Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Real Time Medical Systems</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb00c80fb9cb9b65</t>
+          <t>https://www.indeed.com/viewjob?jk=415686b53cfda723</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Sr. Data Platform Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Real Time Medical Systems</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fd1863254c88e5d</t>
+          <t>https://www.indeed.com/viewjob?jk=41a92f9802d4f918</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Data Platform Engineer</t>
+          <t>Senior Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Real Time Medical Systems</t>
+          <t>ALTRUIST</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=415686b53cfda723</t>
+          <t>https://www.indeed.com/viewjob?jk=b2b2e3b90367f3b4</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Data Platform Engineer</t>
+          <t>Senior Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Real Time Medical Systems</t>
+          <t>ALTRUIST</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41a92f9802d4f918</t>
+          <t>https://www.indeed.com/viewjob?jk=15721c69bc524693</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Infrastructure</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ALTRUIST</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,42 +2061,42 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2b2e3b90367f3b4</t>
+          <t>https://www.indeed.com/viewjob?jk=a6c4839e7fe64d8e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Infrastructure</t>
+          <t>Enterprise Data Platform Engineer – Washington, DC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ALTRUIST</t>
+          <t>Creative Information Technology India</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Photon, Scala, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,207 +2106,207 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15721c69bc524693</t>
+          <t>https://www.indeed.com/viewjob?jk=0a74e373b48da5fc</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II,</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables</t>
+          <t>AWS, Redshift, ECS, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6c4839e7fe64d8e</t>
+          <t>https://www.indeed.com/viewjob?jk=b4edb591674d441f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AI/ML Architect with Databricks , AWS</t>
+          <t>Blockchain Java Backend Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Prosper, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5774b4765e1a54ce</t>
+          <t>https://www.indeed.com/viewjob?jk=e49019e3e57d794c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AI/ML Architect with Databricks , AWS</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Vytwo Technologies</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Prosper, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29c402e4a2f5220b</t>
+          <t>https://www.indeed.com/viewjob?jk=9188fd233f524c42</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>aws Databricks architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cloudious</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03a1eccc5605f732</t>
+          <t>https://www.indeed.com/viewjob?jk=4cc63cdd2328277c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer II,</t>
+          <t>Google Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>NMI</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4edb591674d441f</t>
+          <t>https://www.indeed.com/viewjob?jk=e7cac4b03aa7cfe7</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Blockchain Java Backend Engineer</t>
+          <t>Software Engineer, AI Analytics</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Residex, LLC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,102 +2316,102 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e49019e3e57d794c</t>
+          <t>https://www.indeed.com/viewjob?jk=3b994e1736909aed</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Google Cloud Data Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Cloudious</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0997a11d6aaf4e73</t>
+          <t>https://www.indeed.com/viewjob?jk=73dc517b82db140b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer - DevOps/ DataOps</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, DataOps, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9188fd233f524c42</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ed15cfc823b0b7</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cc63cdd2328277c</t>
+          <t>https://www.indeed.com/viewjob?jk=b08c3dc1b325be49</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Google Cloud Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NMI</t>
+          <t>SRS Distribution</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,67 +2456,67 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7cac4b03aa7cfe7</t>
+          <t>https://www.indeed.com/viewjob?jk=4cde050af8749e53</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer, AI Analytics</t>
+          <t>SQL Developer - Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Residex, LLC</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b994e1736909aed</t>
+          <t>https://www.indeed.com/viewjob?jk=41d495363374161e</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Engineer - DevOps/ DataOps</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, DataOps, MLOps, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,19 +2526,19 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ed15cfc823b0b7</t>
+          <t>https://www.indeed.com/viewjob?jk=bf6f08ab2860bc5c</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Ncontracts</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2547,11 +2547,11 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b08c3dc1b325be49</t>
+          <t>https://www.indeed.com/viewjob?jk=da52963e4860aaaa</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Cloud Data Platform Administrator - 26-02191</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SRS Distribution</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cde050af8749e53</t>
+          <t>https://www.indeed.com/viewjob?jk=3695a4ce423ac8e5</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SQL Developer - Enterprise Data &amp; Analytics</t>
+          <t>Cloud Data Platform Administrator - 26-02191</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41d495363374161e</t>
+          <t>https://www.indeed.com/viewjob?jk=67be12c15c92c4c5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Data Platform Administrator - 26-02191</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf6f08ab2860bc5c</t>
+          <t>https://www.indeed.com/viewjob?jk=861fabb5acea2ca4</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Cloud Data Platform Administrator - 26-02191</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Ncontracts</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,17 +2691,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da52963e4860aaaa</t>
+          <t>https://www.indeed.com/viewjob?jk=6235a9d4364b9757</t>
         </is>
       </c>
     </row>
@@ -2848,17 +2848,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PDM Implementation Data Architect</t>
+          <t>SSO Administrator</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3576de9e88dd4c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=a9064a81c91aa262</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Hitachi Digital Services</t>
+          <t>ivo</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33510d4bb406c6e2</t>
+          <t>https://www.indeed.com/viewjob?jk=8bc5aaef611937ad</t>
         </is>
       </c>
     </row>
@@ -2923,20 +2923,20 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ROLLER</t>
+          <t>SRR Consultants</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Glue, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,67 +2946,67 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb709659d664135</t>
+          <t>https://www.indeed.com/viewjob?jk=88619a1e983eef30</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer, CDC</t>
+          <t>Senior Data Engineer, Data Lakehouse Infrastructure</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>DRT Strategies, Inc.</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Scala, ETL, Power BI, Tableau, CI/CD, Docker</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a223a368864e5d1b</t>
+          <t>https://www.indeed.com/viewjob?jk=e899ea40640da235</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SQL Server Database Engineer</t>
+          <t>AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>IDBNY</t>
+          <t>Seqster PDM, Inc</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, HBase, Snowflake, Oracle, SQL Server, MongoDB</t>
+          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,172 +3016,172 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15c2f3c4f1ddf6ac</t>
+          <t>https://www.indeed.com/viewjob?jk=191c0857581cffe3</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Cloud Identity Architect</t>
+          <t>Risk Data AI/ML Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdd1e41d5949d150</t>
+          <t>https://www.indeed.com/viewjob?jk=979402388d34b409</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Senior Software Engineer II - AI/ML</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ivo</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bc5aaef611937ad</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0bc9a390582054</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Databricks AI Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>Powerplan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd0439895496e24</t>
+          <t>https://www.indeed.com/viewjob?jk=3b5753d39b44c782</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Recursion Technologies, Inc</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6138105d361c110c</t>
+          <t>https://www.indeed.com/viewjob?jk=e1b9bbef981d9232</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer, Data Product</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SRR Consultants</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88619a1e983eef30</t>
+          <t>https://www.indeed.com/viewjob?jk=351b720407fa6f6d</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Lakehouse Infrastructure</t>
+          <t>Analytics, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,67 +3226,67 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e899ea40640da235</t>
+          <t>https://www.indeed.com/viewjob?jk=c24274a4aa989f95</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AWS DevOps Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Seqster PDM, Inc</t>
+          <t>Waters</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milford, MA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=191c0857581cffe3</t>
+          <t>https://www.indeed.com/viewjob?jk=1975adb5bfc7de33</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-2</t>
+          <t>Software Engineer III - Java/Spark/AWS</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, EMR, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,67 +3296,67 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f9103ddd4f544e</t>
+          <t>https://www.indeed.com/viewjob?jk=c95674c932d41fb6</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>Tableau Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Michael Kors</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>East Rutherford, NJ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Redshift, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d602908669423e</t>
+          <t>https://www.indeed.com/viewjob?jk=904e084e965a45c4</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Rogue Community College</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,207 +3366,207 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10de5f0ca2f7673d</t>
+          <t>https://www.indeed.com/viewjob?jk=7f9335cc41b5edf2</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6750fd9ad4e72e</t>
+          <t>https://www.indeed.com/viewjob?jk=a8b55e090bbab627</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45db6ac50eb5587</t>
+          <t>https://www.indeed.com/viewjob?jk=e65cdb592eb57da5</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Clarksville, TN, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1c0f7e27e90a87e</t>
+          <t>https://www.indeed.com/viewjob?jk=e1a1d694cac30055</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4dc81e5cd9b6b72</t>
+          <t>https://www.indeed.com/viewjob?jk=8a517be0e10b2a44</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>Senior Data Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14fea47c1dbfabac</t>
+          <t>https://www.indeed.com/viewjob?jk=60f6c2aecd2d1bdf</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, Kafka, Dimensional Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,102 +3576,102 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02d7bcc2bd0697b0</t>
+          <t>https://www.indeed.com/viewjob?jk=503c92a0918e2779</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Analytics &amp; AI</t>
+          <t>Software Engineer (Backend) - Global Dining</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50e0ff85e5f89851</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f71d52efce43e2</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Full Stack Web Developer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>UP Management LLC</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Bedford, TX, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e000e4c87bc0a4b</t>
+          <t>https://www.indeed.com/viewjob?jk=7f3534222ab81e17</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Risk Data AI/ML Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,102 +3681,102 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=979402388d34b409</t>
+          <t>https://www.indeed.com/viewjob?jk=f9637232a826c3ad</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Databricks AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Powerplan</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5753d39b44c782</t>
+          <t>https://www.indeed.com/viewjob?jk=e5b3837921976566</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - AI/ML</t>
+          <t>Senior Data Engineer - Microsoft Fabric</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>EoS Fitness</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT, Power BI</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0bc9a390582054</t>
+          <t>https://www.indeed.com/viewjob?jk=7bd7f3590528db3c</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend/Cloud Services</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Hunter Industries</t>
+          <t>PGA TOUR Superstore</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, DynamoDB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab5afc3cedfad680</t>
+          <t>https://www.indeed.com/viewjob?jk=73bdb2d180484ce2</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1b9bbef981d9232</t>
+          <t>https://www.indeed.com/viewjob?jk=110f275787ec7bdb</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Network IoT Engineer</t>
+          <t>Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Middesk</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, RDS, Azure, Spark, Data Modeling, Terraform, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,67 +3856,67 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da29d3af250447a</t>
+          <t>https://www.indeed.com/viewjob?jk=514717df8eb087ca</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Product</t>
+          <t>Sr. Software Engineer, Data, Autonomy</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351b720407fa6f6d</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3560765ed8e488</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Analytics, Full-Stack Engineer</t>
+          <t>Customer Reliability Engineer, Airflow</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24274a4aa989f95</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac244565083c1d9</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Waters</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Milford, MA, US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,67 +3961,67 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1975adb5bfc7de33</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf4b62fe049b84e</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8b55e090bbab627</t>
+          <t>https://www.indeed.com/viewjob?jk=57ca41478bb936cd</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Salesforce Architect - Senior</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CommunityForce Inc.</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, Google Cloud Platform, Vertex AI, Scala</t>
+          <t>ECS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,67 +4031,67 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be47bff9f1c0f69d</t>
+          <t>https://www.indeed.com/viewjob?jk=7d236cba8a6e8ae3</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>.NET Angular Reporting Developer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, Star Schema, ETL, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e65cdb592eb57da5</t>
+          <t>https://www.indeed.com/viewjob?jk=f21a948f0ac42414</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Software Engineer - Master</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Clarksville, TN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,67 +4101,67 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1a1d694cac30055</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb1207979169793</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Data Engineer - GRC Technology</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Rogue Community College</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Power BI</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f9335cc41b5edf2</t>
+          <t>https://www.indeed.com/viewjob?jk=8842e67bf37c518a</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Backend)</t>
+          <t>Sr. Data Engineer, Engineering &amp; Ops</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>PlanHub</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, Scala, MySQL, DynamoDB, CI/CD, GitHub Actions</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, ELT, dbt, MLOps, Airflow</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,14 +4171,14 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b63efe5dfc4a026c</t>
+          <t>https://www.indeed.com/viewjob?jk=df536a2594fa5881</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4192,11 +4192,11 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a517be0e10b2a44</t>
+          <t>https://www.indeed.com/viewjob?jk=dcb7ea8003fbc5dc</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Platform</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Callaway Golf</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,67 +4241,67 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f6c2aecd2d1bdf</t>
+          <t>https://www.indeed.com/viewjob?jk=2cf949704a694c55</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Microsoft Entra</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, Kafka, Dimensional Modeling, ETL, Airflow</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503c92a0918e2779</t>
+          <t>https://www.indeed.com/viewjob?jk=f61688604ed96074</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Engineering Java/Python</t>
+          <t>Entry-Level Data Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dfc1c1ddf5b07e8</t>
+          <t>https://www.indeed.com/viewjob?jk=dd80dc2e6636141e</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
+          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,102 +4346,102 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab7b07d708701fa</t>
+          <t>https://www.indeed.com/viewjob?jk=8b5cdc524b199967</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend) - Global Dining</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Westchester Medical Center Health Network</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Valhalla, NY, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Snowflake, SQL Server, Data Modeling, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f71d52efce43e2</t>
+          <t>https://www.indeed.com/viewjob?jk=d807a7856ebe08db</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Sr. Data Engineer, Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, Databricks, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f3534222ab81e17</t>
+          <t>https://www.indeed.com/viewjob?jk=b74ac1e46b3dfa89</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer, Attribution Expansion</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5b3837921976566</t>
+          <t>https://www.indeed.com/viewjob?jk=539a18aebac4ef5f</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Microsoft Fabric</t>
+          <t>Senior Data Engineer, Attribution Expansion</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>EoS Fitness</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT, Power BI</t>
+          <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,1197 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bd7f3590528db3c</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>PGA TOUR Superstore</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Roswell, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=73bdb2d180484ce2</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Azure Data Engineer</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Gilbert, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=110f275787ec7bdb</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Software Engineer, Data Platform</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Middesk</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, RDS, Azure, Spark, Data Modeling, Terraform, Kubernetes, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=514717df8eb087ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer, Data, Autonomy</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Rivian</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, DynamoDB, CI/CD</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3560765ed8e488</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Cloud Infrastructure Architect</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Ford Motor Company</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=518fd46821df25d8</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Al Warren Oil Company, Inc.</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Bensenville, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6304fa25b90dcc51</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Al Warren Oil Company, Inc.</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9a4e15b6a0305b12</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Altom Transport, Inc.</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=40b321afc8939ff9</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Salesforce Architect - Senior</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>CommunityForce Inc.</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Ashburn, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>ECS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7d236cba8a6e8ae3</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Altom Transport, Inc.</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=176afb0ac80a4191</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Senior Database Reliability Engineer (Oracle &amp; Automation Focus)</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>BILL</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Oracle, DynamoDB, NoSQL, Splunk, CI/CD, Terraform, Git</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=104eb630cab2bc86</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Reporting Engineer</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Surgery Partners</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=57ca41478bb936cd</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Skechers</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Hermosa Beach, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf4b62fe049b84e</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>.NET Angular Reporting Developer</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, Star Schema, ETL, Power BI, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f21a948f0ac42414</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Software Engineer - Master</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Equifax</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb1207979169793</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Senior Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>TRM Labs</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, dbt, Power BI, Tableau, CI/CD</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dcb7ea8003fbc5dc</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Sr Data Engineer</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Callaway Golf</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Carlsbad, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2cf949704a694c55</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Microsoft Entra</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f61688604ed96074</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Entry-Level Data Engineer</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Warren, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dd80dc2e6636141e</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Lyric</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8b5cdc524b199967</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Westchester Medical Center Health Network</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Valhalla, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Snowflake, SQL Server, Data Modeling, ELT, Power BI, Tableau, CI/CD</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d807a7856ebe08db</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Sr. Data Engineer, Enterprise Data &amp; Analytics</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Rivian</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, Databricks, Data Modeling, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b74ac1e46b3dfa89</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Cyber Architecture - Sr Advisor II</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Fiserv</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f6692a3fd9db94db</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer, Attribution Expansion</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>TRM Labs</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=539a18aebac4ef5f</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer, Attribution Expansion</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>TRM Labs</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=26436308d22e947d</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Solution Architect</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Proxet</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>AWS, S3, ECS, RDS, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2c123eaea5e60741</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>SSO Administrator</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b109c86f55c8c21f</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Senior Engineer - .NET</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=843b039e4e75f61f</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ead7f0da7c5db1</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae8a17a1c6f39e3</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Senior Engineer - .NET</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e5c91aac0db662ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>IT PROFESSIONAL-APPLICATIONS (Database Administrator) (HEC)</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>City of Houston, TX</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c369e1e8241c9f</t>
-        </is>
-      </c>
-    </row>
-    <row